--- a/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
   <si>
     <t>DAVA</t>
   </si>
@@ -656,131 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
@@ -790,92 +790,95 @@
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>233700</v>
+        <v>234100</v>
       </c>
       <c r="E8" s="3">
-        <v>235500</v>
+        <v>240200</v>
       </c>
       <c r="F8" s="3">
-        <v>252500</v>
+        <v>242000</v>
       </c>
       <c r="G8" s="3">
-        <v>254600</v>
+        <v>259500</v>
       </c>
       <c r="H8" s="3">
-        <v>243400</v>
+        <v>261700</v>
       </c>
       <c r="I8" s="3">
-        <v>223800</v>
+        <v>250200</v>
       </c>
       <c r="J8" s="3">
+        <v>230000</v>
+      </c>
+      <c r="K8" s="3">
         <v>209900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>199900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>186900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>165800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>131500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>123200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>112500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>110400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>122700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>117100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>112400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>105200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>97300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>94800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>87700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>79500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>201800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>65200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>62000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>56100</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
@@ -885,92 +888,95 @@
       <c r="AG8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>166200</v>
+        <v>176800</v>
       </c>
       <c r="E9" s="3">
-        <v>161600</v>
+        <v>170800</v>
       </c>
       <c r="F9" s="3">
-        <v>172300</v>
+        <v>166100</v>
       </c>
       <c r="G9" s="3">
-        <v>164700</v>
+        <v>177100</v>
       </c>
       <c r="H9" s="3">
-        <v>159700</v>
+        <v>169300</v>
       </c>
       <c r="I9" s="3">
-        <v>152200</v>
+        <v>164200</v>
       </c>
       <c r="J9" s="3">
+        <v>156400</v>
+      </c>
+      <c r="K9" s="3">
         <v>141200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>133800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>120100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>109100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>86400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>79900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>73600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>77400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>75200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>106700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>71900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>69600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>64000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>61300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>58000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>51800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>136200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>44400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>42200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>38000</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
@@ -980,92 +986,95 @@
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>67500</v>
+        <v>57300</v>
       </c>
       <c r="E10" s="3">
-        <v>73900</v>
+        <v>69400</v>
       </c>
       <c r="F10" s="3">
-        <v>80200</v>
+        <v>75900</v>
       </c>
       <c r="G10" s="3">
-        <v>89900</v>
+        <v>82400</v>
       </c>
       <c r="H10" s="3">
-        <v>83700</v>
+        <v>92400</v>
       </c>
       <c r="I10" s="3">
-        <v>71700</v>
+        <v>86000</v>
       </c>
       <c r="J10" s="3">
+        <v>73600</v>
+      </c>
+      <c r="K10" s="3">
         <v>68700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>66000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>66800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>56700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>45100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>43400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>38900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>33000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>47500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>40500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>35600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>33300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>33500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>29700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>27700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>65600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>20900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>19700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>18100</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1075,8 +1084,11 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1110,8 +1122,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1205,8 +1218,11 @@
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1300,92 +1316,95 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>900</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="H14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>800</v>
       </c>
-      <c r="F14" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="G14" s="3">
-        <v>2900</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="M14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>1600</v>
       </c>
-      <c r="I14" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>800</v>
-      </c>
-      <c r="L14" s="3">
-        <v>1500</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD14" s="3">
         <v>500</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1395,71 +1414,74 @@
       <c r="AG14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>5200</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H15" s="3">
         <v>4900</v>
       </c>
-      <c r="G15" s="3">
-        <v>4800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>4500</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="I15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K15" s="3">
         <v>4200</v>
-      </c>
-      <c r="K15" s="3">
-        <v>3900</v>
       </c>
       <c r="L15" s="3">
         <v>3900</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N15" s="3">
+      <c r="M15" s="3">
+        <v>3900</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3">
         <v>1800</v>
-      </c>
-      <c r="O15" s="3">
-        <v>2100</v>
       </c>
       <c r="P15" s="3">
         <v>2100</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R15" s="3">
+      <c r="Q15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3">
         <v>2200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1900</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W15" s="3">
         <v>1300</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1469,8 +1491,8 @@
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1490,8 +1512,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1522,92 +1547,93 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>213800</v>
+        <v>228200</v>
       </c>
       <c r="E17" s="3">
-        <v>207300</v>
+        <v>219700</v>
       </c>
       <c r="F17" s="3">
-        <v>215200</v>
+        <v>213000</v>
       </c>
       <c r="G17" s="3">
-        <v>213900</v>
+        <v>221100</v>
       </c>
       <c r="H17" s="3">
-        <v>209600</v>
+        <v>219900</v>
       </c>
       <c r="I17" s="3">
-        <v>190700</v>
+        <v>215400</v>
       </c>
       <c r="J17" s="3">
+        <v>196100</v>
+      </c>
+      <c r="K17" s="3">
         <v>178400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>175200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>156600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>141200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>110400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>106800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>98700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>102000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>104000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>132800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>92500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>93300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>87400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>82900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>77400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>71200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>177300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>57200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>52900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>47800</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1617,92 +1643,95 @@
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>20000</v>
+        <v>5900</v>
       </c>
       <c r="E18" s="3">
-        <v>28200</v>
+        <v>20500</v>
       </c>
       <c r="F18" s="3">
-        <v>37300</v>
+        <v>29000</v>
       </c>
       <c r="G18" s="3">
-        <v>40600</v>
+        <v>38300</v>
       </c>
       <c r="H18" s="3">
-        <v>33800</v>
+        <v>41800</v>
       </c>
       <c r="I18" s="3">
-        <v>33100</v>
+        <v>34800</v>
       </c>
       <c r="J18" s="3">
+        <v>34000</v>
+      </c>
+      <c r="K18" s="3">
         <v>31500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>24700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>30300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>24500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>21100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>18800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-15600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>19900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>11900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>9900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>12000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>10300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>8400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>24500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>8000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>9000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>8200</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1712,8 +1741,11 @@
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1747,92 +1779,93 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1500</v>
+        <v>7600</v>
       </c>
       <c r="E20" s="3">
-        <v>2700</v>
+        <v>1600</v>
       </c>
       <c r="F20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
-        <v>-15500</v>
-      </c>
       <c r="H20" s="3">
-        <v>14000</v>
+        <v>-15900</v>
       </c>
       <c r="I20" s="3">
-        <v>7300</v>
+        <v>14400</v>
       </c>
       <c r="J20" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-7900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1842,92 +1875,95 @@
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>33200</v>
+        <v>13400</v>
       </c>
       <c r="E21" s="3">
-        <v>30700</v>
+        <v>34100</v>
       </c>
       <c r="F21" s="3">
-        <v>37900</v>
+        <v>31600</v>
       </c>
       <c r="G21" s="3">
-        <v>26000</v>
+        <v>39000</v>
       </c>
       <c r="H21" s="3">
-        <v>57400</v>
+        <v>26700</v>
       </c>
       <c r="I21" s="3">
-        <v>39700</v>
+        <v>59000</v>
       </c>
       <c r="J21" s="3">
+        <v>40800</v>
+      </c>
+      <c r="K21" s="3">
         <v>32500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>24500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>40400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>24500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>18100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>13300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>16600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>24700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-22900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>29500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>14400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>11600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>12400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>11000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>29000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>7900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>8900</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1937,8 +1973,11 @@
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2032,92 +2071,95 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>21500</v>
+        <v>13500</v>
       </c>
       <c r="E23" s="3">
-        <v>30900</v>
+        <v>22100</v>
       </c>
       <c r="F23" s="3">
-        <v>37700</v>
+        <v>31800</v>
       </c>
       <c r="G23" s="3">
-        <v>25100</v>
+        <v>38700</v>
       </c>
       <c r="H23" s="3">
-        <v>47800</v>
+        <v>25800</v>
       </c>
       <c r="I23" s="3">
-        <v>40300</v>
+        <v>49200</v>
       </c>
       <c r="J23" s="3">
+        <v>41400</v>
+      </c>
+      <c r="K23" s="3">
         <v>32100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>24200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>31600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>23000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>19300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>24400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-23500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>23800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>14300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>10100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>12400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>23200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>7900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>7200</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2127,92 +2169,95 @@
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>6100</v>
+        <v>2900</v>
       </c>
       <c r="E24" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G24" s="3">
+        <v>7700</v>
+      </c>
+      <c r="H24" s="3">
+        <v>6700</v>
+      </c>
+      <c r="I24" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J24" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K24" s="3">
+        <v>7200</v>
+      </c>
+      <c r="L24" s="3">
+        <v>4700</v>
+      </c>
+      <c r="M24" s="3">
+        <v>5500</v>
+      </c>
+      <c r="N24" s="3">
+        <v>3200</v>
+      </c>
+      <c r="O24" s="3">
+        <v>4100</v>
+      </c>
+      <c r="P24" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="R24" s="3">
+        <v>800</v>
+      </c>
+      <c r="S24" s="3">
+        <v>4900</v>
+      </c>
+      <c r="T24" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="U24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="V24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="W24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="X24" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z24" s="3">
         <v>2300</v>
       </c>
-      <c r="F24" s="3">
-        <v>7500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>6500</v>
-      </c>
-      <c r="H24" s="3">
-        <v>8500</v>
-      </c>
-      <c r="I24" s="3">
-        <v>6800</v>
-      </c>
-      <c r="J24" s="3">
-        <v>7200</v>
-      </c>
-      <c r="K24" s="3">
-        <v>4700</v>
-      </c>
-      <c r="L24" s="3">
-        <v>5500</v>
-      </c>
-      <c r="M24" s="3">
-        <v>3200</v>
-      </c>
-      <c r="N24" s="3">
-        <v>4100</v>
-      </c>
-      <c r="O24" s="3">
-        <v>3300</v>
-      </c>
-      <c r="P24" s="3">
-        <v>2400</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>800</v>
-      </c>
-      <c r="R24" s="3">
-        <v>4900</v>
-      </c>
-      <c r="S24" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="T24" s="3">
-        <v>4000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>3000</v>
-      </c>
-      <c r="V24" s="3">
-        <v>1700</v>
-      </c>
-      <c r="W24" s="3">
-        <v>2600</v>
-      </c>
-      <c r="X24" s="3">
-        <v>800</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1600</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2222,8 +2267,11 @@
       <c r="AG24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2317,92 +2365,95 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>15300</v>
+        <v>10600</v>
       </c>
       <c r="E26" s="3">
-        <v>28600</v>
+        <v>15800</v>
       </c>
       <c r="F26" s="3">
-        <v>30200</v>
+        <v>29400</v>
       </c>
       <c r="G26" s="3">
-        <v>18600</v>
+        <v>31100</v>
       </c>
       <c r="H26" s="3">
-        <v>39400</v>
+        <v>19200</v>
       </c>
       <c r="I26" s="3">
-        <v>33500</v>
+        <v>40500</v>
       </c>
       <c r="J26" s="3">
+        <v>34500</v>
+      </c>
+      <c r="K26" s="3">
         <v>24900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>26000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>15200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-18800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>19800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>11300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>8400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>9800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>6300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>18200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5600</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2412,92 +2463,95 @@
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>15300</v>
+        <v>10600</v>
       </c>
       <c r="E27" s="3">
-        <v>28600</v>
+        <v>15800</v>
       </c>
       <c r="F27" s="3">
-        <v>30200</v>
+        <v>29400</v>
       </c>
       <c r="G27" s="3">
-        <v>18600</v>
+        <v>31100</v>
       </c>
       <c r="H27" s="3">
-        <v>39400</v>
+        <v>19200</v>
       </c>
       <c r="I27" s="3">
-        <v>33500</v>
+        <v>40500</v>
       </c>
       <c r="J27" s="3">
+        <v>34500</v>
+      </c>
+      <c r="K27" s="3">
         <v>24900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>26000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>15200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-18800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>19800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>11300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>8400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>9800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>18200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5600</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2507,8 +2561,11 @@
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2602,8 +2659,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2697,8 +2757,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2792,8 +2855,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2887,92 +2953,95 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1500</v>
+        <v>-7600</v>
       </c>
       <c r="E32" s="3">
-        <v>-2700</v>
+        <v>-1600</v>
       </c>
       <c r="F32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
-        <v>15500</v>
-      </c>
       <c r="H32" s="3">
-        <v>-14000</v>
+        <v>15900</v>
       </c>
       <c r="I32" s="3">
-        <v>-7300</v>
+        <v>-14400</v>
       </c>
       <c r="J32" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1000</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2982,92 +3051,95 @@
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>15300</v>
+        <v>10600</v>
       </c>
       <c r="E33" s="3">
-        <v>28600</v>
+        <v>15800</v>
       </c>
       <c r="F33" s="3">
-        <v>30200</v>
+        <v>29400</v>
       </c>
       <c r="G33" s="3">
-        <v>18600</v>
+        <v>31100</v>
       </c>
       <c r="H33" s="3">
-        <v>39400</v>
+        <v>19200</v>
       </c>
       <c r="I33" s="3">
-        <v>33500</v>
+        <v>40500</v>
       </c>
       <c r="J33" s="3">
+        <v>34500</v>
+      </c>
+      <c r="K33" s="3">
         <v>24900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>26000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>15200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-18800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>19800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>11300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>8400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>9800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>18200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5600</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3077,8 +3149,11 @@
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3172,92 +3247,95 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>15300</v>
+        <v>10600</v>
       </c>
       <c r="E35" s="3">
-        <v>28600</v>
+        <v>15800</v>
       </c>
       <c r="F35" s="3">
-        <v>30200</v>
+        <v>29400</v>
       </c>
       <c r="G35" s="3">
-        <v>18600</v>
+        <v>31100</v>
       </c>
       <c r="H35" s="3">
-        <v>39400</v>
+        <v>19200</v>
       </c>
       <c r="I35" s="3">
-        <v>33500</v>
+        <v>40500</v>
       </c>
       <c r="J35" s="3">
+        <v>34500</v>
+      </c>
+      <c r="K35" s="3">
         <v>24900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>26000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>15200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-18800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>19800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>11300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>8400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>9800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>18200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5600</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3267,97 +3345,100 @@
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3367,8 +3448,11 @@
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3402,8 +3486,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3437,89 +3522,90 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>208700</v>
+        <v>253200</v>
       </c>
       <c r="E41" s="3">
-        <v>204300</v>
+        <v>214500</v>
       </c>
       <c r="F41" s="3">
-        <v>247100</v>
+        <v>210000</v>
       </c>
       <c r="G41" s="3">
-        <v>229900</v>
+        <v>254000</v>
       </c>
       <c r="H41" s="3">
-        <v>226300</v>
+        <v>236300</v>
       </c>
       <c r="I41" s="3">
-        <v>202000</v>
+        <v>232600</v>
       </c>
       <c r="J41" s="3">
+        <v>207600</v>
+      </c>
+      <c r="K41" s="3">
         <v>149400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>144700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>104000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>86700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>92300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>98600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>82800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>123600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>116000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>107700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>114100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>96400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>79000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>67400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>55200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>19500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>32700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>21700</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,37 +3618,40 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E42" s="3">
         <v>100</v>
       </c>
       <c r="F42" s="3">
+        <v>100</v>
+      </c>
+      <c r="G42" s="3">
         <v>200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>600</v>
-      </c>
-      <c r="L42" s="3">
-        <v>700</v>
       </c>
       <c r="M42" s="3">
         <v>700</v>
@@ -3580,7 +3669,7 @@
         <v>700</v>
       </c>
       <c r="R42" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="S42" s="3">
         <v>800</v>
@@ -3588,8 +3677,8 @@
       <c r="T42" s="3">
         <v>800</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
+      <c r="U42" s="3">
+        <v>800</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
@@ -3606,8 +3695,8 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -3627,89 +3716,92 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>237300</v>
+        <v>220100</v>
       </c>
       <c r="E43" s="3">
-        <v>225700</v>
+        <v>243900</v>
       </c>
       <c r="F43" s="3">
-        <v>228500</v>
+        <v>232000</v>
       </c>
       <c r="G43" s="3">
-        <v>218500</v>
+        <v>234900</v>
       </c>
       <c r="H43" s="3">
-        <v>240300</v>
+        <v>224500</v>
       </c>
       <c r="I43" s="3">
-        <v>204700</v>
+        <v>247000</v>
       </c>
       <c r="J43" s="3">
+        <v>210400</v>
+      </c>
+      <c r="K43" s="3">
         <v>199500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>183800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>180400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>148000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>129500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>110300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>112800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>104300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>108700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>107000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>93700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>91600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>84800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>84900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>80800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>68600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>64900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>64400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>59300</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3722,8 +3814,11 @@
       <c r="AG43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3794,17 +3889,17 @@
         <v>0</v>
       </c>
       <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
         <v>100</v>
       </c>
-      <c r="AA44" s="3">
-        <v>0</v>
-      </c>
       <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3">
         <v>100</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3817,8 +3912,11 @@
       <c r="AG44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3912,89 +4010,92 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>446100</v>
+        <v>473600</v>
       </c>
       <c r="E46" s="3">
-        <v>430100</v>
+        <v>458500</v>
       </c>
       <c r="F46" s="3">
-        <v>475800</v>
+        <v>442000</v>
       </c>
       <c r="G46" s="3">
-        <v>448700</v>
+        <v>489100</v>
       </c>
       <c r="H46" s="3">
-        <v>467000</v>
+        <v>461100</v>
       </c>
       <c r="I46" s="3">
-        <v>407100</v>
+        <v>480000</v>
       </c>
       <c r="J46" s="3">
+        <v>418500</v>
+      </c>
+      <c r="K46" s="3">
         <v>349300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>329100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>285100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>235400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>222500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>209600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>196300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>228700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>225500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>215500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>208600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>188000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>163800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>152400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>136000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>88000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>77200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>97100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>81100</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4007,65 +4108,68 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3900</v>
+        <v>8100</v>
       </c>
       <c r="E47" s="3">
-        <v>6500</v>
+        <v>4100</v>
       </c>
       <c r="F47" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G47" s="3">
         <v>2500</v>
       </c>
-      <c r="G47" s="3">
-        <v>1700</v>
-      </c>
       <c r="H47" s="3">
-        <v>3500</v>
+        <v>1800</v>
       </c>
       <c r="I47" s="3">
-        <v>2800</v>
+        <v>3600</v>
       </c>
       <c r="J47" s="3">
-        <v>200</v>
+        <v>2900</v>
       </c>
       <c r="K47" s="3">
         <v>200</v>
       </c>
       <c r="L47" s="3">
+        <v>200</v>
+      </c>
+      <c r="M47" s="3">
         <v>300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1500</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,14 +4179,14 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>3</v>
+      <c r="AA47" s="3">
+        <v>0</v>
       </c>
       <c r="AB47" s="3" t="s">
         <v>3</v>
@@ -4102,89 +4206,92 @@
       <c r="AG47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>111200</v>
+        <v>99600</v>
       </c>
       <c r="E48" s="3">
-        <v>112900</v>
+        <v>114300</v>
       </c>
       <c r="F48" s="3">
-        <v>105700</v>
+        <v>116100</v>
       </c>
       <c r="G48" s="3">
-        <v>107700</v>
+        <v>108600</v>
       </c>
       <c r="H48" s="3">
-        <v>102900</v>
+        <v>110700</v>
       </c>
       <c r="I48" s="3">
-        <v>89400</v>
+        <v>105800</v>
       </c>
       <c r="J48" s="3">
+        <v>91900</v>
+      </c>
+      <c r="K48" s="3">
         <v>86200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>87400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>89500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>87500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>62700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>68900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>72400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>77900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>81500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>83000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>65700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>14500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10400</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4197,89 +4304,92 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>403500</v>
+        <v>404600</v>
       </c>
       <c r="E49" s="3">
-        <v>380900</v>
+        <v>414800</v>
       </c>
       <c r="F49" s="3">
-        <v>295100</v>
+        <v>391500</v>
       </c>
       <c r="G49" s="3">
-        <v>303700</v>
+        <v>303300</v>
       </c>
       <c r="H49" s="3">
-        <v>259200</v>
+        <v>312100</v>
       </c>
       <c r="I49" s="3">
-        <v>250700</v>
+        <v>266400</v>
       </c>
       <c r="J49" s="3">
+        <v>257700</v>
+      </c>
+      <c r="K49" s="3">
         <v>251200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>239500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>246300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>233800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>178500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>161300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>167700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>116800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>127400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>124000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>89100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>90200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>93200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>96100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>94900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>92900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>89600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>93700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>41900</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4292,8 +4402,11 @@
       <c r="AG49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4387,8 +4500,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4482,89 +4598,92 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>25600</v>
+        <v>27200</v>
       </c>
       <c r="E52" s="3">
+        <v>26300</v>
+      </c>
+      <c r="F52" s="3">
+        <v>25700</v>
+      </c>
+      <c r="G52" s="3">
+        <v>17200</v>
+      </c>
+      <c r="H52" s="3">
+        <v>17200</v>
+      </c>
+      <c r="I52" s="3">
         <v>25000</v>
       </c>
-      <c r="F52" s="3">
-        <v>16800</v>
-      </c>
-      <c r="G52" s="3">
-        <v>16700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>24300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>21400</v>
-      </c>
       <c r="J52" s="3">
+        <v>22000</v>
+      </c>
+      <c r="K52" s="3">
         <v>22300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>27100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>30300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>24900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>18700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>15600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>13400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>13100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6300</v>
-      </c>
-      <c r="W52" s="3">
-        <v>3300</v>
       </c>
       <c r="X52" s="3">
         <v>3300</v>
       </c>
       <c r="Y52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Z52" s="3">
         <v>3200</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>1200</v>
       </c>
       <c r="AA52" s="3">
         <v>1200</v>
       </c>
       <c r="AB52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC52" s="3">
         <v>1100</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4577,8 +4696,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4672,89 +4794,92 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>990300</v>
+        <v>1013200</v>
       </c>
       <c r="E54" s="3">
-        <v>955400</v>
+        <v>1017800</v>
       </c>
       <c r="F54" s="3">
-        <v>895800</v>
+        <v>982000</v>
       </c>
       <c r="G54" s="3">
-        <v>878500</v>
+        <v>920800</v>
       </c>
       <c r="H54" s="3">
-        <v>856900</v>
+        <v>902900</v>
       </c>
       <c r="I54" s="3">
-        <v>771500</v>
+        <v>880800</v>
       </c>
       <c r="J54" s="3">
+        <v>792900</v>
+      </c>
+      <c r="K54" s="3">
         <v>709200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>683300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>651500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>582000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>479500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>456400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>456000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>440400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>448000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>439300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>378300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>305800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>275800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>265000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>246400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>195200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>178800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>203400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>134500</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4767,8 +4892,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4802,8 +4930,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4837,89 +4966,90 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>104100</v>
+        <v>108000</v>
       </c>
       <c r="E57" s="3">
-        <v>113100</v>
+        <v>107000</v>
       </c>
       <c r="F57" s="3">
-        <v>114900</v>
+        <v>116200</v>
       </c>
       <c r="G57" s="3">
-        <v>119700</v>
+        <v>118100</v>
       </c>
       <c r="H57" s="3">
-        <v>126800</v>
+        <v>123000</v>
       </c>
       <c r="I57" s="3">
-        <v>121900</v>
+        <v>130400</v>
       </c>
       <c r="J57" s="3">
+        <v>125300</v>
+      </c>
+      <c r="K57" s="3">
         <v>110200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>119200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>109000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>97400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>76600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>73900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>78200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>71500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>84200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>98900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>65600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>62500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>58600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>55300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>53900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>52000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>42500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>37200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>32700</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4932,89 +5062,92 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>18200</v>
+        <v>17600</v>
       </c>
       <c r="E58" s="3">
-        <v>18100</v>
+        <v>18700</v>
       </c>
       <c r="F58" s="3">
-        <v>17200</v>
+        <v>18600</v>
       </c>
       <c r="G58" s="3">
-        <v>17100</v>
+        <v>17700</v>
       </c>
       <c r="H58" s="3">
-        <v>16100</v>
+        <v>17600</v>
       </c>
       <c r="I58" s="3">
-        <v>14800</v>
+        <v>16500</v>
       </c>
       <c r="J58" s="3">
+        <v>15200</v>
+      </c>
+      <c r="K58" s="3">
         <v>14600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>16500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>16800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>14300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>14200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>13600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>14300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>15600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>11700</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
       <c r="W58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X58" s="3">
         <v>100</v>
       </c>
       <c r="Y58" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z58" s="3">
         <v>25500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>30500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>50800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>26800</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5027,89 +5160,92 @@
       <c r="AG58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>20200</v>
+        <v>16500</v>
       </c>
       <c r="E59" s="3">
-        <v>18400</v>
+        <v>20800</v>
       </c>
       <c r="F59" s="3">
-        <v>19400</v>
+        <v>18900</v>
       </c>
       <c r="G59" s="3">
-        <v>25400</v>
+        <v>19900</v>
       </c>
       <c r="H59" s="3">
-        <v>31800</v>
+        <v>26100</v>
       </c>
       <c r="I59" s="3">
-        <v>22700</v>
+        <v>32700</v>
       </c>
       <c r="J59" s="3">
+        <v>23300</v>
+      </c>
+      <c r="K59" s="3">
         <v>19000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>23400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>10900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>23300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>500</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5122,89 +5258,92 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>142600</v>
+        <v>142000</v>
       </c>
       <c r="E60" s="3">
-        <v>149600</v>
+        <v>146600</v>
       </c>
       <c r="F60" s="3">
-        <v>151500</v>
+        <v>153800</v>
       </c>
       <c r="G60" s="3">
-        <v>162200</v>
+        <v>155700</v>
       </c>
       <c r="H60" s="3">
-        <v>174700</v>
+        <v>166700</v>
       </c>
       <c r="I60" s="3">
-        <v>159300</v>
+        <v>179500</v>
       </c>
       <c r="J60" s="3">
+        <v>163700</v>
+      </c>
+      <c r="K60" s="3">
         <v>143900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>150900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>148800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>127500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>99400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>94900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>100800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>93300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>108200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>119700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>85800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>74400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>65300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>64900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>61500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>92000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>83900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>111300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>60000</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5217,65 +5356,68 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>67300</v>
+        <v>58200</v>
       </c>
       <c r="E61" s="3">
-        <v>67500</v>
+        <v>69200</v>
       </c>
       <c r="F61" s="3">
-        <v>62300</v>
+        <v>69400</v>
       </c>
       <c r="G61" s="3">
-        <v>66900</v>
+        <v>64000</v>
       </c>
       <c r="H61" s="3">
-        <v>63700</v>
+        <v>68800</v>
       </c>
       <c r="I61" s="3">
+        <v>65400</v>
+      </c>
+      <c r="J61" s="3">
+        <v>56100</v>
+      </c>
+      <c r="K61" s="3">
         <v>54600</v>
       </c>
-      <c r="J61" s="3">
-        <v>54600</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>56600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>60300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>62200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>40500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>45800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>48000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>51500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>53800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>53900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>40400</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -5292,13 +5434,13 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB61" s="3">
         <v>100</v>
       </c>
       <c r="AC61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD61" s="3">
         <v>0</v>
@@ -5312,89 +5454,92 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>36900</v>
+        <v>22400</v>
       </c>
       <c r="E62" s="3">
-        <v>29500</v>
+        <v>38000</v>
       </c>
       <c r="F62" s="3">
-        <v>14900</v>
+        <v>30300</v>
       </c>
       <c r="G62" s="3">
-        <v>16100</v>
+        <v>15400</v>
       </c>
       <c r="H62" s="3">
-        <v>17400</v>
+        <v>16500</v>
       </c>
       <c r="I62" s="3">
-        <v>20700</v>
+        <v>17900</v>
       </c>
       <c r="J62" s="3">
+        <v>21300</v>
+      </c>
+      <c r="K62" s="3">
         <v>20600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>17100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>13400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>14100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>14500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3800</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5407,8 +5552,11 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5502,8 +5650,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5597,8 +5748,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5692,89 +5846,92 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>246900</v>
+        <v>222600</v>
       </c>
       <c r="E66" s="3">
-        <v>246600</v>
+        <v>253700</v>
       </c>
       <c r="F66" s="3">
-        <v>228700</v>
+        <v>253500</v>
       </c>
       <c r="G66" s="3">
-        <v>245200</v>
+        <v>235100</v>
       </c>
       <c r="H66" s="3">
-        <v>255800</v>
+        <v>252000</v>
       </c>
       <c r="I66" s="3">
-        <v>234600</v>
+        <v>262900</v>
       </c>
       <c r="J66" s="3">
+        <v>241200</v>
+      </c>
+      <c r="K66" s="3">
         <v>219100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>222500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>227300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>214200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>157000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>153200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>161700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>152200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>171300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>180200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>129000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>77400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>68500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>68700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>65600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>105400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>98000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>125900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>63800</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5787,8 +5944,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5822,8 +5982,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5917,8 +6078,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6012,8 +6176,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6107,8 +6274,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6202,89 +6372,92 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>723900</v>
+        <v>766400</v>
       </c>
       <c r="E72" s="3">
-        <v>689200</v>
+        <v>744000</v>
       </c>
       <c r="F72" s="3">
-        <v>649100</v>
+        <v>708400</v>
       </c>
       <c r="G72" s="3">
-        <v>605500</v>
+        <v>667100</v>
       </c>
       <c r="H72" s="3">
-        <v>588600</v>
+        <v>622300</v>
       </c>
       <c r="I72" s="3">
-        <v>524300</v>
+        <v>604900</v>
       </c>
       <c r="J72" s="3">
+        <v>538800</v>
+      </c>
+      <c r="K72" s="3">
         <v>479400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>453800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>422600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>366300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>321100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>301800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>293700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>288300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>248800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>232200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>226700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>205700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>186900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>133700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>118200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>88000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>79000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>75700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>68800</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6297,8 +6470,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6392,8 +6568,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6487,8 +6666,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6582,89 +6764,92 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>743400</v>
+        <v>790500</v>
       </c>
       <c r="E76" s="3">
-        <v>708800</v>
+        <v>764100</v>
       </c>
       <c r="F76" s="3">
-        <v>667100</v>
+        <v>728500</v>
       </c>
       <c r="G76" s="3">
-        <v>633300</v>
+        <v>685700</v>
       </c>
       <c r="H76" s="3">
-        <v>601200</v>
+        <v>650900</v>
       </c>
       <c r="I76" s="3">
-        <v>536800</v>
+        <v>617900</v>
       </c>
       <c r="J76" s="3">
+        <v>551800</v>
+      </c>
+      <c r="K76" s="3">
         <v>490000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>460800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>424100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>367800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>322500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>303200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>294200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>288300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>276700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>259100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>249300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>228400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>207200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>196300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>180800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>89800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>80800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>77500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>70700</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6677,8 +6862,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6772,97 +6960,100 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6872,92 +7063,95 @@
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>15300</v>
+        <v>10600</v>
       </c>
       <c r="E81" s="3">
-        <v>28600</v>
+        <v>15800</v>
       </c>
       <c r="F81" s="3">
-        <v>30200</v>
+        <v>29400</v>
       </c>
       <c r="G81" s="3">
-        <v>18600</v>
+        <v>31100</v>
       </c>
       <c r="H81" s="3">
-        <v>39400</v>
+        <v>19200</v>
       </c>
       <c r="I81" s="3">
-        <v>33500</v>
+        <v>40500</v>
       </c>
       <c r="J81" s="3">
+        <v>34500</v>
+      </c>
+      <c r="K81" s="3">
         <v>24900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>26000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>15200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-18800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>19800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>11300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>8400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>9800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>18200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5600</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6967,8 +7161,11 @@
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7002,8 +7199,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7064,30 +7262,30 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3">
         <v>2300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>5800</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD83" s="3">
         <v>1700</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7097,8 +7295,11 @@
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7192,8 +7393,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7287,8 +7491,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7382,8 +7589,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7477,8 +7687,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7572,92 +7785,95 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>20600</v>
+        <v>44700</v>
       </c>
       <c r="E89" s="3">
-        <v>41300</v>
+        <v>21200</v>
       </c>
       <c r="F89" s="3">
-        <v>31100</v>
+        <v>42500</v>
       </c>
       <c r="G89" s="3">
-        <v>50700</v>
+        <v>32000</v>
       </c>
       <c r="H89" s="3">
-        <v>31300</v>
+        <v>52100</v>
       </c>
       <c r="I89" s="3">
-        <v>58400</v>
+        <v>32200</v>
       </c>
       <c r="J89" s="3">
+        <v>60100</v>
+      </c>
+      <c r="K89" s="3">
         <v>23200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>44300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>25200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>43300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>13500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>23900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>25400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>15800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>15100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>21000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>15200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>16800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>12700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>17600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>26300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>11200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>5000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>14300</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7667,8 +7883,11 @@
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7702,92 +7921,93 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>4300</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7797,8 +8017,11 @@
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7892,8 +8115,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7987,92 +8213,95 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-12500</v>
+        <v>-2500</v>
       </c>
       <c r="E94" s="3">
-        <v>-81000</v>
+        <v>-12900</v>
       </c>
       <c r="F94" s="3">
-        <v>-7900</v>
+        <v>-83200</v>
       </c>
       <c r="G94" s="3">
-        <v>-44800</v>
+        <v>-8200</v>
       </c>
       <c r="H94" s="3">
-        <v>-3800</v>
+        <v>-46100</v>
       </c>
       <c r="I94" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="K94" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="L94" s="3">
         <v>-4800</v>
       </c>
-      <c r="J94" s="3">
-        <v>-15100</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-49200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-58800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-34300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-37600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
@@ -8082,8 +8311,11 @@
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8117,8 +8349,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8212,8 +8445,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8307,8 +8543,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8402,8 +8641,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8497,92 +8739,95 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-4900</v>
+        <v>-800</v>
       </c>
       <c r="E100" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-3400</v>
       </c>
-      <c r="F100" s="3">
-        <v>-5100</v>
-      </c>
       <c r="G100" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="H100" s="3">
         <v>-1300</v>
       </c>
-      <c r="H100" s="3">
-        <v>-3900</v>
-      </c>
       <c r="I100" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="O100" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="P100" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="R100" s="3">
+        <v>16700</v>
+      </c>
+      <c r="S100" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="T100" s="3">
+        <v>16900</v>
+      </c>
+      <c r="U100" s="3">
         <v>-2200</v>
       </c>
-      <c r="J100" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K100" s="3">
-        <v>1200</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>16700</v>
-      </c>
-      <c r="R100" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="S100" s="3">
-        <v>16900</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>2100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>32700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>23800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-11900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>3300</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8592,91 +8837,94 @@
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E101" s="3">
         <v>1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
-        <v>-800</v>
-      </c>
       <c r="G101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1200</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-4100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>200</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-100</v>
       </c>
       <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>3</v>
+      <c r="AD101" s="3">
+        <v>-100</v>
       </c>
       <c r="AE101" s="3" t="s">
         <v>3</v>
@@ -8687,92 +8935,95 @@
       <c r="AG101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>4300</v>
+        <v>38800</v>
       </c>
       <c r="E102" s="3">
-        <v>-42800</v>
+        <v>4400</v>
       </c>
       <c r="F102" s="3">
-        <v>17200</v>
+        <v>-44000</v>
       </c>
       <c r="G102" s="3">
-        <v>3600</v>
+        <v>17700</v>
       </c>
       <c r="H102" s="3">
-        <v>24300</v>
+        <v>3700</v>
       </c>
       <c r="I102" s="3">
-        <v>52600</v>
+        <v>25000</v>
       </c>
       <c r="J102" s="3">
+        <v>54100</v>
+      </c>
+      <c r="K102" s="3">
         <v>7700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>40700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>16600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>17300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>10900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>18400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>14900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>11000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>12300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>35300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>7200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-18200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>11000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>12500</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8780,6 +9031,9 @@
         <v>3</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
   <si>
     <t>DAVA</t>
   </si>
@@ -656,134 +656,135 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
@@ -793,95 +794,98 @@
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>234100</v>
+        <v>223200</v>
       </c>
       <c r="E8" s="3">
-        <v>240200</v>
+        <v>234900</v>
       </c>
       <c r="F8" s="3">
-        <v>242000</v>
+        <v>241100</v>
       </c>
       <c r="G8" s="3">
-        <v>259500</v>
+        <v>242900</v>
       </c>
       <c r="H8" s="3">
-        <v>261700</v>
+        <v>260400</v>
       </c>
       <c r="I8" s="3">
-        <v>250200</v>
+        <v>262600</v>
       </c>
       <c r="J8" s="3">
+        <v>251100</v>
+      </c>
+      <c r="K8" s="3">
         <v>230000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>209900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>199900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>186900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>165800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>131500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>123200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>112500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>110400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>122700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>117100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>112400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>105200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>97300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>94800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>87700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>79500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>201800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>65200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>62000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>56100</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
@@ -891,95 +895,98 @@
       <c r="AH8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>176800</v>
+        <v>175500</v>
       </c>
       <c r="E9" s="3">
-        <v>170800</v>
+        <v>177500</v>
       </c>
       <c r="F9" s="3">
-        <v>166100</v>
+        <v>171400</v>
       </c>
       <c r="G9" s="3">
-        <v>177100</v>
+        <v>166700</v>
       </c>
       <c r="H9" s="3">
-        <v>169300</v>
+        <v>177700</v>
       </c>
       <c r="I9" s="3">
-        <v>164200</v>
+        <v>169900</v>
       </c>
       <c r="J9" s="3">
+        <v>164800</v>
+      </c>
+      <c r="K9" s="3">
         <v>156400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>141200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>133800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>120100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>109100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>86400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>79900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>73600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>77400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>75200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>106700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>71900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>69600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>64000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>61300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>58000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>51800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>136200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>44400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>42200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>38000</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
@@ -989,95 +996,98 @@
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>57300</v>
+        <v>47600</v>
       </c>
       <c r="E10" s="3">
-        <v>69400</v>
+        <v>57500</v>
       </c>
       <c r="F10" s="3">
-        <v>75900</v>
+        <v>69700</v>
       </c>
       <c r="G10" s="3">
-        <v>82400</v>
+        <v>76200</v>
       </c>
       <c r="H10" s="3">
-        <v>92400</v>
+        <v>82700</v>
       </c>
       <c r="I10" s="3">
-        <v>86000</v>
+        <v>92700</v>
       </c>
       <c r="J10" s="3">
+        <v>86300</v>
+      </c>
+      <c r="K10" s="3">
         <v>73600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>68700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>66000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>66800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>56700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>45100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>43400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>38900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>33000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>47500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>40500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>35600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>33300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>33500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>29700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>27700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>65600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>20900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>19700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>18100</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1087,8 +1097,11 @@
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,8 +1136,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1221,8 +1235,11 @@
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1319,8 +1336,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1330,33 +1350,33 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-4300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1400</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1500</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1376,11 +1396,11 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-3000</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1390,24 +1410,24 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>1600</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE14" s="3">
         <v>500</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1417,74 +1437,77 @@
       <c r="AH14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E15" s="3">
         <v>5700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5400</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="G15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3">
         <v>5000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4600</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" s="3">
         <v>4200</v>
-      </c>
-      <c r="L15" s="3">
-        <v>3900</v>
       </c>
       <c r="M15" s="3">
         <v>3900</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="3">
+      <c r="N15" s="3">
+        <v>3900</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3">
         <v>1800</v>
-      </c>
-      <c r="P15" s="3">
-        <v>2100</v>
       </c>
       <c r="Q15" s="3">
         <v>2100</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="R15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T15" s="3">
         <v>2200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1900</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X15" s="3">
         <v>1300</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1494,8 +1517,8 @@
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
@@ -1515,8 +1538,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1548,95 +1574,96 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>228200</v>
+        <v>225500</v>
       </c>
       <c r="E17" s="3">
-        <v>219700</v>
+        <v>229000</v>
       </c>
       <c r="F17" s="3">
-        <v>213000</v>
+        <v>220500</v>
       </c>
       <c r="G17" s="3">
-        <v>221100</v>
+        <v>213800</v>
       </c>
       <c r="H17" s="3">
-        <v>219900</v>
+        <v>221900</v>
       </c>
       <c r="I17" s="3">
-        <v>215400</v>
+        <v>220700</v>
       </c>
       <c r="J17" s="3">
+        <v>216200</v>
+      </c>
+      <c r="K17" s="3">
         <v>196100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>178400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>175200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>156600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>141200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>110400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>106800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>98700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>102000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>104000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>132800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>92500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>93300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>87400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>82900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>77400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>71200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>177300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>57200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>52900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>47800</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,95 +1673,98 @@
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>5900</v>
+        <v>-2300</v>
       </c>
       <c r="E18" s="3">
-        <v>20500</v>
+        <v>6000</v>
       </c>
       <c r="F18" s="3">
-        <v>29000</v>
+        <v>20600</v>
       </c>
       <c r="G18" s="3">
-        <v>38300</v>
+        <v>29100</v>
       </c>
       <c r="H18" s="3">
-        <v>41800</v>
+        <v>38500</v>
       </c>
       <c r="I18" s="3">
-        <v>34800</v>
+        <v>41900</v>
       </c>
       <c r="J18" s="3">
+        <v>34900</v>
+      </c>
+      <c r="K18" s="3">
         <v>34000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>31500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>30300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>24500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>21100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>18800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-15600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>19900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>11900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>12000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>10300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>24500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>8000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>9000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>8200</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1744,8 +1774,11 @@
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1780,95 +1813,96 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E20" s="3">
         <v>7600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
-        <v>-15900</v>
-      </c>
       <c r="I20" s="3">
-        <v>14400</v>
+        <v>-16000</v>
       </c>
       <c r="J20" s="3">
+        <v>14500</v>
+      </c>
+      <c r="K20" s="3">
         <v>7500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-7900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1878,95 +1912,98 @@
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>13400</v>
+        <v>-1700</v>
       </c>
       <c r="E21" s="3">
-        <v>34100</v>
+        <v>13500</v>
       </c>
       <c r="F21" s="3">
-        <v>31600</v>
+        <v>34200</v>
       </c>
       <c r="G21" s="3">
-        <v>39000</v>
+        <v>31700</v>
       </c>
       <c r="H21" s="3">
-        <v>26700</v>
+        <v>39100</v>
       </c>
       <c r="I21" s="3">
-        <v>59000</v>
+        <v>26800</v>
       </c>
       <c r="J21" s="3">
+        <v>59200</v>
+      </c>
+      <c r="K21" s="3">
         <v>40800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>32500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>24500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>40400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>24500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>18100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>16600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>24700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-22900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>29500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>14400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>11600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>12400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>11000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>29000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>8900</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1976,8 +2013,11 @@
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2074,95 +2114,98 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>13500</v>
+        <v>-700</v>
       </c>
       <c r="E23" s="3">
-        <v>22100</v>
+        <v>13600</v>
       </c>
       <c r="F23" s="3">
-        <v>31800</v>
+        <v>22200</v>
       </c>
       <c r="G23" s="3">
-        <v>38700</v>
+        <v>31900</v>
       </c>
       <c r="H23" s="3">
-        <v>25800</v>
+        <v>38900</v>
       </c>
       <c r="I23" s="3">
-        <v>49200</v>
+        <v>25900</v>
       </c>
       <c r="J23" s="3">
+        <v>49400</v>
+      </c>
+      <c r="K23" s="3">
         <v>41400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>32100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>24200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>31600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>23000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>19300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>12400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>24400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-23500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>23800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>14300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>10100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>12400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>23200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>7900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>7200</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2172,95 +2215,98 @@
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E24" s="3">
         <v>2900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6700</v>
       </c>
-      <c r="I24" s="3">
-        <v>8700</v>
-      </c>
       <c r="J24" s="3">
+        <v>8800</v>
+      </c>
+      <c r="K24" s="3">
         <v>7000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-4700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1600</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2270,8 +2316,11 @@
       <c r="AH24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2368,95 +2417,98 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>10600</v>
+        <v>-2200</v>
       </c>
       <c r="E26" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F26" s="3">
         <v>15800</v>
       </c>
-      <c r="F26" s="3">
-        <v>29400</v>
-      </c>
       <c r="G26" s="3">
-        <v>31100</v>
+        <v>29500</v>
       </c>
       <c r="H26" s="3">
+        <v>31200</v>
+      </c>
+      <c r="I26" s="3">
         <v>19200</v>
       </c>
-      <c r="I26" s="3">
-        <v>40500</v>
-      </c>
       <c r="J26" s="3">
+        <v>40600</v>
+      </c>
+      <c r="K26" s="3">
         <v>34500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>24900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>26000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>15200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>19400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-18800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>19800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>11300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>8400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>9800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>18200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5600</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2466,95 +2518,98 @@
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>10600</v>
+        <v>-2200</v>
       </c>
       <c r="E27" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F27" s="3">
         <v>15800</v>
       </c>
-      <c r="F27" s="3">
-        <v>29400</v>
-      </c>
       <c r="G27" s="3">
-        <v>31100</v>
+        <v>29500</v>
       </c>
       <c r="H27" s="3">
+        <v>31200</v>
+      </c>
+      <c r="I27" s="3">
         <v>19200</v>
       </c>
-      <c r="I27" s="3">
-        <v>40500</v>
-      </c>
       <c r="J27" s="3">
+        <v>40600</v>
+      </c>
+      <c r="K27" s="3">
         <v>34500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>24900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>26000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>15200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>9100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>19400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-18800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>19800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>11300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>8400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>9800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>18200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>6600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5600</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2564,8 +2619,11 @@
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2662,8 +2720,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2760,8 +2821,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2858,8 +2922,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2956,95 +3023,98 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
-        <v>15900</v>
-      </c>
       <c r="I32" s="3">
-        <v>-14400</v>
+        <v>16000</v>
       </c>
       <c r="J32" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-7500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>7900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1000</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
@@ -3054,95 +3124,98 @@
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>10600</v>
+        <v>-2200</v>
       </c>
       <c r="E33" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F33" s="3">
         <v>15800</v>
       </c>
-      <c r="F33" s="3">
-        <v>29400</v>
-      </c>
       <c r="G33" s="3">
-        <v>31100</v>
+        <v>29500</v>
       </c>
       <c r="H33" s="3">
+        <v>31200</v>
+      </c>
+      <c r="I33" s="3">
         <v>19200</v>
       </c>
-      <c r="I33" s="3">
-        <v>40500</v>
-      </c>
       <c r="J33" s="3">
+        <v>40600</v>
+      </c>
+      <c r="K33" s="3">
         <v>34500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>24900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>26000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>15200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>9100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>19400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-18800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>19800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>11300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>8400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>9800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>18200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5600</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3152,8 +3225,11 @@
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3250,95 +3326,98 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>10600</v>
+        <v>-2200</v>
       </c>
       <c r="E35" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F35" s="3">
         <v>15800</v>
       </c>
-      <c r="F35" s="3">
-        <v>29400</v>
-      </c>
       <c r="G35" s="3">
-        <v>31100</v>
+        <v>29500</v>
       </c>
       <c r="H35" s="3">
+        <v>31200</v>
+      </c>
+      <c r="I35" s="3">
         <v>19200</v>
       </c>
-      <c r="I35" s="3">
-        <v>40500</v>
-      </c>
       <c r="J35" s="3">
+        <v>40600</v>
+      </c>
+      <c r="K35" s="3">
         <v>34500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>24900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>26000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>15200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>9100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>19400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-18800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>19800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>11300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>8400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>9800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>18200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5600</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3348,100 +3427,103 @@
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3451,8 +3533,11 @@
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3487,8 +3572,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3523,92 +3609,93 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>253200</v>
+        <v>243200</v>
       </c>
       <c r="E41" s="3">
-        <v>214500</v>
+        <v>254100</v>
       </c>
       <c r="F41" s="3">
-        <v>210000</v>
+        <v>215200</v>
       </c>
       <c r="G41" s="3">
-        <v>254000</v>
+        <v>210800</v>
       </c>
       <c r="H41" s="3">
-        <v>236300</v>
+        <v>254900</v>
       </c>
       <c r="I41" s="3">
-        <v>232600</v>
+        <v>237100</v>
       </c>
       <c r="J41" s="3">
+        <v>233400</v>
+      </c>
+      <c r="K41" s="3">
         <v>207600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>149400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>144700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>104000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>86700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>92300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>98600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>82800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>123600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>116000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>107700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>114100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>96400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>79000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>67400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>55200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>19500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>12200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>32700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>21700</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,8 +3708,11 @@
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3630,31 +3720,31 @@
         <v>200</v>
       </c>
       <c r="E42" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F42" s="3">
         <v>100</v>
       </c>
       <c r="G42" s="3">
+        <v>100</v>
+      </c>
+      <c r="H42" s="3">
         <v>200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>600</v>
-      </c>
-      <c r="M42" s="3">
-        <v>700</v>
       </c>
       <c r="N42" s="3">
         <v>700</v>
@@ -3672,7 +3762,7 @@
         <v>700</v>
       </c>
       <c r="S42" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="T42" s="3">
         <v>800</v>
@@ -3680,8 +3770,8 @@
       <c r="U42" s="3">
         <v>800</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
+      <c r="V42" s="3">
+        <v>800</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
@@ -3698,8 +3788,8 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
@@ -3719,92 +3809,95 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>220100</v>
+        <v>228600</v>
       </c>
       <c r="E43" s="3">
-        <v>243900</v>
+        <v>220900</v>
       </c>
       <c r="F43" s="3">
-        <v>232000</v>
+        <v>244800</v>
       </c>
       <c r="G43" s="3">
-        <v>234900</v>
+        <v>232800</v>
       </c>
       <c r="H43" s="3">
-        <v>224500</v>
+        <v>235700</v>
       </c>
       <c r="I43" s="3">
-        <v>247000</v>
+        <v>225300</v>
       </c>
       <c r="J43" s="3">
+        <v>247900</v>
+      </c>
+      <c r="K43" s="3">
         <v>210400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>199500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>183800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>180400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>148000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>129500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>110300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>112800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>104300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>108700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>107000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>93700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>91600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>84800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>84900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>80800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>68600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>64900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>64400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>59300</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3817,8 +3910,11 @@
       <c r="AH43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3892,17 +3988,17 @@
         <v>0</v>
       </c>
       <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="3">
         <v>100</v>
       </c>
-      <c r="AB44" s="3">
-        <v>0</v>
-      </c>
       <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="3">
         <v>100</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3915,8 +4011,11 @@
       <c r="AH44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4013,92 +4112,95 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>473600</v>
+        <v>472000</v>
       </c>
       <c r="E46" s="3">
-        <v>458500</v>
+        <v>475300</v>
       </c>
       <c r="F46" s="3">
-        <v>442000</v>
+        <v>460100</v>
       </c>
       <c r="G46" s="3">
-        <v>489100</v>
+        <v>443600</v>
       </c>
       <c r="H46" s="3">
-        <v>461100</v>
+        <v>490800</v>
       </c>
       <c r="I46" s="3">
-        <v>480000</v>
+        <v>462800</v>
       </c>
       <c r="J46" s="3">
+        <v>481700</v>
+      </c>
+      <c r="K46" s="3">
         <v>418500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>349300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>329100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>285100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>235400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>222500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>209600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>196300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>228700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>225500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>215500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>208600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>188000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>163800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>152400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>136000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>88000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>77200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>97100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>81100</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4111,68 +4213,71 @@
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8100</v>
+        <v>9400</v>
       </c>
       <c r="E47" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F47" s="3">
         <v>4100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2900</v>
-      </c>
-      <c r="K47" s="3">
-        <v>200</v>
       </c>
       <c r="L47" s="3">
         <v>200</v>
       </c>
       <c r="M47" s="3">
+        <v>200</v>
+      </c>
+      <c r="N47" s="3">
         <v>300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1500</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4182,14 +4287,14 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>3</v>
+      <c r="AB47" s="3">
+        <v>0</v>
       </c>
       <c r="AC47" s="3" t="s">
         <v>3</v>
@@ -4209,92 +4314,95 @@
       <c r="AH47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>99600</v>
+        <v>95800</v>
       </c>
       <c r="E48" s="3">
-        <v>114300</v>
+        <v>100000</v>
       </c>
       <c r="F48" s="3">
-        <v>116100</v>
+        <v>114700</v>
       </c>
       <c r="G48" s="3">
-        <v>108600</v>
+        <v>116500</v>
       </c>
       <c r="H48" s="3">
-        <v>110700</v>
+        <v>109000</v>
       </c>
       <c r="I48" s="3">
-        <v>105800</v>
+        <v>111100</v>
       </c>
       <c r="J48" s="3">
+        <v>106100</v>
+      </c>
+      <c r="K48" s="3">
         <v>91900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>86200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>87400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>89500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>87500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>62700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>68900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>72400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>77900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>81500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>83000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>65700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10400</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4307,92 +4415,95 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>404600</v>
+        <v>411400</v>
       </c>
       <c r="E49" s="3">
-        <v>414800</v>
+        <v>406000</v>
       </c>
       <c r="F49" s="3">
-        <v>391500</v>
+        <v>416200</v>
       </c>
       <c r="G49" s="3">
-        <v>303300</v>
+        <v>392900</v>
       </c>
       <c r="H49" s="3">
-        <v>312100</v>
+        <v>304400</v>
       </c>
       <c r="I49" s="3">
-        <v>266400</v>
+        <v>313200</v>
       </c>
       <c r="J49" s="3">
+        <v>267400</v>
+      </c>
+      <c r="K49" s="3">
         <v>257700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>251200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>239500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>246300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>233800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>178500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>161300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>167700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>116800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>127400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>124000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>89100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>90200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>93200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>96100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>94900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>92900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>89600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>93700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>41900</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4405,8 +4516,11 @@
       <c r="AH49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4503,8 +4617,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4601,92 +4718,95 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>27200</v>
+        <v>25500</v>
       </c>
       <c r="E52" s="3">
-        <v>26300</v>
+        <v>27300</v>
       </c>
       <c r="F52" s="3">
-        <v>25700</v>
+        <v>26400</v>
       </c>
       <c r="G52" s="3">
-        <v>17200</v>
+        <v>25800</v>
       </c>
       <c r="H52" s="3">
-        <v>17200</v>
+        <v>17300</v>
       </c>
       <c r="I52" s="3">
-        <v>25000</v>
+        <v>17300</v>
       </c>
       <c r="J52" s="3">
+        <v>25100</v>
+      </c>
+      <c r="K52" s="3">
         <v>22000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>27100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>30300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>24900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>18700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>12400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>15600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>13400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>13100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6300</v>
-      </c>
-      <c r="X52" s="3">
-        <v>3300</v>
       </c>
       <c r="Y52" s="3">
         <v>3300</v>
       </c>
       <c r="Z52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AA52" s="3">
         <v>3200</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>1200</v>
       </c>
       <c r="AB52" s="3">
         <v>1200</v>
       </c>
       <c r="AC52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AD52" s="3">
         <v>1100</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4699,8 +4819,11 @@
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4797,92 +4920,95 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1013200</v>
+        <v>1014000</v>
       </c>
       <c r="E54" s="3">
-        <v>1017800</v>
+        <v>1016700</v>
       </c>
       <c r="F54" s="3">
-        <v>982000</v>
+        <v>1021400</v>
       </c>
       <c r="G54" s="3">
-        <v>920800</v>
+        <v>985500</v>
       </c>
       <c r="H54" s="3">
-        <v>902900</v>
+        <v>924000</v>
       </c>
       <c r="I54" s="3">
-        <v>880800</v>
+        <v>906100</v>
       </c>
       <c r="J54" s="3">
+        <v>883900</v>
+      </c>
+      <c r="K54" s="3">
         <v>792900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>709200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>683300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>651500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>582000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>479500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>456400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>456000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>440400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>448000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>439300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>378300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>305800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>275800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>265000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>246400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>195200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>178800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>203400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>134500</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4895,8 +5021,11 @@
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4931,8 +5060,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4967,92 +5097,93 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>108000</v>
+        <v>105300</v>
       </c>
       <c r="E57" s="3">
-        <v>107000</v>
+        <v>108400</v>
       </c>
       <c r="F57" s="3">
-        <v>116200</v>
+        <v>107400</v>
       </c>
       <c r="G57" s="3">
-        <v>118100</v>
+        <v>116600</v>
       </c>
       <c r="H57" s="3">
-        <v>123000</v>
+        <v>118600</v>
       </c>
       <c r="I57" s="3">
-        <v>130400</v>
+        <v>123500</v>
       </c>
       <c r="J57" s="3">
+        <v>130800</v>
+      </c>
+      <c r="K57" s="3">
         <v>125300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>110200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>119200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>109000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>97400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>76600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>73900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>78200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>71500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>84200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>98900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>65600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>62500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>58600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>55300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>53900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>52000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>42500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>37200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>32700</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5065,92 +5196,95 @@
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E58" s="3">
         <v>17600</v>
       </c>
-      <c r="E58" s="3">
-        <v>18700</v>
-      </c>
       <c r="F58" s="3">
+        <v>18800</v>
+      </c>
+      <c r="G58" s="3">
         <v>18600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>17700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
+        <v>16600</v>
+      </c>
+      <c r="K58" s="3">
+        <v>15200</v>
+      </c>
+      <c r="L58" s="3">
+        <v>14600</v>
+      </c>
+      <c r="M58" s="3">
+        <v>15200</v>
+      </c>
+      <c r="N58" s="3">
         <v>16500</v>
       </c>
-      <c r="J58" s="3">
-        <v>15200</v>
-      </c>
-      <c r="K58" s="3">
-        <v>14600</v>
-      </c>
-      <c r="L58" s="3">
-        <v>15200</v>
-      </c>
-      <c r="M58" s="3">
-        <v>16500</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>16800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>14300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>14200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>13100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>13600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>14300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>15600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>11700</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
       <c r="X58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y58" s="3">
         <v>100</v>
       </c>
       <c r="Z58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA58" s="3">
         <v>25500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>30500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>50800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>26800</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5163,92 +5297,95 @@
       <c r="AH58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>16500</v>
+        <v>13900</v>
       </c>
       <c r="E59" s="3">
-        <v>20800</v>
+        <v>16600</v>
       </c>
       <c r="F59" s="3">
-        <v>18900</v>
+        <v>20900</v>
       </c>
       <c r="G59" s="3">
-        <v>19900</v>
+        <v>19000</v>
       </c>
       <c r="H59" s="3">
-        <v>26100</v>
+        <v>20000</v>
       </c>
       <c r="I59" s="3">
-        <v>32700</v>
+        <v>26200</v>
       </c>
       <c r="J59" s="3">
+        <v>32800</v>
+      </c>
+      <c r="K59" s="3">
         <v>23300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>19000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>23400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>23300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>500</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5261,92 +5398,95 @@
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>142000</v>
+        <v>137500</v>
       </c>
       <c r="E60" s="3">
-        <v>146600</v>
+        <v>142500</v>
       </c>
       <c r="F60" s="3">
-        <v>153800</v>
+        <v>147100</v>
       </c>
       <c r="G60" s="3">
-        <v>155700</v>
+        <v>154300</v>
       </c>
       <c r="H60" s="3">
-        <v>166700</v>
+        <v>156300</v>
       </c>
       <c r="I60" s="3">
-        <v>179500</v>
+        <v>167300</v>
       </c>
       <c r="J60" s="3">
+        <v>180200</v>
+      </c>
+      <c r="K60" s="3">
         <v>163700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>143900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>150900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>148800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>127500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>99400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>94900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>100800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>93300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>108200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>119700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>85800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>74400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>65300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>64900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>61500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>92000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>83900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>111300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>60000</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5359,68 +5499,71 @@
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>58200</v>
+        <v>55000</v>
       </c>
       <c r="E61" s="3">
-        <v>69200</v>
+        <v>58400</v>
       </c>
       <c r="F61" s="3">
         <v>69400</v>
       </c>
       <c r="G61" s="3">
-        <v>64000</v>
+        <v>69700</v>
       </c>
       <c r="H61" s="3">
-        <v>68800</v>
+        <v>64200</v>
       </c>
       <c r="I61" s="3">
-        <v>65400</v>
+        <v>69000</v>
       </c>
       <c r="J61" s="3">
+        <v>65700</v>
+      </c>
+      <c r="K61" s="3">
         <v>56100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>54600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>56600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>60300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>62200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>40500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>45800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>48000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>51500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>53800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>53900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>40400</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -5437,13 +5580,13 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC61" s="3">
         <v>100</v>
       </c>
       <c r="AD61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
@@ -5457,92 +5600,95 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>22400</v>
+        <v>22100</v>
       </c>
       <c r="E62" s="3">
-        <v>38000</v>
+        <v>22500</v>
       </c>
       <c r="F62" s="3">
-        <v>30300</v>
+        <v>38100</v>
       </c>
       <c r="G62" s="3">
+        <v>30400</v>
+      </c>
+      <c r="H62" s="3">
         <v>15400</v>
       </c>
-      <c r="H62" s="3">
-        <v>16500</v>
-      </c>
       <c r="I62" s="3">
-        <v>17900</v>
+        <v>16600</v>
       </c>
       <c r="J62" s="3">
+        <v>18000</v>
+      </c>
+      <c r="K62" s="3">
         <v>21300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>17100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>13400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>14100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>14500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3800</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5555,8 +5701,11 @@
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5653,8 +5802,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5751,8 +5903,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5849,92 +6004,95 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>222600</v>
+        <v>214500</v>
       </c>
       <c r="E66" s="3">
-        <v>253700</v>
+        <v>223400</v>
       </c>
       <c r="F66" s="3">
-        <v>253500</v>
+        <v>254600</v>
       </c>
       <c r="G66" s="3">
-        <v>235100</v>
+        <v>254400</v>
       </c>
       <c r="H66" s="3">
-        <v>252000</v>
+        <v>235900</v>
       </c>
       <c r="I66" s="3">
-        <v>262900</v>
+        <v>252900</v>
       </c>
       <c r="J66" s="3">
+        <v>263800</v>
+      </c>
+      <c r="K66" s="3">
         <v>241200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>219100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>222500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>227300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>214200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>157000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>153200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>161700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>152200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>171300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>180200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>129000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>77400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>68500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>68700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>65600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>105400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>98000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>125900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>63800</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5947,8 +6105,11 @@
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5983,8 +6144,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6081,8 +6243,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6179,8 +6344,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6277,8 +6445,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6375,92 +6546,95 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>766400</v>
+        <v>770900</v>
       </c>
       <c r="E72" s="3">
-        <v>744000</v>
+        <v>769200</v>
       </c>
       <c r="F72" s="3">
-        <v>708400</v>
+        <v>746600</v>
       </c>
       <c r="G72" s="3">
-        <v>667100</v>
+        <v>710900</v>
       </c>
       <c r="H72" s="3">
-        <v>622300</v>
+        <v>669500</v>
       </c>
       <c r="I72" s="3">
-        <v>604900</v>
+        <v>624600</v>
       </c>
       <c r="J72" s="3">
+        <v>607100</v>
+      </c>
+      <c r="K72" s="3">
         <v>538800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>479400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>453800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>422600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>366300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>321100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>301800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>293700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>288300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>248800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>232200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>226700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>205700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>186900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>133700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>118200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>88000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>79000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>75700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>68800</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6473,8 +6647,11 @@
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6571,8 +6748,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6669,8 +6849,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6767,92 +6950,95 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>790500</v>
+        <v>799500</v>
       </c>
       <c r="E76" s="3">
-        <v>764100</v>
+        <v>793300</v>
       </c>
       <c r="F76" s="3">
-        <v>728500</v>
+        <v>766800</v>
       </c>
       <c r="G76" s="3">
-        <v>685700</v>
+        <v>731100</v>
       </c>
       <c r="H76" s="3">
-        <v>650900</v>
+        <v>688100</v>
       </c>
       <c r="I76" s="3">
-        <v>617900</v>
+        <v>653200</v>
       </c>
       <c r="J76" s="3">
+        <v>620100</v>
+      </c>
+      <c r="K76" s="3">
         <v>551800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>490000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>460800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>424100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>367800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>322500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>303200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>294200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>288300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>276700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>259100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>249300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>228400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>207200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>196300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>180800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>89800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>80800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>77500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>70700</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6865,8 +7051,11 @@
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6963,100 +7152,103 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
@@ -7066,95 +7258,98 @@
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>10600</v>
+        <v>-2200</v>
       </c>
       <c r="E81" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F81" s="3">
         <v>15800</v>
       </c>
-      <c r="F81" s="3">
-        <v>29400</v>
-      </c>
       <c r="G81" s="3">
-        <v>31100</v>
+        <v>29500</v>
       </c>
       <c r="H81" s="3">
+        <v>31200</v>
+      </c>
+      <c r="I81" s="3">
         <v>19200</v>
       </c>
-      <c r="I81" s="3">
-        <v>40500</v>
-      </c>
       <c r="J81" s="3">
+        <v>40600</v>
+      </c>
+      <c r="K81" s="3">
         <v>34500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>24900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>26000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>15200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>9100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>19400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-18800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>19800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>11300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>8400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>9800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>18200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5600</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
@@ -7164,8 +7359,11 @@
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7200,8 +7398,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7265,30 +7464,30 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
+      <c r="X83" s="3">
+        <v>0</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA83" s="3">
         <v>2300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>5800</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE83" s="3">
         <v>1700</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7298,8 +7497,11 @@
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7396,8 +7598,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7494,8 +7699,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7592,8 +7800,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7690,8 +7901,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7788,95 +8002,98 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>44700</v>
+        <v>3800</v>
       </c>
       <c r="E89" s="3">
+        <v>44800</v>
+      </c>
+      <c r="F89" s="3">
         <v>21200</v>
       </c>
-      <c r="F89" s="3">
-        <v>42500</v>
-      </c>
       <c r="G89" s="3">
-        <v>32000</v>
+        <v>42600</v>
       </c>
       <c r="H89" s="3">
-        <v>52100</v>
+        <v>32100</v>
       </c>
       <c r="I89" s="3">
-        <v>32200</v>
+        <v>52300</v>
       </c>
       <c r="J89" s="3">
+        <v>32300</v>
+      </c>
+      <c r="K89" s="3">
         <v>60100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>23200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>44300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>25200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>43300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>13500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>23900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>25400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>15800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>15100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>21000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>15200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>16800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>12700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>17600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>26300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>11200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>5000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>14300</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7886,8 +8103,11 @@
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7922,95 +8142,96 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>4300</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
@@ -8020,8 +8241,11 @@
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8118,8 +8342,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8216,95 +8443,98 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2500</v>
+        <v>-15200</v>
       </c>
       <c r="E94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-12900</v>
       </c>
-      <c r="F94" s="3">
-        <v>-83200</v>
-      </c>
       <c r="G94" s="3">
+        <v>-83500</v>
+      </c>
+      <c r="H94" s="3">
         <v>-8200</v>
       </c>
-      <c r="H94" s="3">
-        <v>-46100</v>
-      </c>
       <c r="I94" s="3">
+        <v>-46200</v>
+      </c>
+      <c r="J94" s="3">
         <v>-3900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-49200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-58800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-34300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-37600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
@@ -8314,8 +8544,11 @@
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8350,8 +8583,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8448,8 +8682,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8546,8 +8783,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8644,8 +8884,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8742,95 +8985,98 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5000</v>
       </c>
-      <c r="F100" s="3">
-        <v>-3400</v>
-      </c>
       <c r="G100" s="3">
-        <v>-5200</v>
+        <v>-3500</v>
       </c>
       <c r="H100" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="I100" s="3">
         <v>-1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>16700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>16900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2200</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>2100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>32700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>23800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-11900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3300</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8840,94 +9086,97 @@
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1200</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>200</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>-100</v>
       </c>
       <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>3</v>
+      <c r="AE101" s="3">
+        <v>-100</v>
       </c>
       <c r="AF101" s="3" t="s">
         <v>3</v>
@@ -8938,95 +9187,98 @@
       <c r="AH101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>38800</v>
+        <v>-11000</v>
       </c>
       <c r="E102" s="3">
-        <v>4400</v>
+        <v>38900</v>
       </c>
       <c r="F102" s="3">
-        <v>-44000</v>
+        <v>4500</v>
       </c>
       <c r="G102" s="3">
-        <v>17700</v>
+        <v>-44100</v>
       </c>
       <c r="H102" s="3">
+        <v>17800</v>
+      </c>
+      <c r="I102" s="3">
         <v>3700</v>
       </c>
-      <c r="I102" s="3">
-        <v>25000</v>
-      </c>
       <c r="J102" s="3">
+        <v>25100</v>
+      </c>
+      <c r="K102" s="3">
         <v>54100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>40700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>16600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-37000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>17300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>10900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>18400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>14900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>11000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>12300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>35300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>7200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-18200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>11000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>12500</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
@@ -9034,6 +9286,9 @@
         <v>3</v>
       </c>
       <c r="AH102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
@@ -803,25 +803,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>223200</v>
+        <v>228800</v>
       </c>
       <c r="E8" s="3">
-        <v>234900</v>
+        <v>240900</v>
       </c>
       <c r="F8" s="3">
-        <v>241100</v>
+        <v>247200</v>
       </c>
       <c r="G8" s="3">
-        <v>242900</v>
+        <v>249100</v>
       </c>
       <c r="H8" s="3">
-        <v>260400</v>
+        <v>267000</v>
       </c>
       <c r="I8" s="3">
-        <v>262600</v>
+        <v>269300</v>
       </c>
       <c r="J8" s="3">
-        <v>251100</v>
+        <v>257500</v>
       </c>
       <c r="K8" s="3">
         <v>230000</v>
@@ -904,25 +904,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>175500</v>
+        <v>180000</v>
       </c>
       <c r="E9" s="3">
-        <v>177500</v>
+        <v>182000</v>
       </c>
       <c r="F9" s="3">
-        <v>171400</v>
+        <v>175800</v>
       </c>
       <c r="G9" s="3">
-        <v>166700</v>
+        <v>170900</v>
       </c>
       <c r="H9" s="3">
-        <v>177700</v>
+        <v>182300</v>
       </c>
       <c r="I9" s="3">
-        <v>169900</v>
+        <v>174200</v>
       </c>
       <c r="J9" s="3">
-        <v>164800</v>
+        <v>169000</v>
       </c>
       <c r="K9" s="3">
         <v>156400</v>
@@ -1005,25 +1005,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>47600</v>
+        <v>48900</v>
       </c>
       <c r="E10" s="3">
-        <v>57500</v>
+        <v>58900</v>
       </c>
       <c r="F10" s="3">
-        <v>69700</v>
+        <v>71400</v>
       </c>
       <c r="G10" s="3">
-        <v>76200</v>
+        <v>78100</v>
       </c>
       <c r="H10" s="3">
-        <v>82700</v>
+        <v>84800</v>
       </c>
       <c r="I10" s="3">
-        <v>92700</v>
+        <v>95100</v>
       </c>
       <c r="J10" s="3">
-        <v>86300</v>
+        <v>88500</v>
       </c>
       <c r="K10" s="3">
         <v>73600</v>
@@ -1357,10 +1357,10 @@
         <v>900</v>
       </c>
       <c r="H14" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="I14" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="J14" s="3">
         <v>1700</v>
@@ -1446,25 +1446,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F15" s="3">
+        <v>5500</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I15" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J15" s="3">
         <v>4700</v>
-      </c>
-      <c r="E15" s="3">
-        <v>5700</v>
-      </c>
-      <c r="F15" s="3">
-        <v>5400</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3">
-        <v>5000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J15" s="3">
-        <v>4600</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1581,25 +1581,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>225500</v>
+        <v>231200</v>
       </c>
       <c r="E17" s="3">
-        <v>229000</v>
+        <v>234800</v>
       </c>
       <c r="F17" s="3">
-        <v>220500</v>
+        <v>226100</v>
       </c>
       <c r="G17" s="3">
-        <v>213800</v>
+        <v>219200</v>
       </c>
       <c r="H17" s="3">
-        <v>221900</v>
+        <v>227600</v>
       </c>
       <c r="I17" s="3">
-        <v>220700</v>
+        <v>226300</v>
       </c>
       <c r="J17" s="3">
-        <v>216200</v>
+        <v>221700</v>
       </c>
       <c r="K17" s="3">
         <v>196100</v>
@@ -1682,25 +1682,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2300</v>
+        <v>-2400</v>
       </c>
       <c r="E18" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="F18" s="3">
-        <v>20600</v>
+        <v>21100</v>
       </c>
       <c r="G18" s="3">
-        <v>29100</v>
+        <v>29800</v>
       </c>
       <c r="H18" s="3">
-        <v>38500</v>
+        <v>39500</v>
       </c>
       <c r="I18" s="3">
-        <v>41900</v>
+        <v>43000</v>
       </c>
       <c r="J18" s="3">
-        <v>34900</v>
+        <v>35800</v>
       </c>
       <c r="K18" s="3">
         <v>34000</v>
@@ -1820,25 +1820,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E20" s="3">
-        <v>7600</v>
+        <v>7800</v>
       </c>
       <c r="F20" s="3">
         <v>1600</v>
       </c>
       <c r="G20" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="H20" s="3">
         <v>400</v>
       </c>
       <c r="I20" s="3">
-        <v>-16000</v>
+        <v>-16400</v>
       </c>
       <c r="J20" s="3">
-        <v>14500</v>
+        <v>14800</v>
       </c>
       <c r="K20" s="3">
         <v>7500</v>
@@ -1924,22 +1924,22 @@
         <v>-1700</v>
       </c>
       <c r="E21" s="3">
-        <v>13500</v>
+        <v>13800</v>
       </c>
       <c r="F21" s="3">
-        <v>34200</v>
+        <v>35100</v>
       </c>
       <c r="G21" s="3">
-        <v>31700</v>
+        <v>32500</v>
       </c>
       <c r="H21" s="3">
-        <v>39100</v>
+        <v>40100</v>
       </c>
       <c r="I21" s="3">
-        <v>26800</v>
+        <v>27500</v>
       </c>
       <c r="J21" s="3">
-        <v>59200</v>
+        <v>60700</v>
       </c>
       <c r="K21" s="3">
         <v>40800</v>
@@ -2126,22 +2126,22 @@
         <v>-700</v>
       </c>
       <c r="E23" s="3">
-        <v>13600</v>
+        <v>13900</v>
       </c>
       <c r="F23" s="3">
-        <v>22200</v>
+        <v>22700</v>
       </c>
       <c r="G23" s="3">
-        <v>31900</v>
+        <v>32700</v>
       </c>
       <c r="H23" s="3">
-        <v>38900</v>
+        <v>39900</v>
       </c>
       <c r="I23" s="3">
-        <v>25900</v>
+        <v>26600</v>
       </c>
       <c r="J23" s="3">
-        <v>49400</v>
+        <v>50600</v>
       </c>
       <c r="K23" s="3">
         <v>41400</v>
@@ -2224,25 +2224,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="E24" s="3">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="F24" s="3">
-        <v>6300</v>
+        <v>6500</v>
       </c>
       <c r="G24" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="H24" s="3">
-        <v>7700</v>
+        <v>7900</v>
       </c>
       <c r="I24" s="3">
-        <v>6700</v>
+        <v>6900</v>
       </c>
       <c r="J24" s="3">
-        <v>8800</v>
+        <v>9000</v>
       </c>
       <c r="K24" s="3">
         <v>7000</v>
@@ -2426,25 +2426,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="E26" s="3">
-        <v>10700</v>
+        <v>11000</v>
       </c>
       <c r="F26" s="3">
-        <v>15800</v>
+        <v>16200</v>
       </c>
       <c r="G26" s="3">
-        <v>29500</v>
+        <v>30300</v>
       </c>
       <c r="H26" s="3">
-        <v>31200</v>
+        <v>32000</v>
       </c>
       <c r="I26" s="3">
-        <v>19200</v>
+        <v>19700</v>
       </c>
       <c r="J26" s="3">
-        <v>40600</v>
+        <v>41600</v>
       </c>
       <c r="K26" s="3">
         <v>34500</v>
@@ -2527,25 +2527,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="E27" s="3">
-        <v>10700</v>
+        <v>11000</v>
       </c>
       <c r="F27" s="3">
-        <v>15800</v>
+        <v>16200</v>
       </c>
       <c r="G27" s="3">
-        <v>29500</v>
+        <v>30300</v>
       </c>
       <c r="H27" s="3">
-        <v>31200</v>
+        <v>32000</v>
       </c>
       <c r="I27" s="3">
-        <v>19200</v>
+        <v>19700</v>
       </c>
       <c r="J27" s="3">
-        <v>40600</v>
+        <v>41600</v>
       </c>
       <c r="K27" s="3">
         <v>34500</v>
@@ -3032,25 +3032,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1600</v>
+        <v>-1700</v>
       </c>
       <c r="E32" s="3">
-        <v>-7600</v>
+        <v>-7800</v>
       </c>
       <c r="F32" s="3">
         <v>-1600</v>
       </c>
       <c r="G32" s="3">
-        <v>-2800</v>
+        <v>-2900</v>
       </c>
       <c r="H32" s="3">
         <v>-400</v>
       </c>
       <c r="I32" s="3">
-        <v>16000</v>
+        <v>16400</v>
       </c>
       <c r="J32" s="3">
-        <v>-14500</v>
+        <v>-14800</v>
       </c>
       <c r="K32" s="3">
         <v>-7500</v>
@@ -3133,25 +3133,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="E33" s="3">
-        <v>10700</v>
+        <v>11000</v>
       </c>
       <c r="F33" s="3">
-        <v>15800</v>
+        <v>16200</v>
       </c>
       <c r="G33" s="3">
-        <v>29500</v>
+        <v>30300</v>
       </c>
       <c r="H33" s="3">
-        <v>31200</v>
+        <v>32000</v>
       </c>
       <c r="I33" s="3">
-        <v>19200</v>
+        <v>19700</v>
       </c>
       <c r="J33" s="3">
-        <v>40600</v>
+        <v>41600</v>
       </c>
       <c r="K33" s="3">
         <v>34500</v>
@@ -3335,25 +3335,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="E35" s="3">
-        <v>10700</v>
+        <v>11000</v>
       </c>
       <c r="F35" s="3">
-        <v>15800</v>
+        <v>16200</v>
       </c>
       <c r="G35" s="3">
-        <v>29500</v>
+        <v>30300</v>
       </c>
       <c r="H35" s="3">
-        <v>31200</v>
+        <v>32000</v>
       </c>
       <c r="I35" s="3">
-        <v>19200</v>
+        <v>19700</v>
       </c>
       <c r="J35" s="3">
-        <v>40600</v>
+        <v>41600</v>
       </c>
       <c r="K35" s="3">
         <v>34500</v>
@@ -3616,25 +3616,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>249300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>260600</v>
+      </c>
+      <c r="F41" s="3">
+        <v>220700</v>
+      </c>
+      <c r="G41" s="3">
+        <v>216100</v>
+      </c>
+      <c r="H41" s="3">
+        <v>261400</v>
+      </c>
+      <c r="I41" s="3">
         <v>243200</v>
       </c>
-      <c r="E41" s="3">
-        <v>254100</v>
-      </c>
-      <c r="F41" s="3">
-        <v>215200</v>
-      </c>
-      <c r="G41" s="3">
-        <v>210800</v>
-      </c>
-      <c r="H41" s="3">
-        <v>254900</v>
-      </c>
-      <c r="I41" s="3">
-        <v>237100</v>
-      </c>
       <c r="J41" s="3">
-        <v>233400</v>
+        <v>239300</v>
       </c>
       <c r="K41" s="3">
         <v>207600</v>
@@ -3735,7 +3735,7 @@
         <v>300</v>
       </c>
       <c r="J42" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K42" s="3">
         <v>500</v>
@@ -3818,25 +3818,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>228600</v>
+        <v>234400</v>
       </c>
       <c r="E43" s="3">
-        <v>220900</v>
+        <v>226500</v>
       </c>
       <c r="F43" s="3">
-        <v>244800</v>
+        <v>251000</v>
       </c>
       <c r="G43" s="3">
-        <v>232800</v>
+        <v>238700</v>
       </c>
       <c r="H43" s="3">
-        <v>235700</v>
+        <v>241700</v>
       </c>
       <c r="I43" s="3">
-        <v>225300</v>
+        <v>231100</v>
       </c>
       <c r="J43" s="3">
-        <v>247900</v>
+        <v>254200</v>
       </c>
       <c r="K43" s="3">
         <v>210400</v>
@@ -4121,25 +4121,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>472000</v>
+        <v>484000</v>
       </c>
       <c r="E46" s="3">
-        <v>475300</v>
+        <v>487400</v>
       </c>
       <c r="F46" s="3">
-        <v>460100</v>
+        <v>471800</v>
       </c>
       <c r="G46" s="3">
-        <v>443600</v>
+        <v>454900</v>
       </c>
       <c r="H46" s="3">
-        <v>490800</v>
+        <v>503300</v>
       </c>
       <c r="I46" s="3">
-        <v>462800</v>
+        <v>474500</v>
       </c>
       <c r="J46" s="3">
-        <v>481700</v>
+        <v>494000</v>
       </c>
       <c r="K46" s="3">
         <v>418500</v>
@@ -4222,25 +4222,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>9400</v>
+        <v>9700</v>
       </c>
       <c r="E47" s="3">
-        <v>8200</v>
+        <v>8400</v>
       </c>
       <c r="F47" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="G47" s="3">
-        <v>6700</v>
+        <v>6900</v>
       </c>
       <c r="H47" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="I47" s="3">
         <v>1800</v>
       </c>
       <c r="J47" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="K47" s="3">
         <v>2900</v>
@@ -4323,25 +4323,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>95800</v>
+        <v>98200</v>
       </c>
       <c r="E48" s="3">
-        <v>100000</v>
+        <v>102500</v>
       </c>
       <c r="F48" s="3">
-        <v>114700</v>
+        <v>117600</v>
       </c>
       <c r="G48" s="3">
-        <v>116500</v>
+        <v>119400</v>
       </c>
       <c r="H48" s="3">
-        <v>109000</v>
+        <v>111800</v>
       </c>
       <c r="I48" s="3">
-        <v>111100</v>
+        <v>113900</v>
       </c>
       <c r="J48" s="3">
-        <v>106100</v>
+        <v>108800</v>
       </c>
       <c r="K48" s="3">
         <v>91900</v>
@@ -4424,25 +4424,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>411400</v>
+        <v>421800</v>
       </c>
       <c r="E49" s="3">
-        <v>406000</v>
+        <v>416400</v>
       </c>
       <c r="F49" s="3">
-        <v>416200</v>
+        <v>426800</v>
       </c>
       <c r="G49" s="3">
-        <v>392900</v>
+        <v>402900</v>
       </c>
       <c r="H49" s="3">
-        <v>304400</v>
+        <v>312100</v>
       </c>
       <c r="I49" s="3">
-        <v>313200</v>
+        <v>321200</v>
       </c>
       <c r="J49" s="3">
-        <v>267400</v>
+        <v>274200</v>
       </c>
       <c r="K49" s="3">
         <v>257700</v>
@@ -4727,25 +4727,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>25500</v>
+        <v>26100</v>
       </c>
       <c r="E52" s="3">
-        <v>27300</v>
+        <v>28000</v>
       </c>
       <c r="F52" s="3">
+        <v>27000</v>
+      </c>
+      <c r="G52" s="3">
         <v>26400</v>
       </c>
-      <c r="G52" s="3">
-        <v>25800</v>
-      </c>
       <c r="H52" s="3">
-        <v>17300</v>
+        <v>17700</v>
       </c>
       <c r="I52" s="3">
-        <v>17300</v>
+        <v>17700</v>
       </c>
       <c r="J52" s="3">
-        <v>25100</v>
+        <v>25700</v>
       </c>
       <c r="K52" s="3">
         <v>22000</v>
@@ -4929,25 +4929,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1014000</v>
+        <v>1039900</v>
       </c>
       <c r="E54" s="3">
-        <v>1016700</v>
+        <v>1042600</v>
       </c>
       <c r="F54" s="3">
-        <v>1021400</v>
+        <v>1047400</v>
       </c>
       <c r="G54" s="3">
-        <v>985500</v>
+        <v>1010600</v>
       </c>
       <c r="H54" s="3">
-        <v>924000</v>
+        <v>947600</v>
       </c>
       <c r="I54" s="3">
-        <v>906100</v>
+        <v>929200</v>
       </c>
       <c r="J54" s="3">
-        <v>883900</v>
+        <v>906400</v>
       </c>
       <c r="K54" s="3">
         <v>792900</v>
@@ -5104,25 +5104,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>105300</v>
+        <v>107900</v>
       </c>
       <c r="E57" s="3">
-        <v>108400</v>
+        <v>111100</v>
       </c>
       <c r="F57" s="3">
-        <v>107400</v>
+        <v>110200</v>
       </c>
       <c r="G57" s="3">
-        <v>116600</v>
+        <v>119600</v>
       </c>
       <c r="H57" s="3">
-        <v>118600</v>
+        <v>121600</v>
       </c>
       <c r="I57" s="3">
-        <v>123500</v>
+        <v>126600</v>
       </c>
       <c r="J57" s="3">
-        <v>130800</v>
+        <v>134200</v>
       </c>
       <c r="K57" s="3">
         <v>125300</v>
@@ -5205,25 +5205,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>18300</v>
+        <v>18800</v>
       </c>
       <c r="E58" s="3">
-        <v>17600</v>
+        <v>18100</v>
       </c>
       <c r="F58" s="3">
-        <v>18800</v>
+        <v>19300</v>
       </c>
       <c r="G58" s="3">
-        <v>18600</v>
+        <v>19100</v>
       </c>
       <c r="H58" s="3">
-        <v>17700</v>
+        <v>18200</v>
       </c>
       <c r="I58" s="3">
-        <v>17600</v>
+        <v>18100</v>
       </c>
       <c r="J58" s="3">
-        <v>16600</v>
+        <v>17000</v>
       </c>
       <c r="K58" s="3">
         <v>15200</v>
@@ -5306,25 +5306,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>13900</v>
+        <v>14300</v>
       </c>
       <c r="E59" s="3">
-        <v>16600</v>
+        <v>17000</v>
       </c>
       <c r="F59" s="3">
-        <v>20900</v>
+        <v>21400</v>
       </c>
       <c r="G59" s="3">
-        <v>19000</v>
+        <v>19500</v>
       </c>
       <c r="H59" s="3">
-        <v>20000</v>
+        <v>20500</v>
       </c>
       <c r="I59" s="3">
-        <v>26200</v>
+        <v>26900</v>
       </c>
       <c r="J59" s="3">
-        <v>32800</v>
+        <v>33600</v>
       </c>
       <c r="K59" s="3">
         <v>23300</v>
@@ -5407,25 +5407,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>137500</v>
+        <v>141000</v>
       </c>
       <c r="E60" s="3">
-        <v>142500</v>
+        <v>146200</v>
       </c>
       <c r="F60" s="3">
-        <v>147100</v>
+        <v>150800</v>
       </c>
       <c r="G60" s="3">
-        <v>154300</v>
+        <v>158200</v>
       </c>
       <c r="H60" s="3">
-        <v>156300</v>
+        <v>160300</v>
       </c>
       <c r="I60" s="3">
-        <v>167300</v>
+        <v>171600</v>
       </c>
       <c r="J60" s="3">
-        <v>180200</v>
+        <v>184800</v>
       </c>
       <c r="K60" s="3">
         <v>163700</v>
@@ -5508,25 +5508,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>55000</v>
+        <v>56400</v>
       </c>
       <c r="E61" s="3">
-        <v>58400</v>
+        <v>59900</v>
       </c>
       <c r="F61" s="3">
-        <v>69400</v>
+        <v>71200</v>
       </c>
       <c r="G61" s="3">
-        <v>69700</v>
+        <v>71400</v>
       </c>
       <c r="H61" s="3">
-        <v>64200</v>
+        <v>65900</v>
       </c>
       <c r="I61" s="3">
-        <v>69000</v>
+        <v>70800</v>
       </c>
       <c r="J61" s="3">
-        <v>65700</v>
+        <v>67300</v>
       </c>
       <c r="K61" s="3">
         <v>56100</v>
@@ -5609,25 +5609,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>22100</v>
+        <v>22600</v>
       </c>
       <c r="E62" s="3">
-        <v>22500</v>
+        <v>23000</v>
       </c>
       <c r="F62" s="3">
-        <v>38100</v>
+        <v>39100</v>
       </c>
       <c r="G62" s="3">
-        <v>30400</v>
+        <v>31200</v>
       </c>
       <c r="H62" s="3">
-        <v>15400</v>
+        <v>15800</v>
       </c>
       <c r="I62" s="3">
-        <v>16600</v>
+        <v>17000</v>
       </c>
       <c r="J62" s="3">
-        <v>18000</v>
+        <v>18400</v>
       </c>
       <c r="K62" s="3">
         <v>21300</v>
@@ -6013,25 +6013,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>214500</v>
+        <v>220000</v>
       </c>
       <c r="E66" s="3">
-        <v>223400</v>
+        <v>229100</v>
       </c>
       <c r="F66" s="3">
-        <v>254600</v>
+        <v>261100</v>
       </c>
       <c r="G66" s="3">
-        <v>254400</v>
+        <v>260900</v>
       </c>
       <c r="H66" s="3">
-        <v>235900</v>
+        <v>241900</v>
       </c>
       <c r="I66" s="3">
-        <v>252900</v>
+        <v>259400</v>
       </c>
       <c r="J66" s="3">
-        <v>263800</v>
+        <v>270600</v>
       </c>
       <c r="K66" s="3">
         <v>241200</v>
@@ -6555,25 +6555,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>770900</v>
+        <v>790500</v>
       </c>
       <c r="E72" s="3">
-        <v>769200</v>
+        <v>788700</v>
       </c>
       <c r="F72" s="3">
-        <v>746600</v>
+        <v>765600</v>
       </c>
       <c r="G72" s="3">
-        <v>710900</v>
+        <v>729000</v>
       </c>
       <c r="H72" s="3">
-        <v>669500</v>
+        <v>686500</v>
       </c>
       <c r="I72" s="3">
-        <v>624600</v>
+        <v>640500</v>
       </c>
       <c r="J72" s="3">
-        <v>607100</v>
+        <v>622500</v>
       </c>
       <c r="K72" s="3">
         <v>538800</v>
@@ -6959,25 +6959,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>799500</v>
+        <v>819900</v>
       </c>
       <c r="E76" s="3">
-        <v>793300</v>
+        <v>813500</v>
       </c>
       <c r="F76" s="3">
-        <v>766800</v>
+        <v>786300</v>
       </c>
       <c r="G76" s="3">
-        <v>731100</v>
+        <v>749700</v>
       </c>
       <c r="H76" s="3">
-        <v>688100</v>
+        <v>705600</v>
       </c>
       <c r="I76" s="3">
-        <v>653200</v>
+        <v>669800</v>
       </c>
       <c r="J76" s="3">
-        <v>620100</v>
+        <v>635800</v>
       </c>
       <c r="K76" s="3">
         <v>551800</v>
@@ -7267,25 +7267,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="E81" s="3">
-        <v>10700</v>
+        <v>11000</v>
       </c>
       <c r="F81" s="3">
-        <v>15800</v>
+        <v>16200</v>
       </c>
       <c r="G81" s="3">
-        <v>29500</v>
+        <v>30300</v>
       </c>
       <c r="H81" s="3">
-        <v>31200</v>
+        <v>32000</v>
       </c>
       <c r="I81" s="3">
-        <v>19200</v>
+        <v>19700</v>
       </c>
       <c r="J81" s="3">
-        <v>40600</v>
+        <v>41600</v>
       </c>
       <c r="K81" s="3">
         <v>34500</v>
@@ -8011,25 +8011,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="E89" s="3">
-        <v>44800</v>
+        <v>46000</v>
       </c>
       <c r="F89" s="3">
-        <v>21200</v>
+        <v>21800</v>
       </c>
       <c r="G89" s="3">
-        <v>42600</v>
+        <v>43700</v>
       </c>
       <c r="H89" s="3">
-        <v>32100</v>
+        <v>32900</v>
       </c>
       <c r="I89" s="3">
-        <v>52300</v>
+        <v>53700</v>
       </c>
       <c r="J89" s="3">
-        <v>32300</v>
+        <v>33100</v>
       </c>
       <c r="K89" s="3">
         <v>60100</v>
@@ -8452,25 +8452,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-15200</v>
+        <v>-15600</v>
       </c>
       <c r="E94" s="3">
         <v>-2600</v>
       </c>
       <c r="F94" s="3">
-        <v>-12900</v>
+        <v>-13300</v>
       </c>
       <c r="G94" s="3">
-        <v>-83500</v>
+        <v>-85700</v>
       </c>
       <c r="H94" s="3">
-        <v>-8200</v>
+        <v>-8400</v>
       </c>
       <c r="I94" s="3">
-        <v>-46200</v>
+        <v>-47400</v>
       </c>
       <c r="J94" s="3">
-        <v>-3900</v>
+        <v>-4000</v>
       </c>
       <c r="K94" s="3">
         <v>-4900</v>
@@ -9000,19 +9000,19 @@
         <v>-800</v>
       </c>
       <c r="F100" s="3">
-        <v>-5000</v>
+        <v>-5200</v>
       </c>
       <c r="G100" s="3">
         <v>-3500</v>
       </c>
       <c r="H100" s="3">
-        <v>-5300</v>
+        <v>-5400</v>
       </c>
       <c r="I100" s="3">
-        <v>-1300</v>
+        <v>-1400</v>
       </c>
       <c r="J100" s="3">
-        <v>-4000</v>
+        <v>-4100</v>
       </c>
       <c r="K100" s="3">
         <v>-2300</v>
@@ -9110,7 +9110,7 @@
         <v>-900</v>
       </c>
       <c r="I101" s="3">
-        <v>-1000</v>
+        <v>-1100</v>
       </c>
       <c r="J101" s="3">
         <v>700</v>
@@ -9196,25 +9196,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-11000</v>
+        <v>-11300</v>
       </c>
       <c r="E102" s="3">
-        <v>38900</v>
+        <v>39900</v>
       </c>
       <c r="F102" s="3">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="G102" s="3">
-        <v>-44100</v>
+        <v>-45300</v>
       </c>
       <c r="H102" s="3">
-        <v>17800</v>
+        <v>18200</v>
       </c>
       <c r="I102" s="3">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="J102" s="3">
-        <v>25100</v>
+        <v>25700</v>
       </c>
       <c r="K102" s="3">
         <v>54100</v>

--- a/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="92">
   <si>
     <t>DAVA</t>
   </si>
@@ -656,452 +656,478 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>228800</v>
+        <v>261400</v>
       </c>
       <c r="E8" s="3">
-        <v>240900</v>
+        <v>245700</v>
       </c>
       <c r="F8" s="3">
-        <v>247200</v>
+        <v>220200</v>
       </c>
       <c r="G8" s="3">
-        <v>249100</v>
+        <v>233800</v>
       </c>
       <c r="H8" s="3">
-        <v>267000</v>
+        <v>229900</v>
       </c>
       <c r="I8" s="3">
+        <v>241200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>251800</v>
+      </c>
+      <c r="K8" s="3">
         <v>269300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>257500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>230000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>209900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>199900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>186900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>165800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>131500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>123200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>112500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>110400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>122700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>117100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>112400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>105200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>97300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>94800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>87700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>79500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>201800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>65200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>62000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>56100</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI8" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK8" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>180000</v>
+        <v>196200</v>
       </c>
       <c r="E9" s="3">
-        <v>182000</v>
+        <v>179600</v>
       </c>
       <c r="F9" s="3">
-        <v>175800</v>
+        <v>173200</v>
       </c>
       <c r="G9" s="3">
-        <v>170900</v>
+        <v>176600</v>
       </c>
       <c r="H9" s="3">
-        <v>182300</v>
+        <v>163500</v>
       </c>
       <c r="I9" s="3">
+        <v>158600</v>
+      </c>
+      <c r="J9" s="3">
+        <v>171800</v>
+      </c>
+      <c r="K9" s="3">
         <v>174200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>169000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>156400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>141200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>133800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>120100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>109100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>86400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>79900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>73600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>77400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>75200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>106700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>71900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>69600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>64000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>61300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>58000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>51800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>136200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>44400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>42200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>38000</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>48900</v>
+        <v>65200</v>
       </c>
       <c r="E10" s="3">
-        <v>58900</v>
+        <v>66100</v>
       </c>
       <c r="F10" s="3">
-        <v>71400</v>
+        <v>47000</v>
       </c>
       <c r="G10" s="3">
-        <v>78100</v>
+        <v>57200</v>
       </c>
       <c r="H10" s="3">
-        <v>84800</v>
+        <v>66500</v>
       </c>
       <c r="I10" s="3">
+        <v>82600</v>
+      </c>
+      <c r="J10" s="3">
+        <v>80000</v>
+      </c>
+      <c r="K10" s="3">
         <v>95100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>88500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>73600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>68700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>66000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>66800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>56700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>45100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>43400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>38900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>33000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>47500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>10500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>40500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>35600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>33300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>33500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>29700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>27700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>65600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>20900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>19700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>18100</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1137,8 +1163,10 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1238,8 +1266,14 @@
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1339,50 +1373,56 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>5900</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>900</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-4400</v>
+        <v>-9900</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>3100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>1700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-1400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>1500</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1399,132 +1439,138 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-3000</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>1600</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG14" s="3">
         <v>500</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>4900</v>
+        <v>9200</v>
       </c>
       <c r="E15" s="3">
-        <v>5900</v>
+        <v>8000</v>
       </c>
       <c r="F15" s="3">
-        <v>5500</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
+        <v>10800</v>
+      </c>
+      <c r="G15" s="3">
+        <v>-5400</v>
       </c>
       <c r="H15" s="3">
         <v>5200</v>
       </c>
       <c r="I15" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J15" s="3">
+        <v>10600</v>
+      </c>
+      <c r="K15" s="3">
         <v>5000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>4700</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3">
         <v>4200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>3900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>3900</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3">
         <v>1800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>2100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>2100</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V15" s="3">
         <v>2200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>2000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>1900</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z15" s="3">
         <v>1300</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>0</v>
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE15" s="3">
         <v>0</v>
@@ -1541,8 +1587,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1575,210 +1627,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>231200</v>
+        <v>255100</v>
       </c>
       <c r="E17" s="3">
-        <v>234800</v>
+        <v>226300</v>
       </c>
       <c r="F17" s="3">
-        <v>226100</v>
+        <v>222500</v>
       </c>
       <c r="G17" s="3">
-        <v>219200</v>
+        <v>226800</v>
       </c>
       <c r="H17" s="3">
-        <v>227600</v>
+        <v>210300</v>
       </c>
       <c r="I17" s="3">
+        <v>201500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>214600</v>
+      </c>
+      <c r="K17" s="3">
         <v>226300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>221700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>196100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>178400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>175200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>156600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>141200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>110400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>106800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>98700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>102000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>104000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>132800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>92500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>93300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>87400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>82900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>77400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>71200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>177300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>57200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>52900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>47800</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2400</v>
+        <v>6300</v>
       </c>
       <c r="E18" s="3">
-        <v>6100</v>
+        <v>19400</v>
       </c>
       <c r="F18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G18" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>19700</v>
+      </c>
+      <c r="I18" s="3">
+        <v>39700</v>
+      </c>
+      <c r="J18" s="3">
+        <v>37200</v>
+      </c>
+      <c r="K18" s="3">
+        <v>43000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>35800</v>
+      </c>
+      <c r="M18" s="3">
+        <v>34000</v>
+      </c>
+      <c r="N18" s="3">
+        <v>31500</v>
+      </c>
+      <c r="O18" s="3">
+        <v>24700</v>
+      </c>
+      <c r="P18" s="3">
+        <v>30300</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>24500</v>
+      </c>
+      <c r="R18" s="3">
         <v>21100</v>
       </c>
-      <c r="G18" s="3">
-        <v>29800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>39500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>43000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>35800</v>
-      </c>
-      <c r="K18" s="3">
-        <v>34000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>31500</v>
-      </c>
-      <c r="M18" s="3">
-        <v>24700</v>
-      </c>
-      <c r="N18" s="3">
-        <v>30300</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="S18" s="3">
+        <v>16400</v>
+      </c>
+      <c r="T18" s="3">
+        <v>13800</v>
+      </c>
+      <c r="U18" s="3">
+        <v>8400</v>
+      </c>
+      <c r="V18" s="3">
+        <v>18800</v>
+      </c>
+      <c r="W18" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="X18" s="3">
+        <v>19900</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>11900</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>12000</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>10300</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>8400</v>
+      </c>
+      <c r="AD18" s="3">
         <v>24500</v>
       </c>
-      <c r="P18" s="3">
-        <v>21100</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>16400</v>
-      </c>
-      <c r="R18" s="3">
-        <v>13800</v>
-      </c>
-      <c r="S18" s="3">
-        <v>8400</v>
-      </c>
-      <c r="T18" s="3">
-        <v>18800</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-15600</v>
-      </c>
-      <c r="V18" s="3">
-        <v>19900</v>
-      </c>
-      <c r="W18" s="3">
-        <v>11900</v>
-      </c>
-      <c r="X18" s="3">
-        <v>9900</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>12000</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>10300</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>8400</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>24500</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>8000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>9000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>8200</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1814,233 +1880,247 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>1700</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>7800</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>2900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>400</v>
+        <v>3200</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I20" s="3">
+        <v>12100</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>-16400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>14800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>7500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-4000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-3400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>5600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-7900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>3900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>2500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1700</v>
+        <v>15500</v>
       </c>
       <c r="E21" s="3">
-        <v>13800</v>
+        <v>24200</v>
       </c>
       <c r="F21" s="3">
-        <v>35100</v>
+        <v>8500</v>
       </c>
       <c r="G21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>24800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>34300</v>
+      </c>
+      <c r="J21" s="3">
+        <v>47800</v>
+      </c>
+      <c r="K21" s="3">
+        <v>27500</v>
+      </c>
+      <c r="L21" s="3">
+        <v>60700</v>
+      </c>
+      <c r="M21" s="3">
+        <v>40800</v>
+      </c>
+      <c r="N21" s="3">
         <v>32500</v>
-      </c>
-      <c r="H21" s="3">
-        <v>40100</v>
-      </c>
-      <c r="I21" s="3">
-        <v>27500</v>
-      </c>
-      <c r="J21" s="3">
-        <v>60700</v>
-      </c>
-      <c r="K21" s="3">
-        <v>40800</v>
-      </c>
-      <c r="L21" s="3">
-        <v>32500</v>
-      </c>
-      <c r="M21" s="3">
-        <v>24500</v>
-      </c>
-      <c r="N21" s="3">
-        <v>40400</v>
       </c>
       <c r="O21" s="3">
         <v>24500</v>
       </c>
       <c r="P21" s="3">
+        <v>40400</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>24500</v>
+      </c>
+      <c r="R21" s="3">
         <v>18100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>13300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>16600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>8500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>24700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-22900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>29500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>14400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>11600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>12400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>4600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>11000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>29000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>7900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>9000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>8900</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+        <v>7900</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+        <v>1900</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>3500</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2117,201 +2197,213 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-700</v>
       </c>
-      <c r="E23" s="3">
-        <v>13900</v>
-      </c>
-      <c r="F23" s="3">
-        <v>22700</v>
-      </c>
       <c r="G23" s="3">
-        <v>32700</v>
+        <v>13500</v>
       </c>
       <c r="H23" s="3">
-        <v>39900</v>
+        <v>21100</v>
       </c>
       <c r="I23" s="3">
+        <v>31700</v>
+      </c>
+      <c r="J23" s="3">
+        <v>37600</v>
+      </c>
+      <c r="K23" s="3">
         <v>26600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>50600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>41400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>32100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>24200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>31600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>23000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>19300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>12400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>10300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>8200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>24400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-23500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>23800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>14300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>10100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>12400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>3500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>8600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>23200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>7900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>8400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>7200</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="E24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G24" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J24" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K24" s="3">
+        <v>6900</v>
+      </c>
+      <c r="L24" s="3">
+        <v>9000</v>
+      </c>
+      <c r="M24" s="3">
+        <v>7000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>7200</v>
+      </c>
+      <c r="O24" s="3">
+        <v>4700</v>
+      </c>
+      <c r="P24" s="3">
+        <v>5500</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>3200</v>
+      </c>
+      <c r="R24" s="3">
+        <v>4100</v>
+      </c>
+      <c r="S24" s="3">
+        <v>3300</v>
+      </c>
+      <c r="T24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="U24" s="3">
+        <v>800</v>
+      </c>
+      <c r="V24" s="3">
+        <v>4900</v>
+      </c>
+      <c r="W24" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="X24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Y24" s="3">
         <v>3000</v>
       </c>
-      <c r="F24" s="3">
-        <v>6500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H24" s="3">
-        <v>7900</v>
-      </c>
-      <c r="I24" s="3">
-        <v>6900</v>
-      </c>
-      <c r="J24" s="3">
-        <v>9000</v>
-      </c>
-      <c r="K24" s="3">
-        <v>7000</v>
-      </c>
-      <c r="L24" s="3">
-        <v>7200</v>
-      </c>
-      <c r="M24" s="3">
-        <v>4700</v>
-      </c>
-      <c r="N24" s="3">
-        <v>5500</v>
-      </c>
-      <c r="O24" s="3">
-        <v>3200</v>
-      </c>
-      <c r="P24" s="3">
-        <v>4100</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>3300</v>
-      </c>
-      <c r="R24" s="3">
-        <v>2400</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="Z24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AB24" s="3">
         <v>800</v>
       </c>
-      <c r="T24" s="3">
-        <v>4900</v>
-      </c>
-      <c r="U24" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="V24" s="3">
-        <v>4000</v>
-      </c>
-      <c r="W24" s="3">
-        <v>3000</v>
-      </c>
-      <c r="X24" s="3">
-        <v>1700</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>2600</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>800</v>
-      </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>2300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>5000</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>1800</v>
       </c>
       <c r="AE24" s="3">
         <v>1600</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG24" s="3" t="s">
-        <v>3</v>
+      <c r="AF24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>1600</v>
       </c>
       <c r="AH24" s="3" t="s">
         <v>3</v>
@@ -2319,8 +2411,14 @@
       <c r="AI24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2420,210 +2518,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2300</v>
       </c>
-      <c r="E26" s="3">
-        <v>11000</v>
-      </c>
       <c r="F26" s="3">
-        <v>16200</v>
+        <v>-2200</v>
       </c>
       <c r="G26" s="3">
-        <v>30300</v>
+        <v>10600</v>
       </c>
       <c r="H26" s="3">
-        <v>32000</v>
+        <v>15100</v>
       </c>
       <c r="I26" s="3">
+        <v>29300</v>
+      </c>
+      <c r="J26" s="3">
+        <v>30100</v>
+      </c>
+      <c r="K26" s="3">
         <v>19700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>41600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>34500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>24900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>19500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>26000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>19800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>15200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>9100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>7900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>7500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>19400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-18800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>19800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>11300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>8400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>9800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>2700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>6300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>18200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>6200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>6600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>5600</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2300</v>
       </c>
-      <c r="E27" s="3">
-        <v>11000</v>
-      </c>
       <c r="F27" s="3">
-        <v>16200</v>
+        <v>-2200</v>
       </c>
       <c r="G27" s="3">
-        <v>30300</v>
+        <v>10600</v>
       </c>
       <c r="H27" s="3">
-        <v>32000</v>
+        <v>15100</v>
       </c>
       <c r="I27" s="3">
+        <v>29300</v>
+      </c>
+      <c r="J27" s="3">
+        <v>30100</v>
+      </c>
+      <c r="K27" s="3">
         <v>19700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>41600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>34500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>24900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>19500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>26000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>19800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>15200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>9100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>7900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>7500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>19400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-18800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>19800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>11300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>8400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>9800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>2700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>6300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>18200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>6200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>6600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>5600</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2723,8 +2839,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2824,8 +2946,14 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2925,8 +3053,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3026,210 +3160,228 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-1700</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-400</v>
+        <v>-3200</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I32" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>16400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-14800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-7500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>1800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>4000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>3400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-5600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>7900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-3900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-2500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>6800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>1300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>1000</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2300</v>
       </c>
-      <c r="E33" s="3">
-        <v>11000</v>
-      </c>
       <c r="F33" s="3">
-        <v>16200</v>
+        <v>-2200</v>
       </c>
       <c r="G33" s="3">
-        <v>30300</v>
+        <v>10600</v>
       </c>
       <c r="H33" s="3">
-        <v>32000</v>
+        <v>15100</v>
       </c>
       <c r="I33" s="3">
+        <v>29300</v>
+      </c>
+      <c r="J33" s="3">
+        <v>30100</v>
+      </c>
+      <c r="K33" s="3">
         <v>19700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>41600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>34500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>24900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>19500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>26000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>19800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>15200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>9100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>7900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>7500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>19400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-18800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>19800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>11300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>8400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>9800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>2700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>6300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>18200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>6200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>6600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>5600</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3329,215 +3481,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2300</v>
       </c>
-      <c r="E35" s="3">
-        <v>11000</v>
-      </c>
       <c r="F35" s="3">
-        <v>16200</v>
+        <v>-2200</v>
       </c>
       <c r="G35" s="3">
-        <v>30300</v>
+        <v>10600</v>
       </c>
       <c r="H35" s="3">
-        <v>32000</v>
+        <v>15100</v>
       </c>
       <c r="I35" s="3">
+        <v>29300</v>
+      </c>
+      <c r="J35" s="3">
+        <v>30100</v>
+      </c>
+      <c r="K35" s="3">
         <v>19700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>41600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>34500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>24900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>19500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>26000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>19800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>15200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>9100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>7900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>7500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>19400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-18800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>19800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>11300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>8400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>9800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>2700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>6300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>18200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>6200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>6600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>5600</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3573,8 +3743,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3610,98 +3782,100 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>249300</v>
+        <v>70800</v>
       </c>
       <c r="E41" s="3">
-        <v>260600</v>
+        <v>78800</v>
       </c>
       <c r="F41" s="3">
-        <v>220700</v>
+        <v>240000</v>
       </c>
       <c r="G41" s="3">
-        <v>216100</v>
+        <v>253000</v>
       </c>
       <c r="H41" s="3">
-        <v>261400</v>
+        <v>205200</v>
       </c>
       <c r="I41" s="3">
+        <v>209300</v>
+      </c>
+      <c r="J41" s="3">
+        <v>246400</v>
+      </c>
+      <c r="K41" s="3">
         <v>243200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>239300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>207600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>149400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>144700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>104000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>86700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>92300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>98600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>82800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>123600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>116000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>107700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>114100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>96400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>79000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>67400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>55200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>19500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>12200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>32700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>21700</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3711,46 +3885,52 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>600</v>
-      </c>
-      <c r="N42" s="3">
-        <v>700</v>
-      </c>
-      <c r="O42" s="3">
-        <v>700</v>
       </c>
       <c r="P42" s="3">
         <v>700</v>
@@ -3765,19 +3945,19 @@
         <v>700</v>
       </c>
       <c r="T42" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="U42" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="V42" s="3">
         <v>800</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
+      <c r="W42" s="3">
+        <v>800</v>
+      </c>
+      <c r="X42" s="3">
+        <v>800</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
@@ -3791,11 +3971,11 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE42" s="3">
         <v>0</v>
@@ -3812,98 +3992,104 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>234400</v>
+        <v>279000</v>
       </c>
       <c r="E43" s="3">
-        <v>226500</v>
+        <v>244900</v>
       </c>
       <c r="F43" s="3">
-        <v>251000</v>
+        <v>225800</v>
       </c>
       <c r="G43" s="3">
-        <v>238700</v>
+        <v>220100</v>
       </c>
       <c r="H43" s="3">
-        <v>241700</v>
+        <v>233500</v>
       </c>
       <c r="I43" s="3">
+        <v>219100</v>
+      </c>
+      <c r="J43" s="3">
+        <v>228100</v>
+      </c>
+      <c r="K43" s="3">
         <v>231100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>254200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>210400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>199500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>183800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>180400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>148000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>129500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>110300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>112800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>104300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>108700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>107000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>93700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>91600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>84800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>84900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>80800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>68600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>64900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>64400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>59300</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3913,31 +4099,37 @@
       <c r="AI43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3991,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="AB44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC44" s="3">
         <v>0</v>
@@ -3999,11 +4191,11 @@
       <c r="AD44" s="3">
         <v>100</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF44" s="3" t="s">
-        <v>3</v>
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="3">
+        <v>100</v>
       </c>
       <c r="AG44" s="3" t="s">
         <v>3</v>
@@ -4014,31 +4206,37 @@
       <c r="AI44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK44" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4115,98 +4313,104 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>484000</v>
+        <v>349800</v>
       </c>
       <c r="E46" s="3">
-        <v>487400</v>
+        <v>338200</v>
       </c>
       <c r="F46" s="3">
-        <v>471800</v>
+        <v>465800</v>
       </c>
       <c r="G46" s="3">
-        <v>454900</v>
+        <v>473100</v>
       </c>
       <c r="H46" s="3">
-        <v>503300</v>
+        <v>438800</v>
       </c>
       <c r="I46" s="3">
+        <v>442400</v>
+      </c>
+      <c r="J46" s="3">
         <v>474500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
+        <v>474500</v>
+      </c>
+      <c r="L46" s="3">
         <v>494000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>418500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>349300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>329100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>285100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>235400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>222500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>209600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>196300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>228700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>225500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>215500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>208600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>188000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>163800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>152400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>136000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>88000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>77200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>97100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>81100</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4216,91 +4420,97 @@
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>9700</v>
-      </c>
-      <c r="E47" s="3">
-        <v>8400</v>
-      </c>
-      <c r="F47" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G47" s="3">
-        <v>6900</v>
-      </c>
-      <c r="H47" s="3">
-        <v>2600</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>1800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>3700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>1500</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD47" s="3" t="s">
-        <v>3</v>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>0</v>
       </c>
       <c r="AE47" s="3" t="s">
         <v>3</v>
@@ -4317,98 +4527,104 @@
       <c r="AI47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>98200</v>
+        <v>92000</v>
       </c>
       <c r="E48" s="3">
-        <v>102500</v>
+        <v>93400</v>
       </c>
       <c r="F48" s="3">
-        <v>117600</v>
+        <v>94500</v>
       </c>
       <c r="G48" s="3">
-        <v>119400</v>
+        <v>99500</v>
       </c>
       <c r="H48" s="3">
-        <v>111800</v>
+        <v>109300</v>
       </c>
       <c r="I48" s="3">
+        <v>115700</v>
+      </c>
+      <c r="J48" s="3">
+        <v>105400</v>
+      </c>
+      <c r="K48" s="3">
         <v>113900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>108800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>91900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>86200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>87400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>89500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>87500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>62700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>68900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>72400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>77900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>81500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>83000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>65700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>14500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>12500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>13200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>12200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>11100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>10800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>11400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>10400</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4418,98 +4634,104 @@
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>421800</v>
+        <v>817600</v>
       </c>
       <c r="E49" s="3">
-        <v>416400</v>
+        <v>813300</v>
       </c>
       <c r="F49" s="3">
-        <v>426800</v>
+        <v>406000</v>
       </c>
       <c r="G49" s="3">
-        <v>402900</v>
+        <v>404200</v>
       </c>
       <c r="H49" s="3">
-        <v>312100</v>
+        <v>397000</v>
       </c>
       <c r="I49" s="3">
+        <v>387200</v>
+      </c>
+      <c r="J49" s="3">
+        <v>294300</v>
+      </c>
+      <c r="K49" s="3">
         <v>321200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>274200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>257700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>251200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>239500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>246300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>233800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>178500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>161300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>167700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>116800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>127400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>124000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>89100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>90200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>93200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>96100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>94900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>92900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>89600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>93700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>41900</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4519,8 +4741,14 @@
       <c r="AI49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4620,8 +4848,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4721,98 +4955,104 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>26100</v>
+        <v>12700</v>
       </c>
       <c r="E52" s="3">
-        <v>28000</v>
+        <v>12800</v>
       </c>
       <c r="F52" s="3">
-        <v>27000</v>
+        <v>9300</v>
       </c>
       <c r="G52" s="3">
-        <v>26400</v>
+        <v>8100</v>
       </c>
       <c r="H52" s="3">
+        <v>3900</v>
+      </c>
+      <c r="I52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K52" s="3">
         <v>17700</v>
       </c>
-      <c r="I52" s="3">
-        <v>17700</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>25700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>22000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>22300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>27100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>30300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>24900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>15200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>15900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>18700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>16300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>12400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>15600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>13400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>13100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>6300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>3300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>3300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>3200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>1200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>1200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>1100</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4822,8 +5062,14 @@
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4923,98 +5169,104 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1039900</v>
+        <v>1297000</v>
       </c>
       <c r="E54" s="3">
-        <v>1042600</v>
+        <v>1281300</v>
       </c>
       <c r="F54" s="3">
-        <v>1047400</v>
+        <v>1000900</v>
       </c>
       <c r="G54" s="3">
-        <v>1010600</v>
+        <v>1012100</v>
       </c>
       <c r="H54" s="3">
-        <v>947600</v>
+        <v>974100</v>
       </c>
       <c r="I54" s="3">
+        <v>978600</v>
+      </c>
+      <c r="J54" s="3">
+        <v>893300</v>
+      </c>
+      <c r="K54" s="3">
         <v>929200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>906400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>792900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>709200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>683300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>651500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>582000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>479500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>456400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>456000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>440400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>448000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>439300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>378300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>305800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>275800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>265000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>246400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>195200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>178800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>203400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>134500</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5024,8 +5276,14 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5061,8 +5319,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5098,98 +5358,100 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>136900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F57" s="3">
+        <v>103900</v>
+      </c>
+      <c r="G57" s="3">
         <v>107900</v>
       </c>
-      <c r="E57" s="3">
-        <v>111100</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
+        <v>102400</v>
+      </c>
+      <c r="I57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>114600</v>
+      </c>
+      <c r="K57" s="3">
+        <v>126600</v>
+      </c>
+      <c r="L57" s="3">
+        <v>134200</v>
+      </c>
+      <c r="M57" s="3">
+        <v>125300</v>
+      </c>
+      <c r="N57" s="3">
         <v>110200</v>
       </c>
-      <c r="G57" s="3">
-        <v>119600</v>
-      </c>
-      <c r="H57" s="3">
-        <v>121600</v>
-      </c>
-      <c r="I57" s="3">
-        <v>126600</v>
-      </c>
-      <c r="J57" s="3">
-        <v>134200</v>
-      </c>
-      <c r="K57" s="3">
-        <v>125300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>110200</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>119200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>109000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>97400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>76600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>73900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>78200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>71500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>84200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>98900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>65600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>62500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>58600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>55300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>53900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>52000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>42500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>37200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>32700</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5199,98 +5461,104 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>18800</v>
+        <v>19000</v>
       </c>
       <c r="E58" s="3">
+        <v>18300</v>
+      </c>
+      <c r="F58" s="3">
         <v>18100</v>
       </c>
-      <c r="F58" s="3">
-        <v>19300</v>
-      </c>
       <c r="G58" s="3">
-        <v>19100</v>
+        <v>17600</v>
       </c>
       <c r="H58" s="3">
-        <v>18200</v>
+        <v>17900</v>
       </c>
       <c r="I58" s="3">
+        <v>18500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>17100</v>
+      </c>
+      <c r="K58" s="3">
         <v>18100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>17000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>15200</v>
-      </c>
-      <c r="L58" s="3">
-        <v>14600</v>
       </c>
       <c r="M58" s="3">
         <v>15200</v>
       </c>
       <c r="N58" s="3">
+        <v>14600</v>
+      </c>
+      <c r="O58" s="3">
+        <v>15200</v>
+      </c>
+      <c r="P58" s="3">
         <v>16500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>16800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>14300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>14200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>13100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>13600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>14300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>15600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>11700</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>25500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>30500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>50800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>26800</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5300,98 +5568,104 @@
       <c r="AI58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>14300</v>
+        <v>28200</v>
       </c>
       <c r="E59" s="3">
-        <v>17000</v>
+        <v>44500</v>
       </c>
       <c r="F59" s="3">
-        <v>21400</v>
+        <v>13700</v>
       </c>
       <c r="G59" s="3">
-        <v>19500</v>
+        <v>16500</v>
       </c>
       <c r="H59" s="3">
-        <v>20500</v>
+        <v>19900</v>
       </c>
       <c r="I59" s="3">
+        <v>32000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>19300</v>
+      </c>
+      <c r="K59" s="3">
         <v>26900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>33600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>23300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>19000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>16600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>23400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>13300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>8500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>6700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>9500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>8300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>9600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>5200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>8500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>11900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>6700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>9500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>7600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>14400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>10900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>23300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>500</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5401,98 +5675,104 @@
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>141000</v>
+        <v>184100</v>
       </c>
       <c r="E60" s="3">
-        <v>146200</v>
+        <v>194400</v>
       </c>
       <c r="F60" s="3">
-        <v>150800</v>
+        <v>135700</v>
       </c>
       <c r="G60" s="3">
-        <v>158200</v>
+        <v>141900</v>
       </c>
       <c r="H60" s="3">
-        <v>160300</v>
+        <v>140300</v>
       </c>
       <c r="I60" s="3">
+        <v>153400</v>
+      </c>
+      <c r="J60" s="3">
+        <v>151100</v>
+      </c>
+      <c r="K60" s="3">
         <v>171600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>184800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>163700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>143900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>150900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>148800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>127500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>99400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>94900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>100800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>93300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>108200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>119700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>85800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>74400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>65300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>64900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>61500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>92000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>83900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>111300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>60000</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5502,74 +5782,80 @@
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>56400</v>
+        <v>232500</v>
       </c>
       <c r="E61" s="3">
-        <v>59900</v>
+        <v>238000</v>
       </c>
       <c r="F61" s="3">
-        <v>71200</v>
+        <v>54300</v>
       </c>
       <c r="G61" s="3">
-        <v>71400</v>
+        <v>58100</v>
       </c>
       <c r="H61" s="3">
-        <v>65900</v>
+        <v>66200</v>
       </c>
       <c r="I61" s="3">
+        <v>69200</v>
+      </c>
+      <c r="J61" s="3">
+        <v>62100</v>
+      </c>
+      <c r="K61" s="3">
         <v>70800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>67300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>56100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>54600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>56600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>60300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>62200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>40500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>45800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>48000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>51500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>53800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>53900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>40400</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -5583,17 +5869,17 @@
         <v>0</v>
       </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>100</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -5603,98 +5889,104 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>22600</v>
+        <v>1800</v>
       </c>
       <c r="E62" s="3">
-        <v>23000</v>
+        <v>1800</v>
       </c>
       <c r="F62" s="3">
-        <v>39100</v>
+        <v>5000</v>
       </c>
       <c r="G62" s="3">
-        <v>31200</v>
+        <v>4900</v>
       </c>
       <c r="H62" s="3">
-        <v>15800</v>
+        <v>19000</v>
       </c>
       <c r="I62" s="3">
+        <v>11600</v>
+      </c>
+      <c r="J62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K62" s="3">
         <v>17000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>18400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>21300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>20600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>15000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>18200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>24400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>17100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>12500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>12900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>7300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>9400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>6600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>3800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>4100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>13400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>14100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>14500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>3800</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5704,8 +5996,14 @@
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5805,8 +6103,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5906,8 +6210,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6007,98 +6317,104 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>220000</v>
+        <v>457400</v>
       </c>
       <c r="E66" s="3">
-        <v>229100</v>
+        <v>473200</v>
       </c>
       <c r="F66" s="3">
-        <v>261100</v>
+        <v>211800</v>
       </c>
       <c r="G66" s="3">
-        <v>260900</v>
+        <v>222400</v>
       </c>
       <c r="H66" s="3">
-        <v>241900</v>
+        <v>242800</v>
       </c>
       <c r="I66" s="3">
+        <v>252600</v>
+      </c>
+      <c r="J66" s="3">
+        <v>228100</v>
+      </c>
+      <c r="K66" s="3">
         <v>259400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>270600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>241200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>219100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>222500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>227300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>214200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>157000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>153200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>161700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>152200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>171300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>180200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>129000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>77400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>68500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>68700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>65600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>105400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>98000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>125900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>63800</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6108,8 +6424,14 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6145,8 +6467,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6246,8 +6570,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6347,8 +6677,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6448,8 +6784,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6549,98 +6891,104 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>790500</v>
+        <v>782700</v>
       </c>
       <c r="E72" s="3">
-        <v>788700</v>
+        <v>725000</v>
       </c>
       <c r="F72" s="3">
-        <v>765600</v>
+        <v>721000</v>
       </c>
       <c r="G72" s="3">
-        <v>729000</v>
+        <v>721700</v>
       </c>
       <c r="H72" s="3">
-        <v>686500</v>
+        <v>666400</v>
       </c>
       <c r="I72" s="3">
+        <v>664500</v>
+      </c>
+      <c r="J72" s="3">
+        <v>608300</v>
+      </c>
+      <c r="K72" s="3">
         <v>640500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>622500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>538800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>479400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>453800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>422600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>366300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>321100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>301800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>293700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>288300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>248800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>232200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>226700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>205700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>186900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>133700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>118200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>88000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>79000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>75700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>68800</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6650,8 +6998,14 @@
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6751,8 +7105,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6852,8 +7212,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6953,98 +7319,104 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>819900</v>
+        <v>839600</v>
       </c>
       <c r="E76" s="3">
-        <v>813500</v>
+        <v>808100</v>
       </c>
       <c r="F76" s="3">
-        <v>786300</v>
+        <v>789100</v>
       </c>
       <c r="G76" s="3">
-        <v>749700</v>
+        <v>789700</v>
       </c>
       <c r="H76" s="3">
-        <v>705600</v>
+        <v>731300</v>
       </c>
       <c r="I76" s="3">
+        <v>726000</v>
+      </c>
+      <c r="J76" s="3">
+        <v>665300</v>
+      </c>
+      <c r="K76" s="3">
         <v>669800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>635800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>551800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>490000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>460800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>424100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>367800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>322500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>303200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>294200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>288300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>276700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>259100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>249300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>228400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>207200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>196300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>180800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>89800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>80800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>77500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>70700</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7054,8 +7426,14 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7155,215 +7533,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2300</v>
       </c>
-      <c r="E81" s="3">
-        <v>11000</v>
-      </c>
       <c r="F81" s="3">
-        <v>16200</v>
+        <v>-2200</v>
       </c>
       <c r="G81" s="3">
-        <v>30300</v>
+        <v>10600</v>
       </c>
       <c r="H81" s="3">
-        <v>32000</v>
+        <v>15100</v>
       </c>
       <c r="I81" s="3">
+        <v>29300</v>
+      </c>
+      <c r="J81" s="3">
+        <v>30100</v>
+      </c>
+      <c r="K81" s="3">
         <v>19700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>41600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>34500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>24900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>19500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>26000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>19800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>15200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>9100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>7900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>7500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>19400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-18800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>19800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>11300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>8400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>9800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>2700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>6300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>18200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>6200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>6600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>5600</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7399,31 +7795,33 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>10100</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7467,41 +7865,47 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC83" s="3">
         <v>2300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>5800</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG83" s="3">
         <v>1700</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7601,8 +8005,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7702,8 +8112,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7803,8 +8219,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7904,8 +8326,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8005,109 +8433,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3900</v>
+        <v>5900</v>
       </c>
       <c r="E89" s="3">
-        <v>46000</v>
+        <v>-300</v>
       </c>
       <c r="F89" s="3">
-        <v>21800</v>
+        <v>3800</v>
       </c>
       <c r="G89" s="3">
-        <v>43700</v>
+        <v>44600</v>
       </c>
       <c r="H89" s="3">
-        <v>32900</v>
+        <v>20200</v>
       </c>
       <c r="I89" s="3">
+        <v>42400</v>
+      </c>
+      <c r="J89" s="3">
+        <v>31000</v>
+      </c>
+      <c r="K89" s="3">
         <v>53700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>33100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>60100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>23200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>44300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>25200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>43300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>13500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>23900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>25400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>2300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>15800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>15100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>21000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>15200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>16800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>12700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>2700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>17600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>26300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>11200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>5000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>14300</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8143,8 +8583,10 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8152,100 +8594,106 @@
         <v>-1500</v>
       </c>
       <c r="E91" s="3">
-        <v>-1400</v>
+        <v>-2300</v>
       </c>
       <c r="F91" s="3">
-        <v>-800</v>
+        <v>-1900</v>
       </c>
       <c r="G91" s="3">
-        <v>-1900</v>
+        <v>-1800</v>
       </c>
       <c r="H91" s="3">
-        <v>-4200</v>
+        <v>-1000</v>
       </c>
       <c r="I91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-4100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-3400</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-2800</v>
       </c>
       <c r="M91" s="3">
         <v>-3800</v>
       </c>
       <c r="N91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="P91" s="3">
         <v>-3600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-2000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-2200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-3000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-4500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-3400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-3100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>4300</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8345,8 +8793,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8446,109 +8900,121 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-15600</v>
+        <v>-1100</v>
       </c>
       <c r="E94" s="3">
+        <v>-336600</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-82900</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="K94" s="3">
+        <v>-47400</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="M94" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="O94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="P94" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>-49200</v>
+      </c>
+      <c r="R94" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="S94" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="T94" s="3">
+        <v>-58800</v>
+      </c>
+      <c r="U94" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="V94" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="W94" s="3">
+        <v>-34300</v>
+      </c>
+      <c r="X94" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-2600</v>
       </c>
-      <c r="F94" s="3">
-        <v>-13300</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-85700</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-47400</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-15100</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-49200</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-16400</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="AB94" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-3500</v>
       </c>
-      <c r="R94" s="3">
-        <v>-58800</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="AD94" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="AE94" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-2100</v>
       </c>
-      <c r="T94" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-34300</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="W94" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="X94" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>-37600</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>-24100</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8584,31 +9050,33 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8685,8 +9153,14 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8786,8 +9260,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8887,8 +9367,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8988,307 +9474,331 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>176800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-800</v>
       </c>
-      <c r="F100" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-3500</v>
-      </c>
       <c r="H100" s="3">
-        <v>-5400</v>
+        <v>-4800</v>
       </c>
       <c r="I100" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-4100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-5000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-4300</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-3500</v>
       </c>
       <c r="R100" s="3">
         <v>-3200</v>
       </c>
       <c r="S100" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="T100" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="U100" s="3">
         <v>16700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-4800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>16900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-2200</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>2100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>32700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>23800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-11900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>3300</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="E101" s="3">
-        <v>-2600</v>
+        <v>200</v>
       </c>
       <c r="F101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H101" s="3">
+        <v>600</v>
+      </c>
+      <c r="I101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="L101" s="3">
+        <v>700</v>
+      </c>
+      <c r="M101" s="3">
         <v>1200</v>
       </c>
-      <c r="G101" s="3">
-        <v>200</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>700</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="U101" s="3">
+        <v>400</v>
+      </c>
+      <c r="V101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="W101" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="X101" s="3">
         <v>1200</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>300</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="Y101" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="S101" s="3">
-        <v>400</v>
-      </c>
-      <c r="T101" s="3">
-        <v>2100</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="V101" s="3">
-        <v>1200</v>
-      </c>
-      <c r="W101" s="3">
-        <v>2600</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>2300</v>
       </c>
       <c r="AA101" s="3">
         <v>100</v>
       </c>
       <c r="AB101" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="AC101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-100</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI101" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK101" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-11300</v>
+        <v>-12800</v>
       </c>
       <c r="E102" s="3">
-        <v>39900</v>
+        <v>-161300</v>
       </c>
       <c r="F102" s="3">
-        <v>4600</v>
+        <v>-10800</v>
       </c>
       <c r="G102" s="3">
-        <v>-45300</v>
+        <v>38700</v>
       </c>
       <c r="H102" s="3">
-        <v>18200</v>
+        <v>4300</v>
       </c>
       <c r="I102" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>17200</v>
+      </c>
+      <c r="K102" s="3">
         <v>3800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>25700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>54100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>7700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>40700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>15400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-11100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>16600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-37000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>17300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>10900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-6300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>18400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>14900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>11000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>12300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>35300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>7200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-18200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>11000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>12500</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
   <si>
     <t>DAVA</t>
   </si>
@@ -656,146 +656,146 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="38" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AI7" s="2" t="s">
         <v>3</v>
       </c>
@@ -805,104 +805,107 @@
       <c r="AK7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AL7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>244900</v>
+      </c>
+      <c r="E8" s="3">
         <v>261400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>245700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>220200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>233800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>229900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>241200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>251800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>269300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>257500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>230000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>209900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>199900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>186900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>165800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>131500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>123200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>112500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>110400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>122700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>117100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>112400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>105200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>97300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>94800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>87700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>79500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>201800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>65200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>62000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>56100</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI8" s="3" t="s">
         <v>3</v>
       </c>
@@ -912,104 +915,107 @@
       <c r="AK8" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL8" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>188500</v>
+      </c>
+      <c r="E9" s="3">
         <v>196200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>179600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>173200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>176600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>163500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>158600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>171800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>174200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>169000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>156400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>141200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>133800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>120100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>109100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>86400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>79900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>73600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>77400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>75200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>106700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>71900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>69600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>64000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>61300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>58000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>51800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>136200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>44400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>42200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>38000</v>
       </c>
-      <c r="AH9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1019,104 +1025,107 @@
       <c r="AK9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E10" s="3">
         <v>65200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>66100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>47000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>57200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>66500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>82600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>80000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>95100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>88500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>73600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>68700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>66000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>66800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>56700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>45100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>43400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>38900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>33000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>47500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>10500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>40500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>35600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>33300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>33500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>29700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>27700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>65600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>20900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>19700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>18100</v>
       </c>
-      <c r="AH10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1126,8 +1135,11 @@
       <c r="AK10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1165,8 +1177,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1272,8 +1285,11 @@
       <c r="AK12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1379,53 +1395,56 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>5900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-9900</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>-2600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>3100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-1400</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1500</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1445,11 +1464,11 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1459,24 +1478,24 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>1600</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH14" s="3">
         <v>500</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1486,83 +1505,86 @@
       <c r="AK14" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E15" s="3">
         <v>9200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10800</v>
       </c>
-      <c r="G15" s="3">
-        <v>-5400</v>
-      </c>
       <c r="H15" s="3">
+        <v>11900</v>
+      </c>
+      <c r="I15" s="3">
         <v>5200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>10600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4700</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3">
         <v>4200</v>
-      </c>
-      <c r="O15" s="3">
-        <v>3900</v>
       </c>
       <c r="P15" s="3">
         <v>3900</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R15" s="3">
+      <c r="Q15" s="3">
+        <v>3900</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3">
         <v>1800</v>
-      </c>
-      <c r="S15" s="3">
-        <v>2100</v>
       </c>
       <c r="T15" s="3">
         <v>2100</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="U15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W15" s="3">
         <v>2200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1900</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z15" s="3">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA15" s="3">
         <v>1300</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1572,8 +1594,8 @@
       <c r="AD15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE15" s="3">
-        <v>0</v>
+      <c r="AE15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF15" s="3">
         <v>0</v>
@@ -1593,8 +1615,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1629,104 +1654,105 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>242800</v>
+      </c>
+      <c r="E17" s="3">
         <v>255100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>226300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>222500</v>
       </c>
-      <c r="G17" s="3">
-        <v>226800</v>
-      </c>
       <c r="H17" s="3">
+        <v>227900</v>
+      </c>
+      <c r="I17" s="3">
         <v>210300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>201500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>214600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>226300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>221700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>196100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>178400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>175200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>156600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>141200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>110400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>106800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>98700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>102000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>104000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>132800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>92500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>93300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>87400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>82900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>77400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>71200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>177300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>57200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>52900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>47800</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1736,104 +1762,107 @@
       <c r="AK17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E18" s="3">
         <v>6300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>19400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2300</v>
       </c>
-      <c r="G18" s="3">
-        <v>7000</v>
-      </c>
       <c r="H18" s="3">
+        <v>5900</v>
+      </c>
+      <c r="I18" s="3">
         <v>19700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>39700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>37200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>43000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>35800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>34000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>31500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>24700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>30300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>24500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>21100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>16400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>8400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>18800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-15600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>19900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>9900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>12000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>8400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>24500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>8000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>9000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>8200</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1843,8 +1872,11 @@
       <c r="AK18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1882,104 +1914,105 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>3200</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>12100</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>-16400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>14800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1989,104 +2022,107 @@
       <c r="AK20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E21" s="3">
         <v>15500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>24200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8500</v>
       </c>
-      <c r="G21" s="3">
-        <v>1600</v>
-      </c>
       <c r="H21" s="3">
+        <v>17800</v>
+      </c>
+      <c r="I21" s="3">
         <v>24800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>34300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>47800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>27500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>60700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>40800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>32500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>24500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>40400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>24500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>18100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>13300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>16600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>8500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>24700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-22900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>29500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>14400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>11600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>12400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>11000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>29000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>7900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>9000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>8900</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2096,34 +2132,37 @@
       <c r="AK21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7900</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1900</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>3500</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2203,104 +2242,107 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E23" s="3">
         <v>5600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>13500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>31700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>37600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>26600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>50600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>41400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>32100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>24200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>31600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>23000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>19300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>12400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>24400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-23500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>23800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>14300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>10100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>12400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>23200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>7900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>7200</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2310,104 +2352,107 @@
       <c r="AK23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E24" s="3">
         <v>2600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-4700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1600</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2417,8 +2462,11 @@
       <c r="AK24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2524,104 +2572,107 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E26" s="3">
         <v>3000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>15100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>29300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>30100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>41600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>34500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>24900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>26000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>15200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>19400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-18800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>19800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>11300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>8400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>9800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>18200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>6200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>5600</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2631,104 +2682,107 @@
       <c r="AK26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E27" s="3">
         <v>3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>29300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>30100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>41600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>34500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>24900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>26000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>15200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>9100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>7500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>19400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-18800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>19800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>11300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>8400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>9800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>6300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>18200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>6200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>6600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>5600</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2738,8 +2792,11 @@
       <c r="AK27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2845,8 +2902,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2952,8 +3012,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3059,8 +3122,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3166,104 +3232,107 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3200</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>-12100</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>16400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-14800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>6800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1000</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI32" s="3" t="s">
         <v>3</v>
       </c>
@@ -3273,104 +3342,107 @@
       <c r="AK32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E33" s="3">
         <v>3000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>29300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>30100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>41600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>34500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>24900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>26000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>15200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>9100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>7500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>19400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-18800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>19800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>11300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>8400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>9800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>18200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>6200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>5600</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3380,8 +3452,11 @@
       <c r="AK33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3487,104 +3562,107 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E35" s="3">
         <v>3000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>29300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>30100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>41600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>34500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>24900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>26000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>15200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>9100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>7500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>19400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-18800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>19800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>11300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>8400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>9800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>18200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>6200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>5600</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,109 +3672,112 @@
       <c r="AK35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AI38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3706,8 +3787,11 @@
       <c r="AK38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AL38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3745,8 +3829,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3784,101 +3869,102 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>75200</v>
+      </c>
+      <c r="E41" s="3">
         <v>70800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>78800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>240000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>253000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>205200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>209300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>246400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>243200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>239300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>207600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>149400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>144700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>104000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>86700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>92300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>98600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>82800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>123600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>116000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>107700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>114100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>96400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>79000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>67400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>55200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>19500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>12200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>32700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>21700</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3891,8 +3977,11 @@
       <c r="AK41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3918,22 +4007,22 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>300</v>
-      </c>
-      <c r="L42" s="3">
-        <v>500</v>
       </c>
       <c r="M42" s="3">
         <v>500</v>
       </c>
       <c r="N42" s="3">
+        <v>500</v>
+      </c>
+      <c r="O42" s="3">
         <v>400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>600</v>
-      </c>
-      <c r="P42" s="3">
-        <v>700</v>
       </c>
       <c r="Q42" s="3">
         <v>700</v>
@@ -3951,7 +4040,7 @@
         <v>700</v>
       </c>
       <c r="V42" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="W42" s="3">
         <v>800</v>
@@ -3959,8 +4048,8 @@
       <c r="X42" s="3">
         <v>800</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
+      <c r="Y42" s="3">
+        <v>800</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>3</v>
@@ -3977,8 +4066,8 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF42" s="3">
         <v>0</v>
@@ -3998,101 +4087,104 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>250700</v>
+      </c>
+      <c r="E43" s="3">
         <v>279000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>244900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>225800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>220100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>233500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>219100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>228100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>231100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>254200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>210400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>199500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>183800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>180400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>148000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>129500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>110300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>112800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>104300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>108700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>107000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>93700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>91600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>84800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>84900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>80800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>68600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>64900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>64400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>59300</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4105,8 +4197,11 @@
       <c r="AK43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4131,8 +4226,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4189,17 +4284,17 @@
         <v>0</v>
       </c>
       <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="3">
         <v>100</v>
       </c>
-      <c r="AE44" s="3">
-        <v>0</v>
-      </c>
       <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
         <v>100</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4212,8 +4307,11 @@
       <c r="AK44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL44" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4238,8 +4336,8 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -4319,101 +4417,104 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>325900</v>
+      </c>
+      <c r="E46" s="3">
         <v>349800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>338200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>465800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>473100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>438800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>442400</v>
-      </c>
-      <c r="J46" s="3">
-        <v>474500</v>
       </c>
       <c r="K46" s="3">
         <v>474500</v>
       </c>
       <c r="L46" s="3">
+        <v>474500</v>
+      </c>
+      <c r="M46" s="3">
         <v>494000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>418500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>349300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>329100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>285100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>235400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>222500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>209600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>196300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>228700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>225500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>215500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>208600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>188000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>163800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>152400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>136000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>88000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>77200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>97100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>81100</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4426,8 +4527,11 @@
       <c r="AK46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4452,51 +4556,51 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>1800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2900</v>
-      </c>
-      <c r="N47" s="3">
-        <v>200</v>
       </c>
       <c r="O47" s="3">
         <v>200</v>
       </c>
       <c r="P47" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q47" s="3">
         <v>300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1500</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4506,14 +4610,14 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>3</v>
+      <c r="AE47" s="3">
+        <v>0</v>
       </c>
       <c r="AF47" s="3" t="s">
         <v>3</v>
@@ -4533,101 +4637,104 @@
       <c r="AK47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>80200</v>
+      </c>
+      <c r="E48" s="3">
         <v>92000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>93400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>94500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>99500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>109300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>115700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>105400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>113900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>108800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>91900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>86200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>87400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>89500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>87500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>62700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>68900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>72400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>77900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>81500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>83000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>65700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>14500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>10800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>11400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>10400</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4640,101 +4747,104 @@
       <c r="AK48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>783400</v>
+      </c>
+      <c r="E49" s="3">
         <v>817600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>813300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>406000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>404200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>397000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>387200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>294300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>321200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>274200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>257700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>251200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>239500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>246300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>233800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>178500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>161300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>167700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>116800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>127400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>124000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>89100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>90200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>93200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>96100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>94900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>92900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>89600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>93700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>41900</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4747,8 +4857,11 @@
       <c r="AK49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4854,8 +4967,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4961,101 +5077,104 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E52" s="3">
         <v>12700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>22000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>22300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>27100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>30300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>24900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>15900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>15600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>13400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>13100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6300</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>3300</v>
       </c>
       <c r="AB52" s="3">
         <v>3300</v>
       </c>
       <c r="AC52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AD52" s="3">
         <v>3200</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>1200</v>
       </c>
       <c r="AE52" s="3">
         <v>1200</v>
       </c>
       <c r="AF52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AG52" s="3">
         <v>1100</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5068,8 +5187,11 @@
       <c r="AK52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5175,101 +5297,104 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1227600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1297000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1281300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1000900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1012100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>974100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>978600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>893300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>929200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>906400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>792900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>709200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>683300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>651500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>582000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>479500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>456400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>456000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>440400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>448000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>439300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>378300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>305800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>275800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>265000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>246400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>195200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>178800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>203400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>134500</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5282,8 +5407,11 @@
       <c r="AK54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5321,8 +5449,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5360,101 +5489,102 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E57" s="3">
         <v>136900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>103900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>107900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>102400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>114600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>126600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>134200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>125300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>110200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>119200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>109000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>97400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>76600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>73900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>78200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>71500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>84200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>98900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>65600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>62500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>58600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>55300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>53900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>52000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>42500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>37200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>32700</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,101 +5597,104 @@
       <c r="AK57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E58" s="3">
         <v>19000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>18300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>17600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>18500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>18100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>15200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>14600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>15200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>16500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>16800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>14300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>14200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>13100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>13600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>14300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>15600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>11700</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
       <c r="AA58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB58" s="3">
         <v>100</v>
       </c>
       <c r="AC58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD58" s="3">
         <v>25500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>30500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>50800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>26800</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5574,101 +5707,104 @@
       <c r="AK58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E59" s="3">
         <v>28200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>44500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>32000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>26900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>33600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>23300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>23400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>10900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>23300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>500</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5681,101 +5817,104 @@
       <c r="AK59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>173100</v>
+      </c>
+      <c r="E60" s="3">
         <v>184100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>194400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>135700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>141900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>140300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>153400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>151100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>171600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>184800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>163700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>143900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>150900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>148800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>127500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>99400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>94900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>100800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>93300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>108200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>119700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>85800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>74400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>65300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>64900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>61500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>92000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>83900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>111300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>60000</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5788,77 +5927,80 @@
       <c r="AK60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>202000</v>
+      </c>
+      <c r="E61" s="3">
         <v>232500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>238000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>54300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>58100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>66200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>69200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>62100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>70800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>67300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>56100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>54600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>56600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>60300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>62200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>40500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>45800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>48000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>51500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>53800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>53900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>40400</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5875,13 +6017,13 @@
         <v>0</v>
       </c>
       <c r="AE61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF61" s="3">
         <v>100</v>
       </c>
       <c r="AG61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH61" s="3">
         <v>0</v>
@@ -5895,101 +6037,104 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="E62" s="3">
         <v>1800</v>
       </c>
       <c r="F62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G62" s="3">
         <v>5000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>19000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>21300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>24400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>17100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>12500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>12900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>9400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>13400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>14100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>14500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3800</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
@@ -6002,8 +6147,11 @@
       <c r="AK62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6109,8 +6257,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6216,8 +6367,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6323,101 +6477,104 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>408000</v>
+      </c>
+      <c r="E66" s="3">
         <v>457400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>473200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>211800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>222400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>242800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>252600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>228100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>259400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>270600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>241200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>219100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>222500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>227300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>214200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>157000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>153200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>161700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>152200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>171300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>180200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>129000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>77400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>68500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>68700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>65600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>105400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>98000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>125900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>63800</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6430,8 +6587,11 @@
       <c r="AK66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6469,8 +6629,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6576,8 +6737,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6683,8 +6847,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6790,8 +6957,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6897,101 +7067,104 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>754500</v>
+      </c>
+      <c r="E72" s="3">
         <v>782700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>725000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>721000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>721700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>666400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>664500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>608300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>640500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>622500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>538800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>479400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>453800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>422600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>366300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>321100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>301800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>293700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>288300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>248800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>232200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>226700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>205700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>186900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>133700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>118200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>88000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>79000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>75700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>68800</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7004,8 +7177,11 @@
       <c r="AK72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7111,8 +7287,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7218,8 +7397,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7325,101 +7507,104 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>819700</v>
+      </c>
+      <c r="E76" s="3">
         <v>839600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>808100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>789100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>789700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>731300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>726000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>665300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>669800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>635800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>551800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>490000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>460800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>424100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>367800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>322500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>303200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>294200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>288300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>276700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>259100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>249300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>228400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>207200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>196300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>180800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>89800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>80800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>77500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>70700</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7432,8 +7617,11 @@
       <c r="AK76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7539,109 +7727,112 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AI80" s="2" t="s">
         <v>3</v>
       </c>
@@ -7651,104 +7842,107 @@
       <c r="AK80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AL80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E81" s="3">
         <v>3000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>29300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>30100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>41600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>34500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>24900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>26000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>15200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>9100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>7500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>19400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-18800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>19800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>11300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>8400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>9800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>18200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>6200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>5600</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI81" s="3" t="s">
         <v>3</v>
       </c>
@@ -7758,8 +7952,11 @@
       <c r="AK81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7797,35 +7994,36 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E83" s="3">
         <v>7300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6200</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -7871,30 +8069,30 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
+      <c r="AA83" s="3">
+        <v>0</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD83" s="3">
         <v>2300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5800</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH83" s="3">
         <v>1700</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7904,8 +8102,11 @@
       <c r="AK83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8011,8 +8212,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8118,8 +8322,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8225,8 +8432,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8332,8 +8542,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8439,104 +8652,107 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E89" s="3">
         <v>5900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>44600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>20200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>42400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>31000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>53700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>33100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>60100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>23200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>44300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>25200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>43300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>13500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>23900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>25400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>15800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>15100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>21000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>15200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>16800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>12700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>17600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>26300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>11200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>5000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>14300</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
@@ -8546,8 +8762,11 @@
       <c r="AK89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8585,104 +8804,105 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>4300</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI91" s="3" t="s">
         <v>3</v>
       </c>
@@ -8692,8 +8912,11 @@
       <c r="AK91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8799,8 +9022,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8906,104 +9132,107 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-336600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-82900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-47400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-49200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-16400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-58800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-34300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-37600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
@@ -9013,8 +9242,11 @@
       <c r="AK94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9052,8 +9284,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9078,8 +9311,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -9159,8 +9392,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9266,8 +9502,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9373,8 +9612,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9480,104 +9722,107 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-16800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>176800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>16700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>16900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>2100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>32700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>23800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-11900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>3300</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI100" s="3" t="s">
         <v>3</v>
       </c>
@@ -9587,103 +9832,106 @@
       <c r="AK100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E101" s="3">
         <v>1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-1100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1200</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-4100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>2300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>200</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>-100</v>
       </c>
       <c r="AG101" s="3">
         <v>-100</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>3</v>
+      <c r="AH101" s="3">
+        <v>-100</v>
       </c>
       <c r="AI101" s="3" t="s">
         <v>3</v>
@@ -9694,104 +9942,107 @@
       <c r="AK101" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL101" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-161300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-10800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>38700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-43800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>17200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>25700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>54100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>40700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-11100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>16600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-37000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>17300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>10900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>18400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>14900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>11000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>12300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>35300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>7200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-18200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>11000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>12500</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
@@ -9799,6 +10050,9 @@
         <v>3</v>
       </c>
       <c r="AK102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="92">
   <si>
     <t>DAVA</t>
   </si>
@@ -656,149 +656,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="38" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="39" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
@@ -808,107 +809,110 @@
       <c r="AL7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AM7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>251700</v>
+      </c>
+      <c r="E8" s="3">
         <v>244900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>261400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>245700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>220200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>233800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>229900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>241200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>251800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>269300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>257500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>230000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>209900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>199900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>186900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>165800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>131500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>123200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>112500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>110400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>122700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>117100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>112400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>105200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>97300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>94800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>87700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>79500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>201800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>65200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>62000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>56100</v>
       </c>
-      <c r="AI8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ8" s="3" t="s">
         <v>3</v>
       </c>
@@ -918,107 +922,110 @@
       <c r="AL8" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM8" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>182500</v>
+      </c>
+      <c r="E9" s="3">
         <v>188500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>196200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>179600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>173200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>176600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>163500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>158600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>171800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>174200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>169000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>156400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>141200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>133800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>120100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>109100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>86400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>79900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>73600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>77400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>75200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>106700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>71900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>69600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>64000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>61300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>58000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>51800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>136200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>44400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>42200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>38000</v>
       </c>
-      <c r="AI9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1028,107 +1035,110 @@
       <c r="AL9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E10" s="3">
         <v>56400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>65200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>66100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>47000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>57200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>66500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>82600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>80000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>95100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>88500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>73600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>68700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>66000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>66800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>56700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>45100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>43400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>38900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>33000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>47500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>10500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>40500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>35600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>33300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>33500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>29700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>27700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>65600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>20900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>19700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>18100</v>
       </c>
-      <c r="AI10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1138,8 +1148,11 @@
       <c r="AL10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1178,8 +1191,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1288,8 +1302,11 @@
       <c r="AL12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1398,8 +1415,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1409,45 +1429,45 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>5900</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>-2600</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>3100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-1400</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1500</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1467,11 +1487,11 @@
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1481,24 +1501,24 @@
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>1600</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI14" s="3">
         <v>500</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1508,86 +1528,89 @@
       <c r="AL14" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E15" s="3">
         <v>15100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>10800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>10600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4700</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3">
         <v>4200</v>
-      </c>
-      <c r="P15" s="3">
-        <v>3900</v>
       </c>
       <c r="Q15" s="3">
         <v>3900</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="R15" s="3">
+        <v>3900</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T15" s="3">
         <v>1800</v>
-      </c>
-      <c r="T15" s="3">
-        <v>2100</v>
       </c>
       <c r="U15" s="3">
         <v>2100</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="V15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X15" s="3">
         <v>2200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1900</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB15" s="3">
         <v>1300</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1597,8 +1620,8 @@
       <c r="AE15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF15" s="3">
-        <v>0</v>
+      <c r="AF15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
@@ -1618,8 +1641,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1655,107 +1681,108 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>230500</v>
+      </c>
+      <c r="E17" s="3">
         <v>242800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>255100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>226300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>222500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>227900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>210300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>201500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>214600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>226300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>221700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>196100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>178400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>175200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>156600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>141200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>110400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>106800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>98700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>102000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>104000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>132800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>92500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>93300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>87400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>82900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>77400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>71200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>177300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>57200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>52900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>47800</v>
       </c>
-      <c r="AI17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1765,107 +1792,110 @@
       <c r="AL17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E18" s="3">
         <v>2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>19400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>19700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>39700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>37200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>43000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>35800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>34000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>31500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>24700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>30300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>24500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>21100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>16400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>8400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>18800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-15600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>19900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>9900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>12000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>8400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>24500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>8000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>9000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>8200</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1875,8 +1905,11 @@
       <c r="AL18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1915,8 +1948,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1926,96 +1960,96 @@
       <c r="E20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
         <v>3200</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>12100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>-16400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>5600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-6800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ20" s="3" t="s">
         <v>3</v>
       </c>
@@ -2025,107 +2059,110 @@
       <c r="AL20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E21" s="3">
         <v>17200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>15500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>24200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>24800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>34300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>47800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>27500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>60700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>40800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>32500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>24500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>40400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>24500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>18100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>13300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>16600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>24700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-22900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>29500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>14400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>12400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>11000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>29000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>7900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>9000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>8900</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2135,37 +2172,40 @@
       <c r="AL21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7900</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
         <v>3500</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2245,107 +2285,110 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E23" s="3">
         <v>3100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>13500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>21100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>31700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>37600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>26600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>50600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>41400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>32100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>24200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>31600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>23000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>19300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>12400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>10300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>24400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-23500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>23800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>14300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>10100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>12400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>23200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>7900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>8400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>7200</v>
       </c>
-      <c r="AI23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2355,107 +2398,110 @@
       <c r="AL23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-5400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1600</v>
       </c>
-      <c r="AI24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2465,8 +2511,11 @@
       <c r="AL24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2575,107 +2624,110 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E26" s="3">
         <v>8600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>29300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>30100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>41600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>34500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>24900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>19500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>26000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>15200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>9100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>7500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>19400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>19800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>11300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>8400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>9800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>6300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>18200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>6600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>5600</v>
       </c>
-      <c r="AI26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2685,107 +2737,110 @@
       <c r="AL26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E27" s="3">
         <v>8600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>15100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>29300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>30100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>41600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>34500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>24900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>19500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>26000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>15200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>9100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>7900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>7500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>19400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>19800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>11300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>8400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>9800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>6300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>18200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>6200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>6600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>5600</v>
       </c>
-      <c r="AI27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2795,8 +2850,11 @@
       <c r="AL27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2905,8 +2963,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3015,8 +3076,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3125,8 +3189,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3235,8 +3302,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3246,96 +3316,96 @@
       <c r="E32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
         <v>-3200</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-12100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>16400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-5600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>7900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>6800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1000</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ32" s="3" t="s">
         <v>3</v>
       </c>
@@ -3345,107 +3415,110 @@
       <c r="AL32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E33" s="3">
         <v>8600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>15100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>29300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>30100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>41600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>34500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>24900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>19500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>26000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>15200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>9100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>7900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>7500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>19400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>19800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>11300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>8400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>9800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>6300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>18200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>6600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>5600</v>
       </c>
-      <c r="AI33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3455,8 +3528,11 @@
       <c r="AL33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3565,107 +3641,110 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E35" s="3">
         <v>8600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>15100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>29300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>30100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>41600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>34500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>24900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>19500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>26000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>15200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>9100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>7900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>7500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>19400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>19800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>11300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>8400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>9800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>6300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>18200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>6600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>5600</v>
       </c>
-      <c r="AI35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3675,112 +3754,115 @@
       <c r="AL35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3790,8 +3872,11 @@
       <c r="AL38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AM38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3830,8 +3915,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3870,104 +3956,105 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>88200</v>
+      </c>
+      <c r="E41" s="3">
         <v>75200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>70800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>78800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>240000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>253000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>205200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>209300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>246400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>243200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>239300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>207600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>149400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>144700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>104000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>86700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>92300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>98600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>82800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>123600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>116000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>107700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>114100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>96400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>79000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>67400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>55200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>19500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>12200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>32700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>21700</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3980,8 +4067,11 @@
       <c r="AL41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4010,22 +4100,22 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>300</v>
-      </c>
-      <c r="M42" s="3">
-        <v>500</v>
       </c>
       <c r="N42" s="3">
         <v>500</v>
       </c>
       <c r="O42" s="3">
+        <v>500</v>
+      </c>
+      <c r="P42" s="3">
         <v>400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>600</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>700</v>
       </c>
       <c r="R42" s="3">
         <v>700</v>
@@ -4043,7 +4133,7 @@
         <v>700</v>
       </c>
       <c r="W42" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="X42" s="3">
         <v>800</v>
@@ -4051,8 +4141,8 @@
       <c r="Y42" s="3">
         <v>800</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
+      <c r="Z42" s="3">
+        <v>800</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>3</v>
@@ -4069,8 +4159,8 @@
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF42" s="3">
-        <v>0</v>
+      <c r="AF42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG42" s="3">
         <v>0</v>
@@ -4090,104 +4180,107 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>262700</v>
+      </c>
+      <c r="E43" s="3">
         <v>250700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>279000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>244900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>225800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>220100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>233500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>219100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>228100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>231100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>254200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>210400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>199500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>183800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>180400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>148000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>129500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>110300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>112800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>104300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>108700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>107000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>93700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>91600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>84800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>84900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>80800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>68600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>64900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>64400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>59300</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4200,8 +4293,11 @@
       <c r="AL43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4229,8 +4325,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4287,17 +4383,17 @@
         <v>0</v>
       </c>
       <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="3">
         <v>100</v>
       </c>
-      <c r="AF44" s="3">
-        <v>0</v>
-      </c>
       <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
         <v>100</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4310,8 +4406,11 @@
       <c r="AL44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM44" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4339,8 +4438,8 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -4420,104 +4519,107 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>350900</v>
+      </c>
+      <c r="E46" s="3">
         <v>325900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>349800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>338200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>465800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>473100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>438800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>442400</v>
-      </c>
-      <c r="K46" s="3">
-        <v>474500</v>
       </c>
       <c r="L46" s="3">
         <v>474500</v>
       </c>
       <c r="M46" s="3">
+        <v>474500</v>
+      </c>
+      <c r="N46" s="3">
         <v>494000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>418500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>349300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>329100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>285100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>235400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>222500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>209600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>196300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>228700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>225500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>215500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>208600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>188000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>163800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>152400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>136000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>88000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>77200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>97100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>81100</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,8 +4632,11 @@
       <c r="AL46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4559,51 +4664,51 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>1800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2900</v>
-      </c>
-      <c r="O47" s="3">
-        <v>200</v>
       </c>
       <c r="P47" s="3">
         <v>200</v>
       </c>
       <c r="Q47" s="3">
+        <v>200</v>
+      </c>
+      <c r="R47" s="3">
         <v>300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1500</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4613,14 +4718,14 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD47" s="3">
-        <v>0</v>
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>3</v>
+      <c r="AF47" s="3">
+        <v>0</v>
       </c>
       <c r="AG47" s="3" t="s">
         <v>3</v>
@@ -4640,104 +4745,107 @@
       <c r="AL47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E48" s="3">
         <v>80200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>92000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>93400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>94500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>99500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>109300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>115700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>105400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>113900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>108800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>91900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>86200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>87400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>89500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>87500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>62700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>68900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>72400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>77900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>81500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>83000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>65700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>14500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>10800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>11400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>10400</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4750,104 +4858,107 @@
       <c r="AL48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>776400</v>
+      </c>
+      <c r="E49" s="3">
         <v>783400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>817600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>813300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>406000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>404200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>397000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>387200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>294300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>321200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>274200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>257700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>251200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>239500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>246300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>233800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>178500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>161300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>167700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>116800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>127400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>124000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>89100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>90200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>93200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>96100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>94900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>92900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>89600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>93700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>41900</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4860,8 +4971,11 @@
       <c r="AL49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4970,8 +5084,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5080,104 +5197,107 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E52" s="3">
         <v>11300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>22000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>22300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>27100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>30300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>24900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>15200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>15900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>18700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>15600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>13400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>13100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6300</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>3300</v>
       </c>
       <c r="AC52" s="3">
         <v>3300</v>
       </c>
       <c r="AD52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AE52" s="3">
         <v>3200</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>1200</v>
       </c>
       <c r="AF52" s="3">
         <v>1200</v>
       </c>
       <c r="AG52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AH52" s="3">
         <v>1100</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5190,8 +5310,11 @@
       <c r="AL52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5300,104 +5423,107 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1242600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1227600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1297000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1281300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1000900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1012100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>974100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>978600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>893300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>929200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>906400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>792900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>709200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>683300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>651500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>582000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>479500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>456400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>456000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>440400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>448000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>439300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>378300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>305800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>275800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>265000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>246400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>195200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>178800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>203400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>134500</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5410,8 +5536,11 @@
       <c r="AL54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5450,8 +5579,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5490,104 +5620,105 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>130700</v>
+      </c>
+      <c r="E57" s="3">
         <v>133000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>136900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>103900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>107900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>102400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>114600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>126600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>134200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>125300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>110200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>119200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>109000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>97400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>76600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>73900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>78200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>71500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>84200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>98900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>65600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>62500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>58600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>55300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>53900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>52000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>42500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>37200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>32700</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5600,104 +5731,107 @@
       <c r="AL57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E58" s="3">
         <v>18100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>19000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>17900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>18500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>18100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>17000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>15200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>14600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>15200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>16500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>16800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>14300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>14200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>13100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>13600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>14300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>15600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>11700</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
       <c r="AA58" s="3">
         <v>0</v>
       </c>
       <c r="AB58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="3">
         <v>100</v>
       </c>
       <c r="AD58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE58" s="3">
         <v>25500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>30500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>50800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>26800</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5710,104 +5844,107 @@
       <c r="AL58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E59" s="3">
         <v>21900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>28200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>44500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>32000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>19300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>26900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>33600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>23300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>23400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>11900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>7600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>14400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>10900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>23300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>500</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5820,104 +5957,107 @@
       <c r="AL59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>161000</v>
+      </c>
+      <c r="E60" s="3">
         <v>173100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>184100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>194400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>135700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>141900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>140300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>153400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>151100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>171600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>184800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>163700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>143900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>150900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>148800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>127500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>99400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>94900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>100800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>93300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>108200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>119700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>85800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>74400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>65300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>64900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>61500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>92000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>83900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>111300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>60000</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5930,80 +6070,83 @@
       <c r="AL60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>221800</v>
+      </c>
+      <c r="E61" s="3">
         <v>202000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>232500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>238000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>54300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>58100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>66200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>69200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>62100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>70800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>67300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>56100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>54600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>56600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>60300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>62200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>40500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>45800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>48000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>51500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>53800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>53900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>40400</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -6020,13 +6163,13 @@
         <v>0</v>
       </c>
       <c r="AF61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG61" s="3">
         <v>100</v>
       </c>
       <c r="AH61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI61" s="3">
         <v>0</v>
@@ -6040,104 +6183,107 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1900</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1800</v>
       </c>
       <c r="F62" s="3">
         <v>1800</v>
       </c>
       <c r="G62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H62" s="3">
         <v>5000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>19000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>17000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>21300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>15000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>24400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>17100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>12500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>12900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>9400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>13400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>14100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>14500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3800</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
@@ -6150,8 +6296,11 @@
       <c r="AL62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6260,8 +6409,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6370,8 +6522,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6480,104 +6635,107 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>408500</v>
+      </c>
+      <c r="E66" s="3">
         <v>408000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>457400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>473200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>211800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>222400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>242800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>252600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>228100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>259400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>270600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>241200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>219100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>222500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>227300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>214200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>157000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>153200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>161700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>152200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>171300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>180200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>129000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>77400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>68500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>68700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>65600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>105400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>98000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>125900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>63800</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6590,8 +6748,11 @@
       <c r="AL66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6630,8 +6791,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6740,8 +6902,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6850,8 +7015,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6960,8 +7128,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7070,104 +7241,107 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>800000</v>
+      </c>
+      <c r="E72" s="3">
         <v>754500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>782700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>725000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>721000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>721700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>666400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>664500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>608300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>640500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>622500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>538800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>479400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>453800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>422600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>366300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>321100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>301800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>293700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>288300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>248800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>232200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>226700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>205700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>186900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>133700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>118200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>88000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>79000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>75700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>68800</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7180,8 +7354,11 @@
       <c r="AL72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7290,8 +7467,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7400,8 +7580,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7510,104 +7693,107 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>834100</v>
+      </c>
+      <c r="E76" s="3">
         <v>819700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>839600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>808100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>789100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>789700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>731300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>726000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>665300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>669800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>635800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>551800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>490000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>460800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>424100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>367800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>322500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>303200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>294200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>288300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>276700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>259100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>249300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>228400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>207200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>196300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>180800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>89800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>80800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>77500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>70700</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7620,8 +7806,11 @@
       <c r="AL76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7730,112 +7919,115 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
@@ -7845,107 +8037,110 @@
       <c r="AL80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AM80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E81" s="3">
         <v>8600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>15100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>29300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>30100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>41600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>34500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>24900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>19500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>26000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>15200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>9100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>7900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>7500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>19400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>19800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>11300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>8400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>9800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>6300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>18200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>6600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>5600</v>
       </c>
-      <c r="AI81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ81" s="3" t="s">
         <v>3</v>
       </c>
@@ -7955,8 +8150,11 @@
       <c r="AL81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7995,38 +8193,39 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E83" s="3">
         <v>11900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6200</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -8072,30 +8271,30 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
+      <c r="AB83" s="3">
+        <v>0</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE83" s="3">
         <v>2300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5800</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI83" s="3">
         <v>1700</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ83" s="3" t="s">
         <v>3</v>
       </c>
@@ -8105,8 +8304,11 @@
       <c r="AL83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8215,8 +8417,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8325,8 +8530,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8435,8 +8643,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8545,8 +8756,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8655,107 +8869,110 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E89" s="3">
         <v>40100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>44600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>20200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>42400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>31000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>53700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>33100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>60100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>23200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>44300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>25200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>43300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>13500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>23900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>25400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>15800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>15100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>21000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>15200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>16800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>12700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>17600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>26300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>11200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>5000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>14300</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
@@ -8765,8 +8982,11 @@
       <c r="AL89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8805,107 +9025,108 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>4300</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ91" s="3" t="s">
         <v>3</v>
       </c>
@@ -8915,8 +9136,11 @@
       <c r="AL91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9025,8 +9249,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9135,107 +9362,110 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-336600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-82900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-47400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-49200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-16400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-58800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-34300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-37600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ94" s="3" t="s">
         <v>3</v>
       </c>
@@ -9245,8 +9475,11 @@
       <c r="AL94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9285,8 +9518,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9314,8 +9548,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9395,8 +9629,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9505,8 +9742,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9615,8 +9855,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9725,107 +9968,110 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-24300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-16800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>176800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>16700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>16900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>2100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>32700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>23800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-11900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>3300</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ100" s="3" t="s">
         <v>3</v>
       </c>
@@ -9835,106 +10081,109 @@
       <c r="AL100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1200</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>2600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>200</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>-100</v>
       </c>
       <c r="AH101" s="3">
         <v>-100</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>3</v>
+      <c r="AI101" s="3">
+        <v>-100</v>
       </c>
       <c r="AJ101" s="3" t="s">
         <v>3</v>
@@ -9945,107 +10194,110 @@
       <c r="AL101" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM101" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E102" s="3">
         <v>9100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-161300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-10800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>38700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-43800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>17200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>25700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>54100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>40700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>16600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-37000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>17300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>10900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>18400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>14900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>11000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>12300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>35300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>7200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-18200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>11000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>12500</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
@@ -10053,6 +10305,9 @@
         <v>3</v>
       </c>
       <c r="AL102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="92">
   <si>
     <t>DAVA</t>
   </si>
@@ -820,8 +820,8 @@
       <c r="D8" s="3">
         <v>251700</v>
       </c>
-      <c r="E8" s="3">
-        <v>244900</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F8" s="3">
         <v>261400</v>
@@ -933,8 +933,8 @@
       <c r="D9" s="3">
         <v>182500</v>
       </c>
-      <c r="E9" s="3">
-        <v>188500</v>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F9" s="3">
         <v>196200</v>
@@ -1046,8 +1046,8 @@
       <c r="D10" s="3">
         <v>69200</v>
       </c>
-      <c r="E10" s="3">
-        <v>56400</v>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F10" s="3">
         <v>65200</v>
@@ -1438,8 +1438,8 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>-9900</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -1537,10 +1537,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>6200</v>
+        <v>12900</v>
       </c>
       <c r="E15" s="3">
-        <v>15100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>9200</v>
@@ -1552,7 +1552,7 @@
         <v>10800</v>
       </c>
       <c r="I15" s="3">
-        <v>11900</v>
+        <v>-5400</v>
       </c>
       <c r="J15" s="3">
         <v>5200</v>
@@ -1690,8 +1690,8 @@
       <c r="D17" s="3">
         <v>230500</v>
       </c>
-      <c r="E17" s="3">
-        <v>242800</v>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F17" s="3">
         <v>255100</v>
@@ -1703,7 +1703,7 @@
         <v>222500</v>
       </c>
       <c r="I17" s="3">
-        <v>227900</v>
+        <v>226800</v>
       </c>
       <c r="J17" s="3">
         <v>210300</v>
@@ -1803,8 +1803,8 @@
       <c r="D18" s="3">
         <v>21300</v>
       </c>
-      <c r="E18" s="3">
-        <v>2100</v>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F18" s="3">
         <v>6300</v>
@@ -1816,7 +1816,7 @@
         <v>-2300</v>
       </c>
       <c r="I18" s="3">
-        <v>5900</v>
+        <v>7000</v>
       </c>
       <c r="J18" s="3">
         <v>19700</v>
@@ -2068,10 +2068,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>27500</v>
+        <v>34100</v>
       </c>
       <c r="E21" s="3">
-        <v>17200</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
         <v>15500</v>
@@ -2083,7 +2083,7 @@
         <v>8500</v>
       </c>
       <c r="I21" s="3">
-        <v>17800</v>
+        <v>1600</v>
       </c>
       <c r="J21" s="3">
         <v>24800</v>
@@ -2195,8 +2195,8 @@
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+      <c r="I22" s="3">
+        <v>1900</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
@@ -2296,8 +2296,8 @@
       <c r="D23" s="3">
         <v>17600</v>
       </c>
-      <c r="E23" s="3">
-        <v>3100</v>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F23" s="3">
         <v>5600</v>
@@ -2409,8 +2409,8 @@
       <c r="D24" s="3">
         <v>3400</v>
       </c>
-      <c r="E24" s="3">
-        <v>-5400</v>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F24" s="3">
         <v>2600</v>
@@ -2635,8 +2635,8 @@
       <c r="D26" s="3">
         <v>14100</v>
       </c>
-      <c r="E26" s="3">
-        <v>8600</v>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F26" s="3">
         <v>3000</v>
@@ -2748,8 +2748,8 @@
       <c r="D27" s="3">
         <v>14100</v>
       </c>
-      <c r="E27" s="3">
-        <v>8600</v>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F27" s="3">
         <v>3000</v>
@@ -3426,8 +3426,8 @@
       <c r="D33" s="3">
         <v>14100</v>
       </c>
-      <c r="E33" s="3">
-        <v>8600</v>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F33" s="3">
         <v>3000</v>
@@ -3652,8 +3652,8 @@
       <c r="D35" s="3">
         <v>14100</v>
       </c>
-      <c r="E35" s="3">
-        <v>8600</v>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F35" s="3">
         <v>3000</v>
@@ -3965,8 +3965,8 @@
       <c r="D41" s="3">
         <v>88200</v>
       </c>
-      <c r="E41" s="3">
-        <v>75200</v>
+      <c r="E41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F41" s="3">
         <v>70800</v>
@@ -4191,8 +4191,8 @@
       <c r="D43" s="3">
         <v>262700</v>
       </c>
-      <c r="E43" s="3">
-        <v>250700</v>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F43" s="3">
         <v>279000</v>
@@ -4530,8 +4530,8 @@
       <c r="D46" s="3">
         <v>350900</v>
       </c>
-      <c r="E46" s="3">
-        <v>325900</v>
+      <c r="E46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F46" s="3">
         <v>349800</v>
@@ -4756,8 +4756,8 @@
       <c r="D48" s="3">
         <v>76600</v>
       </c>
-      <c r="E48" s="3">
-        <v>80200</v>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F48" s="3">
         <v>92000</v>
@@ -4869,8 +4869,8 @@
       <c r="D49" s="3">
         <v>776400</v>
       </c>
-      <c r="E49" s="3">
-        <v>783400</v>
+      <c r="E49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F49" s="3">
         <v>817600</v>
@@ -5208,8 +5208,8 @@
       <c r="D52" s="3">
         <v>11800</v>
       </c>
-      <c r="E52" s="3">
-        <v>11300</v>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>12700</v>
@@ -5434,8 +5434,8 @@
       <c r="D54" s="3">
         <v>1242600</v>
       </c>
-      <c r="E54" s="3">
-        <v>1227600</v>
+      <c r="E54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F54" s="3">
         <v>1297000</v>
@@ -5629,8 +5629,8 @@
       <c r="D57" s="3">
         <v>130700</v>
       </c>
-      <c r="E57" s="3">
-        <v>133000</v>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F57" s="3">
         <v>136900</v>
@@ -5742,8 +5742,8 @@
       <c r="D58" s="3">
         <v>18000</v>
       </c>
-      <c r="E58" s="3">
-        <v>18100</v>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F58" s="3">
         <v>19000</v>
@@ -5855,8 +5855,8 @@
       <c r="D59" s="3">
         <v>12300</v>
       </c>
-      <c r="E59" s="3">
-        <v>21900</v>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F59" s="3">
         <v>28200</v>
@@ -5968,8 +5968,8 @@
       <c r="D60" s="3">
         <v>161000</v>
       </c>
-      <c r="E60" s="3">
-        <v>173100</v>
+      <c r="E60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F60" s="3">
         <v>184100</v>
@@ -6082,7 +6082,7 @@
         <v>221800</v>
       </c>
       <c r="E61" s="3">
-        <v>202000</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>232500</v>
@@ -6194,8 +6194,8 @@
       <c r="D62" s="3">
         <v>900</v>
       </c>
-      <c r="E62" s="3">
-        <v>1900</v>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F62" s="3">
         <v>1800</v>
@@ -6646,8 +6646,8 @@
       <c r="D66" s="3">
         <v>408500</v>
       </c>
-      <c r="E66" s="3">
-        <v>408000</v>
+      <c r="E66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F66" s="3">
         <v>457400</v>
@@ -7252,8 +7252,8 @@
       <c r="D72" s="3">
         <v>800000</v>
       </c>
-      <c r="E72" s="3">
-        <v>754500</v>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F72" s="3">
         <v>782700</v>
@@ -7704,8 +7704,8 @@
       <c r="D76" s="3">
         <v>834100</v>
       </c>
-      <c r="E76" s="3">
-        <v>819700</v>
+      <c r="E76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F76" s="3">
         <v>839600</v>
@@ -8048,8 +8048,8 @@
       <c r="D81" s="3">
         <v>14100</v>
       </c>
-      <c r="E81" s="3">
-        <v>8600</v>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F81" s="3">
         <v>3000</v>
@@ -8880,8 +8880,8 @@
       <c r="D89" s="3">
         <v>24100</v>
       </c>
-      <c r="E89" s="3">
-        <v>40100</v>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F89" s="3">
         <v>5900</v>
@@ -9034,8 +9034,8 @@
       <c r="D91" s="3">
         <v>-1800</v>
       </c>
-      <c r="E91" s="3">
-        <v>-500</v>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
         <v>-1500</v>
@@ -9373,8 +9373,8 @@
       <c r="D94" s="3">
         <v>-2100</v>
       </c>
-      <c r="E94" s="3">
-        <v>-7400</v>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F94" s="3">
         <v>-1100</v>
@@ -9979,8 +9979,8 @@
       <c r="D100" s="3">
         <v>-11200</v>
       </c>
-      <c r="E100" s="3">
-        <v>-24300</v>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
         <v>-16800</v>
@@ -10206,7 +10206,7 @@
         <v>10600</v>
       </c>
       <c r="E102" s="3">
-        <v>9100</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
         <v>-12800</v>

--- a/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="92">
   <si>
     <t>DAVA</t>
   </si>
@@ -656,516 +656,540 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="40" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="42" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
-        <v>45382</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AK7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AM7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AN7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AO7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>247800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>239500</v>
+      </c>
+      <c r="F8" s="3">
         <v>255900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>251700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
+        <v>244900</v>
+      </c>
+      <c r="I8" s="3">
         <v>261400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="J8" s="3">
         <v>245700</v>
       </c>
-      <c r="H8" s="3">
-        <v>220200</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>233800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>229900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>229900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>241200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>251800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>269300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>257500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>230000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>209900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>199900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>186900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>165800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>131500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>123200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>112500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>110400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>122700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>117100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>112400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>105200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>97300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>94800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>87700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>79500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>201800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>65200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>62000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>56100</v>
       </c>
-      <c r="AK8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN8" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP8" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>197200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>188900</v>
+      </c>
+      <c r="F9" s="3">
         <v>186200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>182500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
+        <v>188500</v>
+      </c>
+      <c r="I9" s="3">
         <v>196200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="J9" s="3">
         <v>179600</v>
       </c>
-      <c r="H9" s="3">
-        <v>173200</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>176600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>163500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>163500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>158600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>171800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>174200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>169000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>156400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>141200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>133800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>120100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>109100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>86400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>79900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>73600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>77400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>75200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>106700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>71900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>69600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>64000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>61300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>58000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>51800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>136200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>44400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>42200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>38000</v>
       </c>
-      <c r="AK9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>50600</v>
+      </c>
+      <c r="F10" s="3">
         <v>69600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>69200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
+        <v>56400</v>
+      </c>
+      <c r="I10" s="3">
         <v>65200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="J10" s="3">
         <v>66100</v>
       </c>
-      <c r="H10" s="3">
-        <v>47000</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>57200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>66500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>66500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>82600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>80000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>95100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>88500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>73600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>68700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>66000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>66800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>56700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>45100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>43400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>38900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>33000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>47500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>10500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>40500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>35600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>33300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>33500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>29700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>27700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>65600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>20900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>19700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>18100</v>
       </c>
-      <c r="AK10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1230,10 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1322,8 +1348,14 @@
       <c r="AN12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1438,65 +1470,71 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>5900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-9900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>-2600</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>3100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>1700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>1500</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
@@ -1513,147 +1551,153 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>1600</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ14" s="3">
+      <c r="AJ14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL14" s="3">
         <v>500</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN14" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP14" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F15" s="3">
         <v>10400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>12900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
+        <v>8500</v>
+      </c>
+      <c r="I15" s="3">
         <v>9200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="J15" s="3">
         <v>8000</v>
       </c>
-      <c r="H15" s="3">
-        <v>10800</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>-5400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>5200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>5200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>6700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>10600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>5000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>4700</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3">
         <v>4200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>3900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>3900</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W15" s="3">
         <v>1800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>2100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>2100</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA15" s="3">
         <v>2200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>2000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>1900</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE15" s="3">
         <v>1300</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>0</v>
+      <c r="AH15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AJ15" s="3">
         <v>0</v>
@@ -1670,8 +1714,14 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1709,240 +1759,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>251800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>243400</v>
+      </c>
+      <c r="F17" s="3">
         <v>236400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>230500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
+        <v>242800</v>
+      </c>
+      <c r="I17" s="3">
         <v>255100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="J17" s="3">
         <v>226300</v>
       </c>
-      <c r="H17" s="3">
-        <v>222500</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>226800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>210300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>210300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>201500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>214600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>226300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>221700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>196100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>178400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>175200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>156600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>141200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>110400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>106800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>98700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>102000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>104000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>132800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>92500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>93300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>87400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>82900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>77400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>71200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>177300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>57200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>52900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>47800</v>
       </c>
-      <c r="AK17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F18" s="3">
         <v>19500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>21300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I18" s="3">
         <v>6300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="J18" s="3">
         <v>19400</v>
       </c>
-      <c r="H18" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>7000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>19700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>19700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>39700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>37200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>43000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>35800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>34000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>31500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>24700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>30300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>24500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>21100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>16400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>13800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>8400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>18800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-15600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>19900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>11900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>9900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>12000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>10300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>8400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>24500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>8000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>8200</v>
       </c>
-      <c r="AK18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1983,278 +2047,292 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>5300</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>3200</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>12100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
         <v>-16400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>14800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>7500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-1500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-4000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-3400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>5600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-7900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>3900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>2500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-6800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F21" s="3">
         <v>24700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>34100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
+        <v>10600</v>
+      </c>
+      <c r="I21" s="3">
         <v>15500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="J21" s="3">
         <v>24200</v>
       </c>
-      <c r="H21" s="3">
-        <v>8500</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>24800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>24800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>34300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>47800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>27500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>60700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>40800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>32500</v>
-      </c>
-      <c r="R21" s="3">
-        <v>24500</v>
-      </c>
-      <c r="S21" s="3">
-        <v>40400</v>
       </c>
       <c r="T21" s="3">
         <v>24500</v>
       </c>
       <c r="U21" s="3">
+        <v>40400</v>
+      </c>
+      <c r="V21" s="3">
+        <v>24500</v>
+      </c>
+      <c r="W21" s="3">
         <v>18100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>13300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>16600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>8500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>24700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-22900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>29500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>14400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>11600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>12400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>4600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>11000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>29000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>7900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>8900</v>
       </c>
-      <c r="AK21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E22" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F22" s="3">
         <v>11200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>3700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="J22" s="3">
         <v>7900</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>1900</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
         <v>3500</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2331,231 +2409,243 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="F23" s="3">
         <v>5200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>17600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I23" s="3">
         <v>5600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="J23" s="3">
         <v>-500</v>
       </c>
-      <c r="H23" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>13500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>21100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>21100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>31700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>37600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>26600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>50600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>41400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>32100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>24200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>31600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>23000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>19300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>12400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>10300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>8200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>24400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-23500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>23800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>14300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>10100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>12400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>3500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>8600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>23200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>7900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>8400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>7200</v>
       </c>
-      <c r="AK23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F24" s="3">
         <v>3600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>3400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="I24" s="3">
         <v>2600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="J24" s="3">
         <v>1800</v>
       </c>
-      <c r="H24" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>2900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>6000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>6000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>2400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>7500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>6900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>9000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>7000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>7200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>4700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>5500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>3200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>4100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>3300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>2400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>4900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>4000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>3000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>1700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>2600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>2300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>5000</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AI24" s="3">
-        <v>1800</v>
       </c>
       <c r="AJ24" s="3">
         <v>1600</v>
       </c>
-      <c r="AK24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL24" s="3" t="s">
-        <v>3</v>
+      <c r="AK24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AL24" s="3">
+        <v>1600</v>
       </c>
       <c r="AM24" s="3" t="s">
         <v>3</v>
@@ -2563,8 +2653,14 @@
       <c r="AN24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2679,240 +2775,258 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="F26" s="3">
         <v>1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>14100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I26" s="3">
         <v>3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="J26" s="3">
         <v>-2300</v>
       </c>
-      <c r="H26" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>10600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>15100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>15100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>29300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>30100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>19700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>41600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>34500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>24900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>19500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>26000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>19800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>15200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>9100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>7900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>7500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>19400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-18800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>19800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>11300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>8400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>9800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>2700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>6300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>18200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>6200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>5600</v>
       </c>
-      <c r="AK26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="F27" s="3">
         <v>1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>14100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I27" s="3">
         <v>3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="H27" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>10600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>15100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>15100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>29300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>30100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>19700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>41600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>34500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>24900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>19500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>26000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>19800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>15200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>9100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>7900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>7500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>19400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-18800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>19800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>11300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>8400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>9800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>2700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>6300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>18200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>6200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>5600</v>
       </c>
-      <c r="AK27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3027,8 +3141,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3143,8 +3263,14 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3259,8 +3385,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3375,240 +3507,258 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>-5300</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>-3200</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>-12100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
         <v>16400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-14800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>1500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>4000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>3400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>7900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>6800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>1300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>1000</v>
       </c>
-      <c r="AK32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="F33" s="3">
         <v>1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>14100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I33" s="3">
         <v>3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="J33" s="3">
         <v>-2300</v>
       </c>
-      <c r="H33" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>10600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>15100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>15100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>29300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>30100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>19700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>41600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>34500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>24900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>19500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>26000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>19800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>15200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>9100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>7900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>7500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>19400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-18800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>19800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>11300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>8400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>9800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>2700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>6300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>18200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>6200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>5600</v>
       </c>
-      <c r="AK33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3723,245 +3873,263 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="F35" s="3">
         <v>1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>14100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I35" s="3">
         <v>3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="J35" s="3">
         <v>-2300</v>
       </c>
-      <c r="H35" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>10600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>15100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>15100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>29300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>30100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>19700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>41600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>34500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>24900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>19500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>26000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>19800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>15200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>9100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>7900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>7500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>19400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-18800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>19800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>11300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>8400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>9800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>2700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>6300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>18200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>6200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>5600</v>
       </c>
-      <c r="AK35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
-        <v>45382</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AK38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AM38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AN38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AO38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4002,8 +4170,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4044,113 +4214,115 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>92200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>63500</v>
+      </c>
+      <c r="F41" s="3">
         <v>81300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>88200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
+        <v>75200</v>
+      </c>
+      <c r="I41" s="3">
         <v>70800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>78800</v>
       </c>
-      <c r="H41" s="3">
-        <v>240000</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>253000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>205200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>205200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>209300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>246400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>243200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>239300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>207600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>149400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>144700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>104000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>86700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>92300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>98600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>82800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>123600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>116000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>107700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>114100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>96400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>79000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>67400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>55200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>19500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>12200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>32700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>21700</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL41" s="3" t="s">
         <v>3</v>
       </c>
@@ -4160,8 +4332,14 @@
       <c r="AN41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4196,25 +4374,25 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>600</v>
-      </c>
-      <c r="S42" s="3">
-        <v>700</v>
-      </c>
-      <c r="T42" s="3">
-        <v>700</v>
       </c>
       <c r="U42" s="3">
         <v>700</v>
@@ -4229,19 +4407,19 @@
         <v>700</v>
       </c>
       <c r="Y42" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Z42" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AA42" s="3">
         <v>800</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC42" s="3" t="s">
-        <v>3</v>
+      <c r="AB42" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>800</v>
       </c>
       <c r="AD42" s="3" t="s">
         <v>3</v>
@@ -4255,11 +4433,11 @@
       <c r="AG42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI42" s="3">
-        <v>0</v>
+      <c r="AH42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AJ42" s="3">
         <v>0</v>
@@ -4276,113 +4454,119 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>266200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>292700</v>
+      </c>
+      <c r="F43" s="3">
         <v>289500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>262700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
+        <v>250700</v>
+      </c>
+      <c r="I43" s="3">
         <v>279000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="J43" s="3">
         <v>244900</v>
       </c>
-      <c r="H43" s="3">
-        <v>225800</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>220100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>233500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>233500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>219100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>228100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>231100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>254200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>210400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>199500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>183800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>180400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>148000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>129500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>110300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>112800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>104300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>108700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>107000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>93700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>91600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>84800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>84900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>80800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>68600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>64900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>64400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>59300</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4392,8 +4576,14 @@
       <c r="AN43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4427,11 +4617,11 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4485,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="AG44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH44" s="3">
         <v>0</v>
@@ -4493,11 +4683,11 @@
       <c r="AI44" s="3">
         <v>100</v>
       </c>
-      <c r="AJ44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK44" s="3" t="s">
-        <v>3</v>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="3">
+        <v>100</v>
       </c>
       <c r="AL44" s="3" t="s">
         <v>3</v>
@@ -4508,8 +4698,14 @@
       <c r="AN44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP44" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4543,11 +4739,11 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3">
-        <v>0</v>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -4624,113 +4820,119 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>358400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>356200</v>
+      </c>
+      <c r="F46" s="3">
         <v>386200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>350900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
+        <v>325900</v>
+      </c>
+      <c r="I46" s="3">
         <v>349800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3">
         <v>338200</v>
       </c>
-      <c r="H46" s="3">
-        <v>465800</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>473100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>438800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>438800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>442400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>474500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>474500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>494000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>418500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>349300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>329100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>285100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>235400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>222500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>209600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>196300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>228700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>225500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>215500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>208600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>188000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>163800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>152400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>136000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>88000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>77200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>97100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>81100</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4740,8 +4942,14 @@
       <c r="AN46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4775,71 +4983,71 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>1800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>3700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>2900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>1100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>1200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>1500</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI47" s="3" t="s">
-        <v>3</v>
+      <c r="AF47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
       </c>
       <c r="AJ47" s="3" t="s">
         <v>3</v>
@@ -4856,113 +5064,119 @@
       <c r="AN47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>78200</v>
+      </c>
+      <c r="F48" s="3">
         <v>76300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>76600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
+        <v>80200</v>
+      </c>
+      <c r="I48" s="3">
         <v>92000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>93600</v>
       </c>
-      <c r="H48" s="3">
-        <v>94500</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>99500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>109300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>109300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>115700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>105400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>113900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>108800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>91900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>86200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>87400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>89500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>87500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>62700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>68900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>72400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>77900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>81500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>83000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>65700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>14500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>12500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>13200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>12200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>11100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>10800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>11400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>10400</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4972,113 +5186,119 @@
       <c r="AN48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>777700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>784000</v>
+      </c>
+      <c r="F49" s="3">
         <v>786700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>776400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
+        <v>783400</v>
+      </c>
+      <c r="I49" s="3">
         <v>817600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="J49" s="3">
         <v>806900</v>
       </c>
-      <c r="H49" s="3">
-        <v>406000</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>404200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>397000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>397000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>387200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>294300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>321200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>274200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>257700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>251200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>239500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>246300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>233800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>178500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>161300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>167700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>116800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>127400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>124000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>89100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>90200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>93200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>96100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>94900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>92900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>89600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>93700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>41900</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL49" s="3" t="s">
         <v>3</v>
       </c>
@@ -5088,8 +5308,14 @@
       <c r="AN49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5204,8 +5430,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5320,113 +5552,119 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F52" s="3">
         <v>6600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>11800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
+        <v>11300</v>
+      </c>
+      <c r="I52" s="3">
         <v>12700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="J52" s="3">
         <v>12800</v>
       </c>
-      <c r="H52" s="3">
-        <v>9300</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>8100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>6700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>17700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>25700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>22000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>22300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>27100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>30300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>24900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>15200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>15900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>18700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>16300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>12400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>15600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>13400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>13100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>6300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>3300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>3300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>3200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>1200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>1200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5436,8 +5674,14 @@
       <c r="AN52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5552,113 +5796,119 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1249500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1255100</v>
+      </c>
+      <c r="F54" s="3">
         <v>1282100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1242600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
+        <v>1227600</v>
+      </c>
+      <c r="I54" s="3">
         <v>1297000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>1275100</v>
       </c>
-      <c r="H54" s="3">
-        <v>1000900</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1012100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>974100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>974100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>978600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>893300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>929200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>906400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>792900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>709200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>683300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>651500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>582000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>479500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>456400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>456000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>440400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>448000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>439300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>378300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>305800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>275800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>265000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>246400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>195200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>178800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>203400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>134500</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5668,8 +5918,14 @@
       <c r="AN54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5710,8 +5966,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5752,113 +6010,115 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>123600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>130400</v>
+      </c>
+      <c r="F57" s="3">
         <v>10800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>130700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
+        <v>133000</v>
+      </c>
+      <c r="I57" s="3">
         <v>136900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="J57" s="3">
         <v>13900</v>
       </c>
-      <c r="H57" s="3">
-        <v>103900</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>107900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>102400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>102400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>7000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>114600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>126600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>134200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>125300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>110200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>119200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>109000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>97400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>76600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>73900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>78200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>71500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>84200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>98900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>65600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>62500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>58600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>55300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>53900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>52000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>42500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>37200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>32700</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5868,113 +6128,119 @@
       <c r="AN57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>19000</v>
+      </c>
+      <c r="F58" s="3">
         <v>18700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>18000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>19000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>18300</v>
       </c>
       <c r="H58" s="3">
         <v>18100</v>
       </c>
       <c r="I58" s="3">
+        <v>19000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>18300</v>
+      </c>
+      <c r="K58" s="3">
         <v>17600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>17900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>17900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>18500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>17100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>18100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>17000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>15200</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>14600</v>
       </c>
       <c r="R58" s="3">
         <v>15200</v>
       </c>
       <c r="S58" s="3">
+        <v>14600</v>
+      </c>
+      <c r="T58" s="3">
+        <v>15200</v>
+      </c>
+      <c r="U58" s="3">
         <v>16500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>16800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>14300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>14200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>13100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>13600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>14300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>15600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>11700</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
       <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3">
         <v>100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>25500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>30500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>50800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>26800</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5984,113 +6250,119 @@
       <c r="AN58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F59" s="3">
         <v>28000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>12300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
+        <v>21900</v>
+      </c>
+      <c r="I59" s="3">
         <v>28200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="J59" s="3">
         <v>41300</v>
       </c>
-      <c r="H59" s="3">
-        <v>13700</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>16500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>19900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>19900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>32000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>19300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>26900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>33600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>23300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>19000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>16600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>23400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>13300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>8500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>6700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>9500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>8300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>9600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>5200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>8500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>11900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>6700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>9500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>7600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>14400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>10900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>23300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>500</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL59" s="3" t="s">
         <v>3</v>
       </c>
@@ -6100,113 +6372,119 @@
       <c r="AN59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>150200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>163500</v>
+      </c>
+      <c r="F60" s="3">
         <v>166800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>161000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
+        <v>173100</v>
+      </c>
+      <c r="I60" s="3">
         <v>184100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="J60" s="3">
         <v>194200</v>
       </c>
-      <c r="H60" s="3">
-        <v>135700</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>141900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>140300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>140300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>153400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>151100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>171600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>184800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>163700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>143900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>150900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>148800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>127500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>99400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>94900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>100800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>93300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>108200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>119700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>85800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>74400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>65300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>64900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>61500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>92000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>83900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>111300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>60000</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL60" s="3" t="s">
         <v>3</v>
       </c>
@@ -6216,89 +6494,95 @@
       <c r="AN60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>317100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>306700</v>
+      </c>
+      <c r="F61" s="3">
         <v>293700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>221800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
+        <v>202000</v>
+      </c>
+      <c r="I61" s="3">
         <v>232500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="J61" s="3">
         <v>238000</v>
       </c>
-      <c r="H61" s="3">
-        <v>54300</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>58100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>66200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>66200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>69200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>62100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>70800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>67300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>56100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>54600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>56600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>60300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>62200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>40500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>45800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>48000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>51500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>53800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>53900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>40400</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -6312,17 +6596,17 @@
         <v>0</v>
       </c>
       <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>100</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK61" s="3">
-        <v>0</v>
-      </c>
       <c r="AL61" s="3">
         <v>0</v>
       </c>
@@ -6332,113 +6616,119 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F62" s="3">
         <v>2100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I62" s="3">
         <v>1800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="J62" s="3">
         <v>1800</v>
       </c>
-      <c r="H62" s="3">
-        <v>5000</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>4900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>19000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>19000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>11600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>17000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>18400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>21300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>20600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>15000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>18200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>24400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>17100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>12500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>12900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>7300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>9400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>6600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>2800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>2900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>3300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>3800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>4100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>13400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>14100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>14500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>3800</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL62" s="3" t="s">
         <v>3</v>
       </c>
@@ -6448,8 +6738,14 @@
       <c r="AN62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6564,8 +6860,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6680,8 +6982,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6796,113 +7104,119 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>488500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>490600</v>
+      </c>
+      <c r="F66" s="3">
         <v>483400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>408500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
+        <v>408000</v>
+      </c>
+      <c r="I66" s="3">
         <v>457400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>467000</v>
       </c>
-      <c r="H66" s="3">
-        <v>211800</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>222400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>242800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>242800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>252600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>228100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>259400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>270600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>241200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>219100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>222500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>227300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>214200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>157000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>153200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>161700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>152200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>171300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>180200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>129000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>77400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>68500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>68700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>65600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>105400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>98000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>125900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>63800</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6912,8 +7226,14 @@
       <c r="AN66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6954,8 +7274,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7070,8 +7392,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7186,8 +7514,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7302,8 +7636,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7418,113 +7758,119 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>721600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>721500</v>
+      </c>
+      <c r="F72" s="3">
         <v>788400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>800000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
+        <v>754500</v>
+      </c>
+      <c r="I72" s="3">
         <v>782700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>725000</v>
       </c>
-      <c r="H72" s="3">
-        <v>721000</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>721700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>666400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>666400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>664500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>608300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>640500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>622500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>538800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>479400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>453800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>422600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>366300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>321100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>301800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>293700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>288300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>248800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>232200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>226700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>205700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>186900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>133700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>118200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>88000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>79000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>75700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>68800</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7534,8 +7880,14 @@
       <c r="AN72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7650,8 +8002,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7766,8 +8124,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7882,113 +8246,119 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>761000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>764600</v>
+      </c>
+      <c r="F76" s="3">
         <v>798700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>834100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
+        <v>819700</v>
+      </c>
+      <c r="I76" s="3">
         <v>839600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>808100</v>
       </c>
-      <c r="H76" s="3">
-        <v>789100</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>789700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>731300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>731300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>726000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>665300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>669800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>635800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>551800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>490000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>460800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>424100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>367800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>322500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>303200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>294200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>288300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>276700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>259100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>249300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>228400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>207200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>196300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>180800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>89800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>80800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>77500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>70700</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7998,8 +8368,14 @@
       <c r="AN76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8114,245 +8490,263 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
-        <v>45382</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AK80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AM80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AN80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AO80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="F81" s="3">
         <v>1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>14100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I81" s="3">
         <v>3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="J81" s="3">
         <v>-2300</v>
       </c>
-      <c r="H81" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>10600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>15100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>15100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>29300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>30100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>19700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>41600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>34500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>24900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>19500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>26000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>19800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>15200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>9100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>7900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>7500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>19400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-18800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>19800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>11300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>8400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>9800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>2700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>6300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>18200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>6200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>5600</v>
       </c>
-      <c r="AK81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8393,47 +8787,49 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F83" s="3">
+        <v>7500</v>
+      </c>
+      <c r="G83" s="3">
         <v>7200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="H83" s="3">
         <v>11900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="I83" s="3">
         <v>7300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="J83" s="3">
         <v>6800</v>
       </c>
-      <c r="H83" s="3">
-        <v>6600</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>10100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>5200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>5200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>4400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>6200</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
@@ -8476,41 +8872,47 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH83" s="3">
         <v>2300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>5800</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ83" s="3">
+      <c r="AJ83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL83" s="3">
         <v>1700</v>
       </c>
-      <c r="AK83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8625,8 +9027,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8741,8 +9149,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8857,8 +9271,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8973,8 +9393,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9089,124 +9515,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>16500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>24100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
+        <v>40100</v>
+      </c>
+      <c r="I89" s="3">
         <v>5900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
-        <v>3800</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>44600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>20200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>20200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>42400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>31000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>53700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>33100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>60100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>23200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>44300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>25200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>43300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>13500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>23900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>25400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>2300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>15800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>15100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>21000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>15200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>16800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>12700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>2700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>17600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>26300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>11200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>14300</v>
       </c>
-      <c r="AK89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9247,124 +9685,132 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="J91" s="3">
         <v>-2300</v>
       </c>
-      <c r="H91" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-5200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-4100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-3400</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-2800</v>
       </c>
       <c r="R91" s="3">
         <v>-3800</v>
       </c>
       <c r="S91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="T91" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="U91" s="3">
         <v>-3600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-1700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-1600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-2000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>4300</v>
       </c>
-      <c r="AK91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9479,8 +9925,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9595,124 +10047,136 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-2100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="J94" s="3">
         <v>-336600</v>
       </c>
-      <c r="H94" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-12300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-12300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-82900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-7900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-47400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-4000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-15100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-4800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-5100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-49200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-16400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-3500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-58800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-34300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-37600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AK94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9753,8 +10217,10 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9788,11 +10254,11 @@
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9869,8 +10335,14 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9985,8 +10457,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10101,8 +10579,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10217,352 +10701,376 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-6200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-11200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="I100" s="3">
         <v>-16800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="J100" s="3">
         <v>176800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="K100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="O100" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="P100" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="R100" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="S100" s="3">
         <v>-400</v>
       </c>
-      <c r="I100" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-400</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>1200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-5000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-4300</v>
-      </c>
-      <c r="U100" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="V100" s="3">
-        <v>-3500</v>
       </c>
       <c r="W100" s="3">
         <v>-3200</v>
       </c>
       <c r="X100" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="Z100" s="3">
         <v>16700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>16900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>2100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>32700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>23800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-11900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>3300</v>
       </c>
-      <c r="AK100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="G101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="H101" s="3">
         <v>-2600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>1100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-1100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>1200</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>2100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>1200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>2600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>2300</v>
       </c>
       <c r="AF101" s="3">
         <v>100</v>
       </c>
       <c r="AG101" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="AH101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>-100</v>
       </c>
-      <c r="AK101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN101" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP101" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-12200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>10600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
+        <v>9100</v>
+      </c>
+      <c r="I102" s="3">
         <v>-12800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>-161300</v>
       </c>
-      <c r="H102" s="3">
-        <v>-10800</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>38700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>4300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>4300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-43800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>17200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>3800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>25700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>54100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>7700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>40700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>15400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-11100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-6300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>16600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-37000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>17300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>10900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>18400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>14900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>11000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>12300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>35300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>7200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-18200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>11000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>12500</v>
       </c>
-      <c r="AK102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
   <si>
     <t>DAVA</t>
   </si>
@@ -1481,20 +1481,20 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="3">
-        <v>-500</v>
+        <v>900</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>-2300</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1604,7 +1604,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>7800</v>
+        <v>-7700</v>
       </c>
       <c r="E15" s="3">
         <v>7700</v>
@@ -1616,7 +1616,7 @@
         <v>12900</v>
       </c>
       <c r="H15" s="3">
-        <v>8500</v>
+        <v>-8600</v>
       </c>
       <c r="I15" s="3">
         <v>9200</v>
@@ -1773,7 +1773,7 @@
         <v>243400</v>
       </c>
       <c r="F17" s="3">
-        <v>236400</v>
+        <v>235000</v>
       </c>
       <c r="G17" s="3">
         <v>230500</v>
@@ -1895,7 +1895,7 @@
         <v>-3900</v>
       </c>
       <c r="F18" s="3">
-        <v>19500</v>
+        <v>20900</v>
       </c>
       <c r="G18" s="3">
         <v>21300</v>
@@ -2177,19 +2177,19 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3800</v>
+        <v>-11600</v>
       </c>
       <c r="E21" s="3">
         <v>3800</v>
       </c>
       <c r="F21" s="3">
-        <v>24700</v>
+        <v>26000</v>
       </c>
       <c r="G21" s="3">
         <v>34100</v>
       </c>
       <c r="H21" s="3">
-        <v>10600</v>
+        <v>-6500</v>
       </c>
       <c r="I21" s="3">
         <v>15500</v>
@@ -2299,7 +2299,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="E22" s="3">
         <v>7500</v>
@@ -2310,8 +2310,8 @@
       <c r="G22" s="3">
         <v>3700</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+      <c r="H22" s="3">
+        <v>1300</v>
       </c>
       <c r="I22" s="3">
         <v>600</v>
@@ -8795,7 +8795,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7500</v>
+        <v>15100</v>
       </c>
       <c r="E83" s="3">
         <v>7900</v>
